--- a/5W-Programm/Fuenfwochenprogramm_KW30-34.xlsx
+++ b/5W-Programm/Fuenfwochenprogramm_KW30-34.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stracloud-my.sharepoint.com/personal/maltvic_sbsit_com/Documents/Claude_Projects/Nalps_Ultra_KI/5W_Programm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_391211456B66DE5FB370AC13A3B52B1DE327BE02" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AACE2A1-EDA6-440D-9980-5CA783270A42}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_391211456B66DE5FB370AC13A3B52B1DE327BE02" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757CDE31-3BCF-4F9C-BC53-E9187C9FD7BC}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="720" yWindow="765" windowWidth="18945" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="223">
   <si>
     <t>5-Wochenprogramm</t>
   </si>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>Polier</t>
-  </si>
-  <si>
-    <t>Samuel Decurtins (KW30 Ferien -&gt; Stv. Jorge)</t>
   </si>
   <si>
     <t>A --&gt; E = Anfang Ende Gesamtbauprogramm</t>
@@ -2909,7 +2906,7 @@
         <v>3</v>
       </c>
       <c r="P2" s="188" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="Q2" s="174"/>
       <c r="R2" s="174"/>
@@ -2969,7 +2966,7 @@
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="186" t="str">
         <f>"Woche " &amp; WEEKNUM(B4)</f>
@@ -3059,7 +3056,7 @@
     </row>
     <row r="4" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="158">
         <f>B1</f>
@@ -3239,360 +3236,360 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A5" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="181" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" s="181" t="s">
-        <v>8</v>
       </c>
       <c r="C5" s="157"/>
       <c r="D5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="157"/>
       <c r="F5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="157"/>
       <c r="H5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" s="157"/>
       <c r="J5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" s="157"/>
       <c r="L5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" s="157"/>
       <c r="N5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O5" s="157"/>
       <c r="P5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="157"/>
       <c r="R5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S5" s="157"/>
       <c r="T5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5" s="157"/>
       <c r="V5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W5" s="157"/>
       <c r="X5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="157"/>
       <c r="Z5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA5" s="157"/>
       <c r="AB5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC5" s="157"/>
       <c r="AD5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE5" s="157"/>
       <c r="AF5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG5" s="157"/>
       <c r="AH5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI5" s="157"/>
       <c r="AJ5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" s="157"/>
       <c r="AL5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM5" s="157"/>
       <c r="AN5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO5" s="157"/>
       <c r="AP5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" s="157"/>
       <c r="AR5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS5" s="157"/>
       <c r="AT5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU5" s="157"/>
       <c r="AV5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW5" s="157"/>
       <c r="AX5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY5" s="157"/>
       <c r="AZ5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA5" s="157"/>
       <c r="BB5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC5" s="157"/>
       <c r="BD5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BE5" s="157"/>
       <c r="BF5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BG5" s="157"/>
       <c r="BH5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI5" s="157"/>
       <c r="BJ5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BK5" s="157"/>
       <c r="BL5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BM5" s="157"/>
       <c r="BN5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BO5" s="157"/>
       <c r="BP5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BQ5" s="157"/>
       <c r="BR5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BS5" s="157"/>
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
       <c r="B6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="H6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="L6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="N6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="P6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="R6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="T6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="U6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="V6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="X6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Y6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="Z6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AA6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AB6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="AD6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AE6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AF6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AG6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AH6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AL6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AM6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AN6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AO6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AP6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AQ6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="AR6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AS6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AT6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AU6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AV6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AW6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AX6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AY6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AZ6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BA6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BA6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BB6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BC6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BD6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="BE6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="BF6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BG6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BH6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BI6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BJ6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BK6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BL6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BM6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BM6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BN6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BO6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BO6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BP6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BQ6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BR6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS6" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="BS6" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3743,7 +3740,7 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A9" s="122" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="31"/>
@@ -3818,7 +3815,7 @@
     </row>
     <row r="10" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A10" s="115" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="31"/>
@@ -4039,7 +4036,7 @@
     </row>
     <row r="13" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A13" s="115" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="116"/>
       <c r="C13" s="117"/>
@@ -4114,7 +4111,7 @@
     </row>
     <row r="14" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A14" s="115" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="31"/>
@@ -4262,7 +4259,7 @@
     </row>
     <row r="16" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A16" s="124" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="119"/>
       <c r="C16" s="120"/>
@@ -4337,7 +4334,7 @@
     </row>
     <row r="17" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A17" s="124" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="91"/>
       <c r="C17" s="92"/>
@@ -4412,7 +4409,7 @@
     </row>
     <row r="18" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A18" s="115" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="125"/>
       <c r="C18" s="31"/>
@@ -4487,7 +4484,7 @@
     </row>
     <row r="19" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A19" s="124" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="31"/>
@@ -4562,7 +4559,7 @@
     </row>
     <row r="20" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A20" s="124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="31"/>
@@ -4637,7 +4634,7 @@
     </row>
     <row r="21" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A21" s="124" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="31"/>
@@ -4712,7 +4709,7 @@
     </row>
     <row r="22" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A22" s="124" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="31"/>
@@ -4787,7 +4784,7 @@
     </row>
     <row r="23" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A23" s="124" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="94"/>
       <c r="C23" s="95"/>
@@ -4862,7 +4859,7 @@
     </row>
     <row r="24" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A24" s="124" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="31"/>
@@ -4937,7 +4934,7 @@
     </row>
     <row r="25" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A25" s="124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="31"/>
@@ -5012,7 +5009,7 @@
     </row>
     <row r="26" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A26" s="124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="31"/>
@@ -5087,7 +5084,7 @@
     </row>
     <row r="27" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A27" s="124" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="32"/>
       <c r="C27" s="31"/>
@@ -5162,7 +5159,7 @@
     </row>
     <row r="28" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A28" s="124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="32"/>
       <c r="C28" s="31"/>
@@ -5237,7 +5234,7 @@
     </row>
     <row r="29" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A29" s="115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="32"/>
       <c r="C29" s="31"/>
@@ -5312,7 +5309,7 @@
     </row>
     <row r="30" spans="1:71" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="32"/>
       <c r="C30" s="31"/>
@@ -5460,7 +5457,7 @@
     </row>
     <row r="32" spans="1:71" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="122" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="32"/>
       <c r="C32" s="31"/>
@@ -5535,7 +5532,7 @@
     </row>
     <row r="33" spans="1:71" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="115" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" s="32"/>
       <c r="C33" s="31"/>
@@ -5610,7 +5607,7 @@
     </row>
     <row r="34" spans="1:71" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="32"/>
       <c r="C34" s="31"/>
@@ -5758,7 +5755,7 @@
     </row>
     <row r="36" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A36" s="126" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="31"/>
@@ -5833,7 +5830,7 @@
     </row>
     <row r="37" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A37" s="127" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="31"/>
@@ -5850,7 +5847,7 @@
       <c r="N37" s="26"/>
       <c r="O37" s="28"/>
       <c r="P37" s="128" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q37" s="31"/>
       <c r="R37" s="9"/>
@@ -5910,7 +5907,7 @@
     </row>
     <row r="38" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A38" s="129" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="32"/>
       <c r="C38" s="31"/>
@@ -5985,7 +5982,7 @@
     </row>
     <row r="39" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A39" s="129" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" s="49"/>
       <c r="C39" s="31"/>
@@ -6020,7 +6017,7 @@
       <c r="AF39" s="9"/>
       <c r="AG39" s="10"/>
       <c r="AH39" s="128" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AI39" s="10"/>
       <c r="AJ39" s="9"/>
@@ -6062,7 +6059,7 @@
     </row>
     <row r="40" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A40" s="129" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" s="128"/>
       <c r="C40" s="31"/>
@@ -6089,7 +6086,7 @@
       <c r="X40" s="54"/>
       <c r="Y40" s="10"/>
       <c r="Z40" s="134" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA40" s="34"/>
       <c r="AB40" s="33"/>
@@ -6139,7 +6136,7 @@
     </row>
     <row r="41" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A41" s="129" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" s="128"/>
       <c r="C41" s="31"/>
@@ -6198,7 +6195,7 @@
       <c r="BD41" s="33"/>
       <c r="BE41" s="35"/>
       <c r="BF41" s="128" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG41" s="31"/>
       <c r="BH41" s="9"/>
@@ -6289,7 +6286,7 @@
     </row>
     <row r="43" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A43" s="130" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" s="49"/>
       <c r="C43" s="31"/>
@@ -6364,7 +6361,7 @@
     </row>
     <row r="44" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A44" s="129" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="100"/>
       <c r="C44" s="101"/>
@@ -6439,7 +6436,7 @@
     </row>
     <row r="45" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A45" s="127" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" s="32"/>
       <c r="C45" s="31"/>
@@ -6514,7 +6511,7 @@
     </row>
     <row r="46" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A46" s="127" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" s="32"/>
       <c r="C46" s="31"/>
@@ -6589,7 +6586,7 @@
     </row>
     <row r="47" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A47" s="127" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" s="32"/>
       <c r="C47" s="31"/>
@@ -6664,7 +6661,7 @@
     </row>
     <row r="48" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A48" s="127" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="32"/>
       <c r="C48" s="31"/>
@@ -6739,7 +6736,7 @@
     </row>
     <row r="49" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A49" s="127" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" s="32"/>
       <c r="C49" s="31"/>
@@ -6814,7 +6811,7 @@
     </row>
     <row r="50" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A50" s="127" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" s="32"/>
       <c r="C50" s="31"/>
@@ -6889,7 +6886,7 @@
     </row>
     <row r="51" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A51" s="127" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" s="32"/>
       <c r="C51" s="31"/>
@@ -6964,7 +6961,7 @@
     </row>
     <row r="52" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A52" s="127" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" s="32"/>
       <c r="C52" s="31"/>
@@ -7039,7 +7036,7 @@
     </row>
     <row r="53" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A53" s="127" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" s="32"/>
       <c r="C53" s="31"/>
@@ -7114,7 +7111,7 @@
     </row>
     <row r="54" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A54" s="127" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" s="32"/>
       <c r="C54" s="31"/>
@@ -7189,7 +7186,7 @@
     </row>
     <row r="55" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A55" s="127" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="32"/>
       <c r="C55" s="31"/>
@@ -7264,7 +7261,7 @@
     </row>
     <row r="56" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A56" s="126" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" s="32"/>
       <c r="C56" s="31"/>
@@ -7339,7 +7336,7 @@
     </row>
     <row r="57" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A57" s="127" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" s="103"/>
       <c r="C57" s="104"/>
@@ -7414,7 +7411,7 @@
     </row>
     <row r="58" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A58" s="127" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" s="32"/>
       <c r="C58" s="31"/>
@@ -7489,7 +7486,7 @@
     </row>
     <row r="59" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A59" s="127" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" s="32"/>
       <c r="C59" s="31"/>
@@ -7564,7 +7561,7 @@
     </row>
     <row r="60" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A60" s="127" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" s="32"/>
       <c r="C60" s="31"/>
@@ -7712,7 +7709,7 @@
     </row>
     <row r="62" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A62" s="126" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" s="32"/>
       <c r="C62" s="31"/>
@@ -7787,7 +7784,7 @@
     </row>
     <row r="63" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A63" s="127" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63" s="32"/>
       <c r="C63" s="31"/>
@@ -7862,7 +7859,7 @@
     </row>
     <row r="64" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A64" s="127" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" s="32"/>
       <c r="C64" s="31"/>
@@ -7937,7 +7934,7 @@
     </row>
     <row r="65" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A65" s="127" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65" s="32"/>
       <c r="C65" s="31"/>
@@ -8158,7 +8155,7 @@
     </row>
     <row r="68" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A68" s="126" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68" s="32"/>
       <c r="C68" s="31"/>
@@ -8233,7 +8230,7 @@
     </row>
     <row r="69" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A69" s="127" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69" s="109"/>
       <c r="C69" s="110"/>
@@ -8308,7 +8305,7 @@
     </row>
     <row r="70" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A70" s="127" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70" s="119"/>
       <c r="C70" s="120"/>
@@ -8383,7 +8380,7 @@
     </row>
     <row r="71" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A71" s="127" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" s="32"/>
       <c r="C71" s="31"/>
@@ -8458,7 +8455,7 @@
     </row>
     <row r="72" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A72" s="127" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B72" s="109"/>
       <c r="C72" s="110"/>
@@ -8533,7 +8530,7 @@
     </row>
     <row r="73" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A73" s="127" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" s="32"/>
       <c r="C73" s="31"/>
@@ -8608,7 +8605,7 @@
     </row>
     <row r="74" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A74" s="127" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74" s="32"/>
       <c r="C74" s="31"/>
@@ -8683,7 +8680,7 @@
     </row>
     <row r="75" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A75" s="127" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75" s="32"/>
       <c r="C75" s="31"/>
@@ -8758,7 +8755,7 @@
     </row>
     <row r="76" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A76" s="131" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" s="32"/>
       <c r="C76" s="31"/>
@@ -8833,7 +8830,7 @@
     </row>
     <row r="77" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A77" s="115" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" s="32"/>
       <c r="C77" s="31"/>
@@ -8908,7 +8905,7 @@
     </row>
     <row r="78" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A78" s="115" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" s="32"/>
       <c r="C78" s="31"/>
@@ -8983,7 +8980,7 @@
     </row>
     <row r="79" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A79" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79" s="112"/>
       <c r="C79" s="113"/>
@@ -9058,7 +9055,7 @@
     </row>
     <row r="80" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A80" s="115" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" s="32"/>
       <c r="C80" s="31"/>
@@ -9133,7 +9130,7 @@
     </row>
     <row r="81" spans="1:71" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="131" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81" s="32"/>
       <c r="C81" s="31"/>
@@ -9164,7 +9161,7 @@
       <c r="AB81" s="33"/>
       <c r="AC81" s="35"/>
       <c r="AD81" s="128" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AE81" s="31"/>
       <c r="AF81" s="9"/>
@@ -9210,7 +9207,7 @@
     </row>
     <row r="82" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A82" s="131" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="31"/>
@@ -9233,7 +9230,7 @@
       <c r="T82" s="9"/>
       <c r="U82" s="10"/>
       <c r="V82" s="132" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W82" s="10"/>
       <c r="X82" s="9"/>
@@ -9287,7 +9284,7 @@
     </row>
     <row r="83" spans="1:71" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="131" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B83" s="109"/>
       <c r="C83" s="110"/>
@@ -9362,7 +9359,7 @@
     </row>
     <row r="84" spans="1:71" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="131" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B84" s="32"/>
       <c r="C84" s="31"/>
@@ -9437,7 +9434,7 @@
     </row>
     <row r="85" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A85" s="131" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B85" s="32"/>
       <c r="C85" s="31"/>
@@ -9512,7 +9509,7 @@
     </row>
     <row r="86" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A86" s="131" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B86" s="32"/>
       <c r="C86" s="31"/>
@@ -9660,7 +9657,7 @@
     </row>
     <row r="88" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A88" s="126" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88" s="32"/>
       <c r="C88" s="31"/>
@@ -9735,7 +9732,7 @@
     </row>
     <row r="89" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A89" s="127" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89" s="112"/>
       <c r="C89" s="113"/>
@@ -9810,7 +9807,7 @@
     </row>
     <row r="90" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A90" s="127" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90" s="112"/>
       <c r="C90" s="113"/>
@@ -9885,7 +9882,7 @@
     </row>
     <row r="91" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A91" s="127" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91" s="112"/>
       <c r="C91" s="113"/>
@@ -9960,7 +9957,7 @@
     </row>
     <row r="92" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A92" s="127" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92" s="32"/>
       <c r="C92" s="113"/>
@@ -10035,7 +10032,7 @@
     </row>
     <row r="93" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A93" s="127" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93" s="32"/>
       <c r="C93" s="31"/>
@@ -10110,7 +10107,7 @@
     </row>
     <row r="94" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A94" s="127" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B94" s="32"/>
       <c r="C94" s="31"/>
@@ -10185,7 +10182,7 @@
     </row>
     <row r="95" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A95" s="126" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B95" s="32"/>
       <c r="C95" s="31"/>
@@ -10260,7 +10257,7 @@
     </row>
     <row r="96" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A96" s="126" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" s="32"/>
       <c r="C96" s="31"/>
@@ -10335,10 +10332,10 @@
     </row>
     <row r="97" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A97" s="127" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97" s="128" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C97" s="31"/>
       <c r="D97" s="9"/>
@@ -10412,7 +10409,7 @@
     </row>
     <row r="98" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A98" s="127" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" s="32"/>
       <c r="C98" s="31"/>
@@ -10487,7 +10484,7 @@
     </row>
     <row r="99" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A99" s="127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99" s="32"/>
       <c r="C99" s="31"/>
@@ -10510,7 +10507,7 @@
       <c r="T99" s="9"/>
       <c r="U99" s="10"/>
       <c r="V99" s="132" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W99" s="10"/>
       <c r="X99" s="9"/>
@@ -10564,7 +10561,7 @@
     </row>
     <row r="100" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A100" s="127" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B100" s="32"/>
       <c r="C100" s="31"/>
@@ -10639,7 +10636,7 @@
     </row>
     <row r="101" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A101" s="127" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" s="32"/>
       <c r="C101" s="31"/>
@@ -10714,7 +10711,7 @@
     </row>
     <row r="102" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A102" s="127" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B102" s="32"/>
       <c r="C102" s="31"/>
@@ -10789,7 +10786,7 @@
     </row>
     <row r="103" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A103" s="127" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" s="32"/>
       <c r="C103" s="31"/>
@@ -10822,7 +10819,7 @@
       <c r="AD103" s="32"/>
       <c r="AE103" s="31"/>
       <c r="AF103" s="132" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AG103" s="10"/>
       <c r="AH103" s="9"/>
@@ -10866,10 +10863,10 @@
     </row>
     <row r="104" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A104" s="127" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" s="128" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C104" s="31"/>
       <c r="D104" s="9"/>
@@ -10943,7 +10940,7 @@
     </row>
     <row r="105" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A105" s="129" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105" s="32"/>
       <c r="C105" s="31"/>
@@ -11018,7 +11015,7 @@
     </row>
     <row r="106" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A106" s="129" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B106" s="32"/>
       <c r="C106" s="31"/>
@@ -11093,7 +11090,7 @@
     </row>
     <row r="107" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="129" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107" s="32"/>
       <c r="C107" s="31"/>
@@ -11168,7 +11165,7 @@
     </row>
     <row r="108" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A108" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B108" s="176">
         <v>22</v>
@@ -11313,7 +11310,7 @@
     </row>
     <row r="109" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109" s="153"/>
       <c r="C109" s="154"/>
@@ -11389,7 +11386,7 @@
     <row r="110" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="177"/>
       <c r="B110" s="162" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C110" s="163"/>
       <c r="D110" s="163"/>
@@ -11405,7 +11402,7 @@
       <c r="N110" s="163"/>
       <c r="O110" s="164"/>
       <c r="P110" s="162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q110" s="163"/>
       <c r="R110" s="163"/>
@@ -11421,7 +11418,7 @@
       <c r="AB110" s="163"/>
       <c r="AC110" s="164"/>
       <c r="AD110" s="162" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AE110" s="163"/>
       <c r="AF110" s="163"/>
@@ -11437,7 +11434,7 @@
       <c r="AP110" s="163"/>
       <c r="AQ110" s="164"/>
       <c r="AR110" s="162" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AS110" s="163"/>
       <c r="AT110" s="163"/>
@@ -11453,7 +11450,7 @@
       <c r="BD110" s="163"/>
       <c r="BE110" s="164"/>
       <c r="BF110" s="162" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="BG110" s="163"/>
       <c r="BH110" s="163"/>
@@ -12158,7 +12155,7 @@
         <v>3</v>
       </c>
       <c r="P2" s="188" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q2" s="174"/>
       <c r="R2" s="174"/>
@@ -12218,7 +12215,7 @@
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="186" t="str">
         <f>"Woche " &amp; WEEKNUM(B4)</f>
@@ -12308,7 +12305,7 @@
     </row>
     <row r="4" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="158">
         <f>B1</f>
@@ -12488,360 +12485,360 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A5" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="181" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" s="181" t="s">
-        <v>8</v>
       </c>
       <c r="C5" s="157"/>
       <c r="D5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="157"/>
       <c r="F5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="157"/>
       <c r="H5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" s="157"/>
       <c r="J5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" s="157"/>
       <c r="L5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" s="157"/>
       <c r="N5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O5" s="157"/>
       <c r="P5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="157"/>
       <c r="R5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S5" s="157"/>
       <c r="T5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5" s="157"/>
       <c r="V5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W5" s="157"/>
       <c r="X5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="157"/>
       <c r="Z5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA5" s="157"/>
       <c r="AB5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC5" s="157"/>
       <c r="AD5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE5" s="157"/>
       <c r="AF5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG5" s="157"/>
       <c r="AH5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI5" s="157"/>
       <c r="AJ5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" s="157"/>
       <c r="AL5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM5" s="157"/>
       <c r="AN5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO5" s="157"/>
       <c r="AP5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" s="157"/>
       <c r="AR5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS5" s="157"/>
       <c r="AT5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU5" s="157"/>
       <c r="AV5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW5" s="157"/>
       <c r="AX5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY5" s="157"/>
       <c r="AZ5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA5" s="157"/>
       <c r="BB5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC5" s="157"/>
       <c r="BD5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BE5" s="157"/>
       <c r="BF5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BG5" s="157"/>
       <c r="BH5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI5" s="157"/>
       <c r="BJ5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BK5" s="157"/>
       <c r="BL5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BM5" s="157"/>
       <c r="BN5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BO5" s="157"/>
       <c r="BP5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BQ5" s="157"/>
       <c r="BR5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BS5" s="157"/>
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
       <c r="B6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="H6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="L6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="N6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="P6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="R6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="T6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="U6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="V6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="X6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Y6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="Z6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AA6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AB6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="AD6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AE6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AF6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AG6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AH6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AL6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AM6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AN6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AO6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AP6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AQ6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="AR6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AS6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AT6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AU6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AV6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AW6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AX6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AY6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AZ6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BA6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BA6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BB6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BC6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BD6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="BE6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="BF6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BG6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BH6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BI6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BJ6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BK6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BL6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BM6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BM6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BN6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BO6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BO6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BP6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BQ6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BR6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS6" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="BS6" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -12919,7 +12916,7 @@
     </row>
     <row r="8" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="65" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8" s="32"/>
       <c r="C8" s="31"/>
@@ -12994,7 +12991,7 @@
     </row>
     <row r="9" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="69" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
@@ -13653,7 +13650,7 @@
     </row>
     <row r="18" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="31"/>
@@ -13728,7 +13725,7 @@
     </row>
     <row r="19" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="31"/>
@@ -13803,7 +13800,7 @@
     </row>
     <row r="20" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="31"/>
@@ -13878,7 +13875,7 @@
     </row>
     <row r="21" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="31"/>
@@ -13953,7 +13950,7 @@
     </row>
     <row r="22" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="31"/>
@@ -14028,7 +14025,7 @@
     </row>
     <row r="23" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="31"/>
@@ -14047,7 +14044,7 @@
       <c r="P23" s="48"/>
       <c r="Q23" s="47"/>
       <c r="R23" s="77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S23" s="55"/>
       <c r="T23" s="46"/>
@@ -14105,7 +14102,7 @@
     </row>
     <row r="24" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="31"/>
@@ -14180,7 +14177,7 @@
     </row>
     <row r="25" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="31"/>
@@ -14255,7 +14252,7 @@
     </row>
     <row r="26" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="31"/>
@@ -14330,7 +14327,7 @@
     </row>
     <row r="27" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B27" s="32"/>
       <c r="C27" s="31"/>
@@ -14478,7 +14475,7 @@
     </row>
     <row r="29" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A29" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B29" s="32"/>
       <c r="C29" s="31"/>
@@ -14553,7 +14550,7 @@
     </row>
     <row r="30" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A30" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B30" s="32"/>
       <c r="C30" s="31"/>
@@ -14628,7 +14625,7 @@
     </row>
     <row r="31" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A31" s="53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="31"/>
@@ -14703,7 +14700,7 @@
     </row>
     <row r="32" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B32" s="72"/>
       <c r="C32" s="20"/>
@@ -14726,7 +14723,7 @@
       <c r="T32" s="46"/>
       <c r="U32" s="47"/>
       <c r="V32" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="W32" s="10"/>
       <c r="X32" s="9"/>
@@ -14739,7 +14736,7 @@
       <c r="AE32" s="31"/>
       <c r="AF32" s="9"/>
       <c r="AG32" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AH32" s="9"/>
       <c r="AI32" s="10"/>
@@ -14782,17 +14779,17 @@
     </row>
     <row r="33" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A33" s="71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9"/>
       <c r="E33" s="10"/>
       <c r="F33" s="29"/>
       <c r="G33" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H33" s="29"/>
       <c r="I33" s="20"/>
@@ -14861,7 +14858,7 @@
     </row>
     <row r="34" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A34" s="71" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="32"/>
       <c r="C34" s="31"/>
@@ -14870,7 +14867,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="10"/>
       <c r="H34" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="29"/>
@@ -14885,7 +14882,7 @@
       <c r="S34" s="20"/>
       <c r="T34" s="29"/>
       <c r="U34" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V34" s="29"/>
       <c r="W34" s="10"/>
@@ -14940,7 +14937,7 @@
     </row>
     <row r="35" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A35" s="36" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" s="32"/>
       <c r="C35" s="31"/>
@@ -14975,10 +14972,10 @@
       <c r="AF35" s="9"/>
       <c r="AG35" s="10"/>
       <c r="AH35" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI35" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="AI35" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="AJ35" s="46"/>
       <c r="AK35" s="47"/>
@@ -15019,7 +15016,7 @@
     </row>
     <row r="36" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A36" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="31"/>
@@ -15058,7 +15055,7 @@
       <c r="AJ36" s="46"/>
       <c r="AK36" s="47"/>
       <c r="AL36" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AM36" s="10"/>
       <c r="AN36" s="26"/>
@@ -15067,7 +15064,7 @@
       <c r="AQ36" s="28"/>
       <c r="AR36" s="32"/>
       <c r="AS36" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AT36" s="9"/>
       <c r="AU36" s="10"/>
@@ -15098,7 +15095,7 @@
     </row>
     <row r="37" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A37" s="36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="31"/>
@@ -15145,10 +15142,10 @@
       <c r="AR37" s="32"/>
       <c r="AS37" s="31"/>
       <c r="AT37" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AU37" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="AU37" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="AV37" s="9"/>
       <c r="AW37" s="10"/>
@@ -15177,7 +15174,7 @@
     </row>
     <row r="38" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A38" s="36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="32"/>
       <c r="C38" s="31"/>
@@ -15226,7 +15223,7 @@
       <c r="AT38" s="9"/>
       <c r="AU38" s="10"/>
       <c r="AV38" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AW38" s="10"/>
       <c r="AX38" s="9"/>
@@ -15239,7 +15236,7 @@
       <c r="BE38" s="28"/>
       <c r="BF38" s="32"/>
       <c r="BG38" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BH38" s="9"/>
       <c r="BI38" s="10"/>
@@ -15256,7 +15253,7 @@
     </row>
     <row r="39" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A39" s="36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B39" s="32"/>
       <c r="C39" s="31"/>
@@ -15317,14 +15314,14 @@
       <c r="BF39" s="32"/>
       <c r="BG39" s="31"/>
       <c r="BH39" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BI39" s="10"/>
       <c r="BJ39" s="9"/>
       <c r="BK39" s="10"/>
       <c r="BL39" s="9"/>
       <c r="BM39" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BN39" s="9"/>
       <c r="BO39" s="10"/>
@@ -15408,7 +15405,7 @@
     </row>
     <row r="41" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A41" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B41" s="32"/>
       <c r="C41" s="31"/>
@@ -15441,10 +15438,10 @@
       <c r="AD41" s="32"/>
       <c r="AE41" s="31"/>
       <c r="AF41" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG41" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="AG41" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="AH41" s="9"/>
       <c r="AI41" s="10"/>
@@ -15487,7 +15484,7 @@
     </row>
     <row r="42" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A42" s="36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B42" s="32"/>
       <c r="C42" s="31"/>
@@ -15552,10 +15549,10 @@
       <c r="BJ42" s="9"/>
       <c r="BK42" s="10"/>
       <c r="BL42" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BM42" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="BM42" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="BN42" s="9"/>
       <c r="BO42" s="10"/>
@@ -16077,7 +16074,7 @@
     </row>
     <row r="50" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A50" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B50" s="32"/>
       <c r="C50" s="31"/>
@@ -16152,7 +16149,7 @@
     </row>
     <row r="51" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A51" s="65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B51" s="32"/>
       <c r="C51" s="31"/>
@@ -16227,7 +16224,7 @@
     </row>
     <row r="52" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A52" s="67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B52" s="32"/>
       <c r="C52" s="31"/>
@@ -16302,14 +16299,14 @@
     </row>
     <row r="53" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A53" s="67" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B53" s="49"/>
       <c r="C53" s="31"/>
       <c r="D53" s="9"/>
       <c r="E53" s="10"/>
       <c r="F53" s="54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G53" s="10"/>
       <c r="H53" s="9"/>
@@ -16379,7 +16376,7 @@
     </row>
     <row r="54" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A54" s="67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B54" s="49"/>
       <c r="C54" s="31"/>
@@ -16410,7 +16407,7 @@
       <c r="AB54" s="33"/>
       <c r="AC54" s="35"/>
       <c r="AD54" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE54" s="31"/>
       <c r="AF54" s="9"/>
@@ -16456,7 +16453,7 @@
     </row>
     <row r="55" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A55" s="67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B55" s="49"/>
       <c r="C55" s="31"/>
@@ -16750,7 +16747,7 @@
     </row>
     <row r="59" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A59" s="65" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B59" s="32"/>
       <c r="C59" s="31"/>
@@ -16825,7 +16822,7 @@
     </row>
     <row r="60" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A60" s="66" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B60" s="70"/>
       <c r="C60" s="55"/>
@@ -16900,7 +16897,7 @@
     </row>
     <row r="61" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A61" s="66" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B61" s="32"/>
       <c r="C61" s="31"/>
@@ -16975,7 +16972,7 @@
     </row>
     <row r="62" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A62" s="66" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B62" s="32"/>
       <c r="C62" s="10"/>
@@ -17050,7 +17047,7 @@
     </row>
     <row r="63" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A63" s="66" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B63" s="32"/>
       <c r="C63" s="31"/>
@@ -17271,7 +17268,7 @@
     </row>
     <row r="66" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A66" s="65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B66" s="32"/>
       <c r="C66" s="31"/>
@@ -17346,7 +17343,7 @@
     </row>
     <row r="67" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A67" s="65" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B67" s="32"/>
       <c r="C67" s="31"/>
@@ -17421,7 +17418,7 @@
     </row>
     <row r="68" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A68" s="66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B68" s="32"/>
       <c r="C68" s="31"/>
@@ -17445,11 +17442,11 @@
       <c r="U68" s="47"/>
       <c r="V68" s="10"/>
       <c r="W68" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="X68" s="9"/>
       <c r="Y68" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Z68" s="33"/>
       <c r="AA68" s="34"/>
@@ -17500,7 +17497,7 @@
     </row>
     <row r="69" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A69" s="66" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B69" s="32"/>
       <c r="C69" s="31"/>
@@ -17519,7 +17516,7 @@
       <c r="P69" s="48"/>
       <c r="Q69" s="47"/>
       <c r="R69" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S69" s="10"/>
       <c r="T69" s="46"/>
@@ -17542,7 +17539,7 @@
       <c r="AK69" s="47"/>
       <c r="AL69" s="9"/>
       <c r="AM69" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AN69" s="33"/>
       <c r="AO69" s="34"/>
@@ -17579,7 +17576,7 @@
     </row>
     <row r="70" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A70" s="66" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B70" s="32"/>
       <c r="C70" s="31"/>
@@ -17624,7 +17621,7 @@
       <c r="AP70" s="33"/>
       <c r="AQ70" s="35"/>
       <c r="AR70" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS70" s="31"/>
       <c r="AT70" s="9"/>
@@ -17643,7 +17640,7 @@
       <c r="BG70" s="31"/>
       <c r="BH70" s="9"/>
       <c r="BI70" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BJ70" s="9"/>
       <c r="BK70" s="10"/>
@@ -17658,7 +17655,7 @@
     </row>
     <row r="71" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A71" s="66" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B71" s="32"/>
       <c r="C71" s="31"/>
@@ -17721,7 +17718,7 @@
       <c r="BH71" s="9"/>
       <c r="BI71" s="10"/>
       <c r="BJ71" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BK71" s="10"/>
       <c r="BL71" s="9"/>
@@ -17735,7 +17732,7 @@
     </row>
     <row r="72" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A72" s="66" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B72" s="32"/>
       <c r="C72" s="31"/>
@@ -17794,14 +17791,14 @@
       <c r="BD72" s="33"/>
       <c r="BE72" s="35"/>
       <c r="BF72" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BG72" s="31"/>
       <c r="BH72" s="9"/>
       <c r="BI72" s="10"/>
       <c r="BJ72" s="9"/>
       <c r="BK72" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BL72" s="9"/>
       <c r="BM72" s="10"/>
@@ -17887,7 +17884,7 @@
     </row>
     <row r="74" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A74" s="66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B74" s="32"/>
       <c r="C74" s="31"/>
@@ -17962,7 +17959,7 @@
     </row>
     <row r="75" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A75" s="66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B75" s="32"/>
       <c r="C75" s="31"/>
@@ -18037,7 +18034,7 @@
     </row>
     <row r="76" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A76" s="66" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B76" s="32"/>
       <c r="C76" s="31"/>
@@ -18185,7 +18182,7 @@
     </row>
     <row r="78" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A78" s="66" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B78" s="32"/>
       <c r="C78" s="31"/>
@@ -18406,7 +18403,7 @@
     </row>
     <row r="81" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A81" s="65" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B81" s="32"/>
       <c r="C81" s="31"/>
@@ -18481,7 +18478,7 @@
     </row>
     <row r="82" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A82" s="66" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B82" s="32"/>
       <c r="C82" s="31"/>
@@ -18556,7 +18553,7 @@
     </row>
     <row r="83" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A83" s="66" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B83" s="32"/>
       <c r="C83" s="31"/>
@@ -18631,7 +18628,7 @@
     </row>
     <row r="84" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A84" s="66" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B84" s="32"/>
       <c r="C84" s="31"/>
@@ -18706,7 +18703,7 @@
     </row>
     <row r="85" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A85" s="66" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B85" s="32"/>
       <c r="C85" s="31"/>
@@ -18781,7 +18778,7 @@
     </row>
     <row r="86" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A86" s="66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B86" s="32"/>
       <c r="C86" s="31"/>
@@ -18856,7 +18853,7 @@
     </row>
     <row r="87" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A87" s="66" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B87" s="32"/>
       <c r="C87" s="31"/>
@@ -18931,7 +18928,7 @@
     </row>
     <row r="88" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A88" s="66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B88" s="32"/>
       <c r="C88" s="31"/>
@@ -19006,7 +19003,7 @@
     </row>
     <row r="89" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A89" s="66" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B89" s="32"/>
       <c r="C89" s="31"/>
@@ -19154,7 +19151,7 @@
     </row>
     <row r="91" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A91" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B91" s="32"/>
       <c r="C91" s="31"/>
@@ -19229,7 +19226,7 @@
     </row>
     <row r="92" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A92" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B92" s="41"/>
       <c r="C92" s="42"/>
@@ -19304,7 +19301,7 @@
     </row>
     <row r="93" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A93" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B93" s="59"/>
       <c r="C93" s="10"/>
@@ -19379,7 +19376,7 @@
     </row>
     <row r="94" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A94" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B94" s="32"/>
       <c r="C94" s="31"/>
@@ -19454,7 +19451,7 @@
     </row>
     <row r="95" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A95" s="45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B95" s="59"/>
       <c r="C95" s="10"/>
@@ -19529,7 +19526,7 @@
     </row>
     <row r="96" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A96" s="45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B96" s="32"/>
       <c r="C96" s="31"/>
@@ -19604,7 +19601,7 @@
     </row>
     <row r="97" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A97" s="45" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B97" s="32"/>
       <c r="C97" s="31"/>
@@ -19679,7 +19676,7 @@
     </row>
     <row r="98" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A98" s="45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B98" s="32"/>
       <c r="C98" s="31"/>
@@ -19754,7 +19751,7 @@
     </row>
     <row r="99" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A99" s="45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B99" s="32"/>
       <c r="C99" s="31"/>
@@ -19974,7 +19971,7 @@
     </row>
     <row r="102" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A102" s="65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B102" s="32"/>
       <c r="C102" s="31"/>
@@ -20049,7 +20046,7 @@
     </row>
     <row r="103" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A103" s="65" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B103" s="32"/>
       <c r="C103" s="31"/>
@@ -20270,7 +20267,7 @@
     </row>
     <row r="106" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A106" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B106" s="32"/>
       <c r="C106" s="31"/>
@@ -20345,7 +20342,7 @@
     </row>
     <row r="107" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A107" s="66" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B107" s="32"/>
       <c r="C107" s="31"/>
@@ -20493,7 +20490,7 @@
     </row>
     <row r="109" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A109" s="65" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B109" s="32"/>
       <c r="C109" s="31"/>
@@ -20568,7 +20565,7 @@
     </row>
     <row r="110" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A110" s="66" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B110" s="32"/>
       <c r="C110" s="31"/>
@@ -20643,7 +20640,7 @@
     </row>
     <row r="111" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B111" s="32"/>
       <c r="C111" s="31"/>
@@ -20718,7 +20715,7 @@
     </row>
     <row r="112" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A112" s="66" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B112" s="32"/>
       <c r="C112" s="31"/>
@@ -20866,7 +20863,7 @@
     </row>
     <row r="114" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A114" s="65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B114" s="32"/>
       <c r="C114" s="31"/>
@@ -21452,7 +21449,7 @@
     </row>
     <row r="122" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B122" s="176">
         <v>22</v>
@@ -21597,7 +21594,7 @@
     </row>
     <row r="123" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B123" s="153"/>
       <c r="C123" s="154"/>
@@ -21673,7 +21670,7 @@
     <row r="124" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="177"/>
       <c r="B124" s="191" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C124" s="163"/>
       <c r="D124" s="163"/>
@@ -21689,7 +21686,7 @@
       <c r="N124" s="163"/>
       <c r="O124" s="164"/>
       <c r="P124" s="191" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q124" s="163"/>
       <c r="R124" s="163"/>
@@ -21719,7 +21716,7 @@
       <c r="AP124" s="163"/>
       <c r="AQ124" s="164"/>
       <c r="AR124" s="191" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AS124" s="163"/>
       <c r="AT124" s="163"/>
@@ -21735,7 +21732,7 @@
       <c r="BD124" s="163"/>
       <c r="BE124" s="164"/>
       <c r="BF124" s="191" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BG124" s="163"/>
       <c r="BH124" s="163"/>
@@ -22441,7 +22438,7 @@
         <v>3</v>
       </c>
       <c r="P2" s="188" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q2" s="174"/>
       <c r="R2" s="174"/>
@@ -22768,357 +22765,357 @@
     <row r="5" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A5" s="75"/>
       <c r="B5" s="181" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="157"/>
       <c r="D5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="157"/>
       <c r="F5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="157"/>
       <c r="H5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" s="157"/>
       <c r="J5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" s="157"/>
       <c r="L5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M5" s="157"/>
       <c r="N5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O5" s="157"/>
       <c r="P5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="157"/>
       <c r="R5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S5" s="157"/>
       <c r="T5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5" s="157"/>
       <c r="V5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W5" s="157"/>
       <c r="X5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="157"/>
       <c r="Z5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA5" s="157"/>
       <c r="AB5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC5" s="157"/>
       <c r="AD5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE5" s="157"/>
       <c r="AF5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG5" s="157"/>
       <c r="AH5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI5" s="157"/>
       <c r="AJ5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK5" s="157"/>
       <c r="AL5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM5" s="157"/>
       <c r="AN5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO5" s="157"/>
       <c r="AP5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" s="157"/>
       <c r="AR5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS5" s="157"/>
       <c r="AT5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU5" s="157"/>
       <c r="AV5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW5" s="157"/>
       <c r="AX5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY5" s="157"/>
       <c r="AZ5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA5" s="157"/>
       <c r="BB5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC5" s="157"/>
       <c r="BD5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BE5" s="157"/>
       <c r="BF5" s="182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BG5" s="157"/>
       <c r="BH5" s="156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI5" s="157"/>
       <c r="BJ5" s="156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BK5" s="157"/>
       <c r="BL5" s="156" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BM5" s="157"/>
       <c r="BN5" s="156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BO5" s="157"/>
       <c r="BP5" s="156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BQ5" s="157"/>
       <c r="BR5" s="156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BS5" s="157"/>
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
       <c r="B6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="H6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="L6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="N6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="P6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="R6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="T6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="U6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="V6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="X6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Y6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="Z6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AA6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AB6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="AD6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AE6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AF6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AG6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AH6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AL6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AM6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AN6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AO6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AP6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AQ6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="AR6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AS6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AT6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AU6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AV6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AW6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AX6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AY6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="AZ6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BA6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BA6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BB6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BC6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BD6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="BE6" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="BF6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BG6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BH6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BI6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BJ6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BK6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BL6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BM6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BM6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BN6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BO6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BO6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BP6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="BQ6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="BR6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS6" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="BS6" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23926,7 +23923,7 @@
     </row>
     <row r="18" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="31"/>
@@ -24001,7 +23998,7 @@
     </row>
     <row r="19" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A19" s="82" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B19" s="79"/>
       <c r="C19" s="80"/>
@@ -24076,7 +24073,7 @@
     </row>
     <row r="20" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A20" s="82" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="31"/>
@@ -24151,7 +24148,7 @@
     </row>
     <row r="21" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A21" s="82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="31"/>
@@ -24901,7 +24898,7 @@
     </row>
     <row r="31" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A31" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="31"/>
@@ -25049,7 +25046,7 @@
     </row>
     <row r="33" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A33" s="53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B33" s="32"/>
       <c r="C33" s="31"/>
@@ -26584,7 +26581,7 @@
     </row>
     <row r="54" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A54" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B54" s="32"/>
       <c r="C54" s="31"/>
@@ -26659,7 +26656,7 @@
     </row>
     <row r="55" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A55" s="65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B55" s="32"/>
       <c r="C55" s="31"/>
@@ -26734,7 +26731,7 @@
     </row>
     <row r="56" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A56" s="67" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B56" s="32"/>
       <c r="C56" s="31"/>
@@ -26745,7 +26742,7 @@
       <c r="H56" s="9"/>
       <c r="I56" s="10"/>
       <c r="J56" s="54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K56" s="10"/>
       <c r="L56" s="33"/>
@@ -26811,7 +26808,7 @@
     </row>
     <row r="57" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A57" s="67" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B57" s="32"/>
       <c r="C57" s="31"/>
@@ -26842,7 +26839,7 @@
       <c r="AB57" s="33"/>
       <c r="AC57" s="35"/>
       <c r="AD57" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE57" s="31"/>
       <c r="AF57" s="9"/>
@@ -26888,7 +26885,7 @@
     </row>
     <row r="58" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A58" s="67" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B58" s="32"/>
       <c r="C58" s="31"/>
@@ -26937,7 +26934,7 @@
       <c r="AT58" s="9"/>
       <c r="AU58" s="10"/>
       <c r="AV58" s="54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AW58" s="10"/>
       <c r="AX58" s="9"/>
@@ -26965,7 +26962,7 @@
     </row>
     <row r="59" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A59" s="67" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B59" s="32"/>
       <c r="C59" s="31"/>
@@ -27332,7 +27329,7 @@
     </row>
     <row r="64" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A64" s="65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B64" s="32"/>
       <c r="C64" s="31"/>
@@ -27407,7 +27404,7 @@
     </row>
     <row r="65" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A65" s="65" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B65" s="32"/>
       <c r="C65" s="31"/>
@@ -27482,10 +27479,10 @@
     </row>
     <row r="66" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A66" s="66" t="s">
+        <v>203</v>
+      </c>
+      <c r="B66" s="197" t="s">
         <v>204</v>
-      </c>
-      <c r="B66" s="197" t="s">
-        <v>205</v>
       </c>
       <c r="C66" s="198"/>
       <c r="D66" s="198"/>
@@ -27559,7 +27556,7 @@
     </row>
     <row r="67" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A67" s="66" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B67" s="165"/>
       <c r="C67" s="166"/>
@@ -27634,7 +27631,7 @@
     </row>
     <row r="68" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A68" s="66" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B68" s="165"/>
       <c r="C68" s="166"/>
@@ -27709,7 +27706,7 @@
     </row>
     <row r="69" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A69" s="66" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B69" s="201"/>
       <c r="C69" s="202"/>
@@ -27784,7 +27781,7 @@
     </row>
     <row r="70" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A70" s="66" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B70" s="32"/>
       <c r="C70" s="31"/>
@@ -27859,7 +27856,7 @@
     </row>
     <row r="71" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A71" s="66" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B71" s="32"/>
       <c r="C71" s="31"/>
@@ -27934,7 +27931,7 @@
     </row>
     <row r="72" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A72" s="66" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B72" s="32"/>
       <c r="C72" s="31"/>
@@ -28009,7 +28006,7 @@
     </row>
     <row r="73" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A73" s="66" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B73" s="32"/>
       <c r="C73" s="31"/>
@@ -28032,7 +28029,7 @@
       <c r="T73" s="9"/>
       <c r="U73" s="10"/>
       <c r="V73" s="196" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W73" s="194"/>
       <c r="X73" s="194"/>
@@ -28042,7 +28039,7 @@
       <c r="AB73" s="33"/>
       <c r="AC73" s="35"/>
       <c r="AD73" s="193" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AE73" s="194"/>
       <c r="AF73" s="194"/>
@@ -28058,7 +28055,7 @@
       <c r="AP73" s="33"/>
       <c r="AQ73" s="35"/>
       <c r="AR73" s="79" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AS73" s="80"/>
       <c r="AT73" s="81"/>
@@ -28090,7 +28087,7 @@
     </row>
     <row r="74" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A74" s="66" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B74" s="32"/>
       <c r="C74" s="31"/>
@@ -28165,7 +28162,7 @@
     </row>
     <row r="75" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A75" s="66" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B75" s="32"/>
       <c r="C75" s="31"/>
@@ -28897,7 +28894,7 @@
     </row>
     <row r="85" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A85" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B85" s="32"/>
       <c r="C85" s="31"/>
@@ -28972,7 +28969,7 @@
     </row>
     <row r="86" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A86" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B86" s="86"/>
       <c r="C86" s="87"/>
@@ -29047,7 +29044,7 @@
     </row>
     <row r="87" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A87" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B87" s="32"/>
       <c r="C87" s="31"/>
@@ -29122,7 +29119,7 @@
     </row>
     <row r="88" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A88" s="45" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B88" s="32"/>
       <c r="C88" s="31"/>
@@ -29197,7 +29194,7 @@
     </row>
     <row r="89" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A89" s="45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B89" s="32"/>
       <c r="C89" s="31"/>
@@ -31024,7 +31021,7 @@
     </row>
     <row r="114" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B114" s="176">
         <v>22</v>
@@ -31169,7 +31166,7 @@
     </row>
     <row r="115" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B115" s="153"/>
       <c r="C115" s="154"/>
@@ -31245,7 +31242,7 @@
     <row r="116" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="177"/>
       <c r="B116" s="191" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C116" s="163"/>
       <c r="D116" s="163"/>
@@ -31261,7 +31258,7 @@
       <c r="N116" s="163"/>
       <c r="O116" s="164"/>
       <c r="P116" s="191" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q116" s="163"/>
       <c r="R116" s="163"/>
@@ -31277,7 +31274,7 @@
       <c r="AB116" s="163"/>
       <c r="AC116" s="164"/>
       <c r="AD116" s="191" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AE116" s="163"/>
       <c r="AF116" s="163"/>

--- a/5W-Programm/Fuenfwochenprogramm_KW30-34.xlsx
+++ b/5W-Programm/Fuenfwochenprogramm_KW30-34.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stracloud-my.sharepoint.com/personal/maltvic_sbsit_com/Documents/Claude_Projects/Nalps_Ultra_KI/5W_Programm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_6D56B15D33FE195CB279E5AAC077F50B4A723547" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{472EF669-16B3-46EC-A79B-FCDDF7EE42F0}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="6_{01B88D63-E41A-4B61-8F1F-738B97B74AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13F9B8BD-C7C8-4E38-B46F-10FA1D20B713}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -270,22 +270,22 @@
     <t xml:space="preserve">    PZ2025 PRIO 3  (1623, ...)                           -&gt; CKW</t>
   </si>
   <si>
-    <t xml:space="preserve">    26_2.1 + 26_2.2  -&gt;  Start Do 23.07. (Stapel 45 frueh runter)</t>
+    <t xml:space="preserve">  26_2.1 + 26_2.2  (49 Tische | Ziel 25 Tische/Woche = 5/Tag)  ab Di 28.07.</t>
   </si>
   <si>
-    <t xml:space="preserve">    STAMMTEAM FREI</t>
+    <t xml:space="preserve">     STAMMTEAM FREI (Ersatzteam uebernimmt, 5 Tische/Tag halten)</t>
   </si>
   <si>
-    <t xml:space="preserve">    ERSATZTEAM: 26_2.1 / 2.2 durchziehen - ohne Unterbruch</t>
+    <t xml:space="preserve">     ERSATZTEAM: 26_2.1 / 2.2 durchziehen - 5 Tische/Tag</t>
   </si>
   <si>
-    <t xml:space="preserve">    26_2.1 + 26_2.2 FERTIG  -&gt;  bis Mi 05.08. (KW32)</t>
+    <t xml:space="preserve">  26_2.1 + 26_2.2 fertigstellen (49 T. total)  -&gt;  ~Mo 10.08.</t>
   </si>
   <si>
-    <t xml:space="preserve">    8 Tische geaenderte Hoehen  26_1.1 / 1.2 / 1.3  - ab Do 06.08.</t>
+    <t xml:space="preserve">  danach: 8 Tische falsche Hoehen  26_1.1 / 1.2 / 1.3</t>
   </si>
   <si>
-    <t xml:space="preserve">    Baupiste B2 / Etappe 2 (9 T.) - Passstuecke muessen da sein!</t>
+    <t xml:space="preserve">  danach: Baupiste B2 (9 T.) - ACHTUNG Passstuecke Batch 12 erst 17.08.!</t>
   </si>
   <si>
     <t xml:space="preserve">    26_4.1 - Reserve KW34, nur wenn Batch 9 rechtzeitig da</t>
@@ -475,8 +475,9 @@
 es bleibt bei 2 Bohrgruppen
 01.08.: Schrauben-Bestellbatch 3 raus
 Alexander Ferien 03.-14.08. | Luka Ferien
-Stahlbau: 2.1 + 2.2 fertig bis Mi 05.08.,
-danach falsche Hoehen 1.1/1.2/1.3</t>
+Stahlbau 2.1+2.2 (49 T.) fertig ~Mo 10.08.
+(Ziel 25 Tische/Woche = 5/Tag),
+danach falsche Hoehen, dann Baupiste B2</t>
   </si>
   <si>
     <t>Alexander + Luka Ferien
@@ -952,7 +953,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1187,6 +1188,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1908,7 +1914,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2432,6 +2438,24 @@
     <xf numFmtId="0" fontId="0" fillId="44" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="44" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="44" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2615,10 +2639,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Grafik 3">
+        <xdr:cNvPr id="3" name="Grafik 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD320DAE-6730-6EE0-1A96-DF9180989516}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F8922E7-A18D-204D-B8EA-586B20C90C88}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2961,15 +2985,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="231" t="s">
+      <c r="A1" s="237" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="221">
+      <c r="B1" s="227">
         <v>46223</v>
       </c>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -2982,71 +3006,71 @@
       <c r="O1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200" t="s">
+      <c r="P1" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="201"/>
-      <c r="Y1" s="201"/>
-      <c r="Z1" s="201"/>
-      <c r="AA1" s="201"/>
-      <c r="AB1" s="201"/>
-      <c r="AC1" s="201"/>
-      <c r="AD1" s="223"/>
-      <c r="AE1" s="201"/>
-      <c r="AF1" s="201"/>
-      <c r="AG1" s="201"/>
-      <c r="AH1" s="201"/>
-      <c r="AI1" s="201"/>
-      <c r="AJ1" s="201"/>
-      <c r="AK1" s="201"/>
-      <c r="AL1" s="201"/>
-      <c r="AM1" s="201"/>
-      <c r="AN1" s="201"/>
-      <c r="AO1" s="201"/>
-      <c r="AP1" s="201"/>
-      <c r="AQ1" s="201"/>
-      <c r="AR1" s="223"/>
-      <c r="AS1" s="201"/>
-      <c r="AT1" s="201"/>
-      <c r="AU1" s="201"/>
-      <c r="AV1" s="201"/>
-      <c r="AW1" s="201"/>
-      <c r="AX1" s="201"/>
-      <c r="AY1" s="201"/>
-      <c r="AZ1" s="201"/>
-      <c r="BA1" s="201"/>
-      <c r="BB1" s="201"/>
-      <c r="BC1" s="201"/>
-      <c r="BD1" s="201"/>
-      <c r="BE1" s="201"/>
-      <c r="BF1" s="224"/>
-      <c r="BG1" s="201"/>
-      <c r="BH1" s="201"/>
-      <c r="BI1" s="201"/>
-      <c r="BJ1" s="201"/>
-      <c r="BK1" s="201"/>
-      <c r="BL1" s="201"/>
-      <c r="BM1" s="201"/>
-      <c r="BN1" s="201"/>
-      <c r="BO1" s="201"/>
-      <c r="BP1" s="201"/>
-      <c r="BQ1" s="201"/>
-      <c r="BR1" s="201"/>
-      <c r="BS1" s="225"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
+      <c r="Y1" s="207"/>
+      <c r="Z1" s="207"/>
+      <c r="AA1" s="207"/>
+      <c r="AB1" s="207"/>
+      <c r="AC1" s="207"/>
+      <c r="AD1" s="229"/>
+      <c r="AE1" s="207"/>
+      <c r="AF1" s="207"/>
+      <c r="AG1" s="207"/>
+      <c r="AH1" s="207"/>
+      <c r="AI1" s="207"/>
+      <c r="AJ1" s="207"/>
+      <c r="AK1" s="207"/>
+      <c r="AL1" s="207"/>
+      <c r="AM1" s="207"/>
+      <c r="AN1" s="207"/>
+      <c r="AO1" s="207"/>
+      <c r="AP1" s="207"/>
+      <c r="AQ1" s="207"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="207"/>
+      <c r="AT1" s="207"/>
+      <c r="AU1" s="207"/>
+      <c r="AV1" s="207"/>
+      <c r="AW1" s="207"/>
+      <c r="AX1" s="207"/>
+      <c r="AY1" s="207"/>
+      <c r="AZ1" s="207"/>
+      <c r="BA1" s="207"/>
+      <c r="BB1" s="207"/>
+      <c r="BC1" s="207"/>
+      <c r="BD1" s="207"/>
+      <c r="BE1" s="207"/>
+      <c r="BF1" s="230"/>
+      <c r="BG1" s="207"/>
+      <c r="BH1" s="207"/>
+      <c r="BI1" s="207"/>
+      <c r="BJ1" s="207"/>
+      <c r="BK1" s="207"/>
+      <c r="BL1" s="207"/>
+      <c r="BM1" s="207"/>
+      <c r="BN1" s="207"/>
+      <c r="BO1" s="207"/>
+      <c r="BP1" s="207"/>
+      <c r="BQ1" s="207"/>
+      <c r="BR1" s="207"/>
+      <c r="BS1" s="231"/>
     </row>
     <row r="2" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="232"/>
-      <c r="B2" s="217"/>
-      <c r="C2" s="217"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="217"/>
+      <c r="A2" s="238"/>
+      <c r="B2" s="223"/>
+      <c r="C2" s="223"/>
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
@@ -3059,479 +3083,479 @@
       <c r="O2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="204" t="s">
+      <c r="P2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="205"/>
-      <c r="R2" s="205"/>
-      <c r="S2" s="205"/>
-      <c r="T2" s="205"/>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
-      <c r="W2" s="205"/>
-      <c r="X2" s="205"/>
-      <c r="Y2" s="205"/>
-      <c r="Z2" s="205"/>
-      <c r="AA2" s="205"/>
-      <c r="AB2" s="205"/>
-      <c r="AC2" s="205"/>
-      <c r="AD2" s="205"/>
-      <c r="AE2" s="205"/>
-      <c r="AF2" s="205"/>
-      <c r="AG2" s="205"/>
-      <c r="AH2" s="205"/>
-      <c r="AI2" s="205"/>
-      <c r="AJ2" s="205"/>
-      <c r="AK2" s="205"/>
-      <c r="AL2" s="205"/>
-      <c r="AM2" s="205"/>
-      <c r="AN2" s="205"/>
-      <c r="AO2" s="205"/>
-      <c r="AP2" s="205"/>
-      <c r="AQ2" s="205"/>
-      <c r="AR2" s="205"/>
-      <c r="AS2" s="205"/>
-      <c r="AT2" s="205"/>
-      <c r="AU2" s="205"/>
-      <c r="AV2" s="205"/>
-      <c r="AW2" s="205"/>
-      <c r="AX2" s="205"/>
-      <c r="AY2" s="205"/>
-      <c r="AZ2" s="205"/>
-      <c r="BA2" s="205"/>
-      <c r="BB2" s="205"/>
-      <c r="BC2" s="205"/>
-      <c r="BD2" s="205"/>
-      <c r="BE2" s="205"/>
-      <c r="BF2" s="205"/>
-      <c r="BG2" s="205"/>
-      <c r="BH2" s="205"/>
-      <c r="BI2" s="205"/>
-      <c r="BJ2" s="205"/>
-      <c r="BK2" s="205"/>
-      <c r="BL2" s="205"/>
-      <c r="BM2" s="205"/>
-      <c r="BN2" s="205"/>
-      <c r="BO2" s="205"/>
-      <c r="BP2" s="205"/>
-      <c r="BQ2" s="205"/>
-      <c r="BR2" s="205"/>
-      <c r="BS2" s="226"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
+      <c r="AA2" s="211"/>
+      <c r="AB2" s="211"/>
+      <c r="AC2" s="211"/>
+      <c r="AD2" s="211"/>
+      <c r="AE2" s="211"/>
+      <c r="AF2" s="211"/>
+      <c r="AG2" s="211"/>
+      <c r="AH2" s="211"/>
+      <c r="AI2" s="211"/>
+      <c r="AJ2" s="211"/>
+      <c r="AK2" s="211"/>
+      <c r="AL2" s="211"/>
+      <c r="AM2" s="211"/>
+      <c r="AN2" s="211"/>
+      <c r="AO2" s="211"/>
+      <c r="AP2" s="211"/>
+      <c r="AQ2" s="211"/>
+      <c r="AR2" s="211"/>
+      <c r="AS2" s="211"/>
+      <c r="AT2" s="211"/>
+      <c r="AU2" s="211"/>
+      <c r="AV2" s="211"/>
+      <c r="AW2" s="211"/>
+      <c r="AX2" s="211"/>
+      <c r="AY2" s="211"/>
+      <c r="AZ2" s="211"/>
+      <c r="BA2" s="211"/>
+      <c r="BB2" s="211"/>
+      <c r="BC2" s="211"/>
+      <c r="BD2" s="211"/>
+      <c r="BE2" s="211"/>
+      <c r="BF2" s="211"/>
+      <c r="BG2" s="211"/>
+      <c r="BH2" s="211"/>
+      <c r="BI2" s="211"/>
+      <c r="BJ2" s="211"/>
+      <c r="BK2" s="211"/>
+      <c r="BL2" s="211"/>
+      <c r="BM2" s="211"/>
+      <c r="BN2" s="211"/>
+      <c r="BO2" s="211"/>
+      <c r="BP2" s="211"/>
+      <c r="BQ2" s="211"/>
+      <c r="BR2" s="211"/>
+      <c r="BS2" s="232"/>
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="197" t="str">
+      <c r="B3" s="203" t="str">
         <f>"Woche " &amp; WEEKNUM(B4)</f>
         <v>Woche 30</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="198"/>
-      <c r="O3" s="199"/>
-      <c r="P3" s="219" t="str">
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="204"/>
+      <c r="J3" s="204"/>
+      <c r="K3" s="204"/>
+      <c r="L3" s="204"/>
+      <c r="M3" s="204"/>
+      <c r="N3" s="204"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(P4)</f>
         <v>Woche 31</v>
       </c>
-      <c r="Q3" s="198"/>
-      <c r="R3" s="198"/>
-      <c r="S3" s="198"/>
-      <c r="T3" s="198"/>
-      <c r="U3" s="198"/>
-      <c r="V3" s="198"/>
-      <c r="W3" s="198"/>
-      <c r="X3" s="198"/>
-      <c r="Y3" s="198"/>
-      <c r="Z3" s="198"/>
-      <c r="AA3" s="198"/>
-      <c r="AB3" s="198"/>
-      <c r="AC3" s="199"/>
-      <c r="AD3" s="219" t="str">
+      <c r="Q3" s="204"/>
+      <c r="R3" s="204"/>
+      <c r="S3" s="204"/>
+      <c r="T3" s="204"/>
+      <c r="U3" s="204"/>
+      <c r="V3" s="204"/>
+      <c r="W3" s="204"/>
+      <c r="X3" s="204"/>
+      <c r="Y3" s="204"/>
+      <c r="Z3" s="204"/>
+      <c r="AA3" s="204"/>
+      <c r="AB3" s="204"/>
+      <c r="AC3" s="205"/>
+      <c r="AD3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(AD4)</f>
         <v>Woche 32</v>
       </c>
-      <c r="AE3" s="198"/>
-      <c r="AF3" s="198"/>
-      <c r="AG3" s="198"/>
-      <c r="AH3" s="198"/>
-      <c r="AI3" s="198"/>
-      <c r="AJ3" s="198"/>
-      <c r="AK3" s="198"/>
-      <c r="AL3" s="198"/>
-      <c r="AM3" s="198"/>
-      <c r="AN3" s="198"/>
-      <c r="AO3" s="198"/>
-      <c r="AP3" s="198"/>
-      <c r="AQ3" s="199"/>
-      <c r="AR3" s="219" t="str">
+      <c r="AE3" s="204"/>
+      <c r="AF3" s="204"/>
+      <c r="AG3" s="204"/>
+      <c r="AH3" s="204"/>
+      <c r="AI3" s="204"/>
+      <c r="AJ3" s="204"/>
+      <c r="AK3" s="204"/>
+      <c r="AL3" s="204"/>
+      <c r="AM3" s="204"/>
+      <c r="AN3" s="204"/>
+      <c r="AO3" s="204"/>
+      <c r="AP3" s="204"/>
+      <c r="AQ3" s="205"/>
+      <c r="AR3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(AR4)</f>
         <v>Woche 33</v>
       </c>
-      <c r="AS3" s="198"/>
-      <c r="AT3" s="198"/>
-      <c r="AU3" s="198"/>
-      <c r="AV3" s="198"/>
-      <c r="AW3" s="198"/>
-      <c r="AX3" s="198"/>
-      <c r="AY3" s="198"/>
-      <c r="AZ3" s="198"/>
-      <c r="BA3" s="198"/>
-      <c r="BB3" s="198"/>
-      <c r="BC3" s="198"/>
-      <c r="BD3" s="198"/>
-      <c r="BE3" s="199"/>
-      <c r="BF3" s="219" t="str">
+      <c r="AS3" s="204"/>
+      <c r="AT3" s="204"/>
+      <c r="AU3" s="204"/>
+      <c r="AV3" s="204"/>
+      <c r="AW3" s="204"/>
+      <c r="AX3" s="204"/>
+      <c r="AY3" s="204"/>
+      <c r="AZ3" s="204"/>
+      <c r="BA3" s="204"/>
+      <c r="BB3" s="204"/>
+      <c r="BC3" s="204"/>
+      <c r="BD3" s="204"/>
+      <c r="BE3" s="205"/>
+      <c r="BF3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(BF4)</f>
         <v>Woche 34</v>
       </c>
-      <c r="BG3" s="198"/>
-      <c r="BH3" s="198"/>
-      <c r="BI3" s="198"/>
-      <c r="BJ3" s="198"/>
-      <c r="BK3" s="198"/>
-      <c r="BL3" s="198"/>
-      <c r="BM3" s="198"/>
-      <c r="BN3" s="198"/>
-      <c r="BO3" s="198"/>
-      <c r="BP3" s="198"/>
-      <c r="BQ3" s="198"/>
-      <c r="BR3" s="198"/>
-      <c r="BS3" s="199"/>
+      <c r="BG3" s="204"/>
+      <c r="BH3" s="204"/>
+      <c r="BI3" s="204"/>
+      <c r="BJ3" s="204"/>
+      <c r="BK3" s="204"/>
+      <c r="BL3" s="204"/>
+      <c r="BM3" s="204"/>
+      <c r="BN3" s="204"/>
+      <c r="BO3" s="204"/>
+      <c r="BP3" s="204"/>
+      <c r="BQ3" s="204"/>
+      <c r="BR3" s="204"/>
+      <c r="BS3" s="205"/>
     </row>
     <row r="4" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="206">
+      <c r="B4" s="212">
         <f>B1</f>
         <v>46223</v>
       </c>
-      <c r="C4" s="207"/>
-      <c r="D4" s="206">
+      <c r="C4" s="213"/>
+      <c r="D4" s="212">
         <f>B4+1</f>
         <v>46224</v>
       </c>
-      <c r="E4" s="207"/>
-      <c r="F4" s="206">
+      <c r="E4" s="213"/>
+      <c r="F4" s="212">
         <f>D4+1</f>
         <v>46225</v>
       </c>
-      <c r="G4" s="207"/>
-      <c r="H4" s="206">
+      <c r="G4" s="213"/>
+      <c r="H4" s="212">
         <f>F4+1</f>
         <v>46226</v>
       </c>
-      <c r="I4" s="207"/>
-      <c r="J4" s="206">
+      <c r="I4" s="213"/>
+      <c r="J4" s="212">
         <f>H4+1</f>
         <v>46227</v>
       </c>
-      <c r="K4" s="207"/>
-      <c r="L4" s="206">
+      <c r="K4" s="213"/>
+      <c r="L4" s="212">
         <f>J4+1</f>
         <v>46228</v>
       </c>
-      <c r="M4" s="207"/>
-      <c r="N4" s="206">
+      <c r="M4" s="213"/>
+      <c r="N4" s="212">
         <f>L4+1</f>
         <v>46229</v>
       </c>
-      <c r="O4" s="207"/>
-      <c r="P4" s="206">
+      <c r="O4" s="213"/>
+      <c r="P4" s="212">
         <f>N4+1</f>
         <v>46230</v>
       </c>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="206">
+      <c r="Q4" s="213"/>
+      <c r="R4" s="212">
         <f>P4+1</f>
         <v>46231</v>
       </c>
-      <c r="S4" s="207"/>
-      <c r="T4" s="206">
+      <c r="S4" s="213"/>
+      <c r="T4" s="212">
         <f>R4+1</f>
         <v>46232</v>
       </c>
-      <c r="U4" s="207"/>
-      <c r="V4" s="206">
+      <c r="U4" s="213"/>
+      <c r="V4" s="212">
         <f>T4+1</f>
         <v>46233</v>
       </c>
-      <c r="W4" s="207"/>
-      <c r="X4" s="206">
+      <c r="W4" s="213"/>
+      <c r="X4" s="212">
         <f>V4+1</f>
         <v>46234</v>
       </c>
-      <c r="Y4" s="207"/>
-      <c r="Z4" s="206">
+      <c r="Y4" s="213"/>
+      <c r="Z4" s="212">
         <f>X4+1</f>
         <v>46235</v>
       </c>
-      <c r="AA4" s="207"/>
-      <c r="AB4" s="220">
+      <c r="AA4" s="213"/>
+      <c r="AB4" s="226">
         <f>Z4+1</f>
         <v>46236</v>
       </c>
-      <c r="AC4" s="207"/>
-      <c r="AD4" s="220">
+      <c r="AC4" s="213"/>
+      <c r="AD4" s="226">
         <f>AB4+1</f>
         <v>46237</v>
       </c>
-      <c r="AE4" s="207"/>
-      <c r="AF4" s="206">
+      <c r="AE4" s="213"/>
+      <c r="AF4" s="212">
         <f>AD4+1</f>
         <v>46238</v>
       </c>
-      <c r="AG4" s="207"/>
-      <c r="AH4" s="206">
+      <c r="AG4" s="213"/>
+      <c r="AH4" s="212">
         <f>AF4+1</f>
         <v>46239</v>
       </c>
-      <c r="AI4" s="207"/>
-      <c r="AJ4" s="206">
+      <c r="AI4" s="213"/>
+      <c r="AJ4" s="212">
         <f>AH4+1</f>
         <v>46240</v>
       </c>
-      <c r="AK4" s="207"/>
-      <c r="AL4" s="206">
+      <c r="AK4" s="213"/>
+      <c r="AL4" s="212">
         <f>AJ4+1</f>
         <v>46241</v>
       </c>
-      <c r="AM4" s="207"/>
-      <c r="AN4" s="206">
+      <c r="AM4" s="213"/>
+      <c r="AN4" s="212">
         <f>AL4+1</f>
         <v>46242</v>
       </c>
-      <c r="AO4" s="207"/>
-      <c r="AP4" s="206">
+      <c r="AO4" s="213"/>
+      <c r="AP4" s="212">
         <f>AN4+1</f>
         <v>46243</v>
       </c>
-      <c r="AQ4" s="207"/>
-      <c r="AR4" s="206">
+      <c r="AQ4" s="213"/>
+      <c r="AR4" s="212">
         <f>AP4+1</f>
         <v>46244</v>
       </c>
-      <c r="AS4" s="207"/>
-      <c r="AT4" s="206">
+      <c r="AS4" s="213"/>
+      <c r="AT4" s="212">
         <f>AR4+1</f>
         <v>46245</v>
       </c>
-      <c r="AU4" s="207"/>
-      <c r="AV4" s="206">
+      <c r="AU4" s="213"/>
+      <c r="AV4" s="212">
         <f>AT4+1</f>
         <v>46246</v>
       </c>
-      <c r="AW4" s="207"/>
-      <c r="AX4" s="206">
+      <c r="AW4" s="213"/>
+      <c r="AX4" s="212">
         <f>AV4+1</f>
         <v>46247</v>
       </c>
-      <c r="AY4" s="207"/>
-      <c r="AZ4" s="206">
+      <c r="AY4" s="213"/>
+      <c r="AZ4" s="212">
         <f>AX4+1</f>
         <v>46248</v>
       </c>
-      <c r="BA4" s="207"/>
-      <c r="BB4" s="206">
+      <c r="BA4" s="213"/>
+      <c r="BB4" s="212">
         <f>AZ4+1</f>
         <v>46249</v>
       </c>
-      <c r="BC4" s="207"/>
-      <c r="BD4" s="206">
+      <c r="BC4" s="213"/>
+      <c r="BD4" s="212">
         <f>BB4+1</f>
         <v>46250</v>
       </c>
-      <c r="BE4" s="207"/>
-      <c r="BF4" s="206">
+      <c r="BE4" s="213"/>
+      <c r="BF4" s="212">
         <f>BD4+1</f>
         <v>46251</v>
       </c>
-      <c r="BG4" s="207"/>
-      <c r="BH4" s="206">
+      <c r="BG4" s="213"/>
+      <c r="BH4" s="212">
         <f>BF4+1</f>
         <v>46252</v>
       </c>
-      <c r="BI4" s="207"/>
-      <c r="BJ4" s="206">
+      <c r="BI4" s="213"/>
+      <c r="BJ4" s="212">
         <f>BH4+1</f>
         <v>46253</v>
       </c>
-      <c r="BK4" s="207"/>
-      <c r="BL4" s="206">
+      <c r="BK4" s="213"/>
+      <c r="BL4" s="212">
         <f>BJ4+1</f>
         <v>46254</v>
       </c>
-      <c r="BM4" s="207"/>
-      <c r="BN4" s="206">
+      <c r="BM4" s="213"/>
+      <c r="BN4" s="212">
         <f>BL4+1</f>
         <v>46255</v>
       </c>
-      <c r="BO4" s="207"/>
-      <c r="BP4" s="206">
+      <c r="BO4" s="213"/>
+      <c r="BP4" s="212">
         <f>BN4+1</f>
         <v>46256</v>
       </c>
-      <c r="BQ4" s="207"/>
-      <c r="BR4" s="206">
+      <c r="BQ4" s="213"/>
+      <c r="BR4" s="212">
         <f>BP4+1</f>
         <v>46257</v>
       </c>
-      <c r="BS4" s="207"/>
+      <c r="BS4" s="213"/>
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A5" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="230" t="s">
+      <c r="B5" s="236" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="196"/>
-      <c r="D5" s="195" t="s">
+      <c r="C5" s="202"/>
+      <c r="D5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="196"/>
-      <c r="F5" s="195" t="s">
+      <c r="E5" s="202"/>
+      <c r="F5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="196"/>
-      <c r="H5" s="195" t="s">
+      <c r="G5" s="202"/>
+      <c r="H5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="196"/>
-      <c r="J5" s="195" t="s">
+      <c r="I5" s="202"/>
+      <c r="J5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="196"/>
-      <c r="L5" s="195" t="s">
+      <c r="K5" s="202"/>
+      <c r="L5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="196"/>
-      <c r="N5" s="195" t="s">
+      <c r="M5" s="202"/>
+      <c r="N5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="196"/>
-      <c r="P5" s="202" t="s">
+      <c r="O5" s="202"/>
+      <c r="P5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="196"/>
-      <c r="R5" s="195" t="s">
+      <c r="Q5" s="202"/>
+      <c r="R5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="S5" s="196"/>
-      <c r="T5" s="195" t="s">
+      <c r="S5" s="202"/>
+      <c r="T5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="U5" s="196"/>
-      <c r="V5" s="195" t="s">
+      <c r="U5" s="202"/>
+      <c r="V5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="196"/>
-      <c r="X5" s="195" t="s">
+      <c r="W5" s="202"/>
+      <c r="X5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="Y5" s="196"/>
-      <c r="Z5" s="195" t="s">
+      <c r="Y5" s="202"/>
+      <c r="Z5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="AA5" s="196"/>
-      <c r="AB5" s="195" t="s">
+      <c r="AA5" s="202"/>
+      <c r="AB5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AC5" s="196"/>
-      <c r="AD5" s="202" t="s">
+      <c r="AC5" s="202"/>
+      <c r="AD5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="AE5" s="196"/>
-      <c r="AF5" s="195" t="s">
+      <c r="AE5" s="202"/>
+      <c r="AF5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="AG5" s="196"/>
-      <c r="AH5" s="195" t="s">
+      <c r="AG5" s="202"/>
+      <c r="AH5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="AI5" s="196"/>
-      <c r="AJ5" s="195" t="s">
+      <c r="AI5" s="202"/>
+      <c r="AJ5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="AK5" s="196"/>
-      <c r="AL5" s="195" t="s">
+      <c r="AK5" s="202"/>
+      <c r="AL5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="AM5" s="196"/>
-      <c r="AN5" s="195" t="s">
+      <c r="AM5" s="202"/>
+      <c r="AN5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="AO5" s="196"/>
-      <c r="AP5" s="195" t="s">
+      <c r="AO5" s="202"/>
+      <c r="AP5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AQ5" s="196"/>
-      <c r="AR5" s="202" t="s">
+      <c r="AQ5" s="202"/>
+      <c r="AR5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="AS5" s="196"/>
-      <c r="AT5" s="195" t="s">
+      <c r="AS5" s="202"/>
+      <c r="AT5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="AU5" s="196"/>
-      <c r="AV5" s="195" t="s">
+      <c r="AU5" s="202"/>
+      <c r="AV5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="AW5" s="196"/>
-      <c r="AX5" s="195" t="s">
+      <c r="AW5" s="202"/>
+      <c r="AX5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="AY5" s="196"/>
-      <c r="AZ5" s="195" t="s">
+      <c r="AY5" s="202"/>
+      <c r="AZ5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="BA5" s="196"/>
-      <c r="BB5" s="195" t="s">
+      <c r="BA5" s="202"/>
+      <c r="BB5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="BC5" s="196"/>
-      <c r="BD5" s="195" t="s">
+      <c r="BC5" s="202"/>
+      <c r="BD5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="BE5" s="196"/>
-      <c r="BF5" s="202" t="s">
+      <c r="BE5" s="202"/>
+      <c r="BF5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="BG5" s="196"/>
-      <c r="BH5" s="195" t="s">
+      <c r="BG5" s="202"/>
+      <c r="BH5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="BI5" s="196"/>
-      <c r="BJ5" s="195" t="s">
+      <c r="BI5" s="202"/>
+      <c r="BJ5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="BK5" s="196"/>
-      <c r="BL5" s="195" t="s">
+      <c r="BK5" s="202"/>
+      <c r="BL5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="BM5" s="196"/>
-      <c r="BN5" s="195" t="s">
+      <c r="BM5" s="202"/>
+      <c r="BN5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="BO5" s="196"/>
-      <c r="BP5" s="195" t="s">
+      <c r="BO5" s="202"/>
+      <c r="BP5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="BQ5" s="196"/>
-      <c r="BR5" s="195" t="s">
+      <c r="BQ5" s="202"/>
+      <c r="BR5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="BS5" s="196"/>
+      <c r="BS5" s="202"/>
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
@@ -6825,20 +6849,20 @@
       <c r="E48" s="10"/>
       <c r="F48" s="9"/>
       <c r="G48" s="10"/>
-      <c r="H48" s="135"/>
-      <c r="I48" s="136"/>
-      <c r="J48" s="135"/>
-      <c r="K48" s="136"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="10"/>
       <c r="L48" s="33"/>
       <c r="M48" s="34"/>
       <c r="N48" s="33"/>
       <c r="O48" s="35"/>
-      <c r="P48" s="137"/>
-      <c r="Q48" s="136"/>
-      <c r="R48" s="135"/>
-      <c r="S48" s="136"/>
-      <c r="T48" s="135"/>
-      <c r="U48" s="136"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="193"/>
+      <c r="S48" s="194"/>
+      <c r="T48" s="193"/>
+      <c r="U48" s="194"/>
       <c r="V48" s="9"/>
       <c r="W48" s="10"/>
       <c r="X48" s="9"/>
@@ -7076,18 +7100,18 @@
       <c r="AE51" s="31"/>
       <c r="AF51" s="9"/>
       <c r="AG51" s="10"/>
-      <c r="AH51" s="135"/>
-      <c r="AI51" s="136"/>
-      <c r="AJ51" s="9"/>
-      <c r="AK51" s="10"/>
-      <c r="AL51" s="9"/>
-      <c r="AM51" s="10"/>
-      <c r="AN51" s="33"/>
-      <c r="AO51" s="34"/>
-      <c r="AP51" s="33"/>
-      <c r="AQ51" s="35"/>
-      <c r="AR51" s="32"/>
-      <c r="AS51" s="31"/>
+      <c r="AH51" s="193"/>
+      <c r="AI51" s="194"/>
+      <c r="AJ51" s="193"/>
+      <c r="AK51" s="194"/>
+      <c r="AL51" s="193"/>
+      <c r="AM51" s="194"/>
+      <c r="AN51" s="195"/>
+      <c r="AO51" s="196"/>
+      <c r="AP51" s="195"/>
+      <c r="AQ51" s="197"/>
+      <c r="AR51" s="198"/>
+      <c r="AS51" s="194"/>
       <c r="AT51" s="9"/>
       <c r="AU51" s="10"/>
       <c r="AV51" s="9"/>
@@ -7153,20 +7177,20 @@
       <c r="AG52" s="10"/>
       <c r="AH52" s="9"/>
       <c r="AI52" s="10"/>
-      <c r="AJ52" s="135"/>
-      <c r="AK52" s="136"/>
-      <c r="AL52" s="135"/>
-      <c r="AM52" s="136"/>
+      <c r="AJ52" s="9"/>
+      <c r="AK52" s="10"/>
+      <c r="AL52" s="9"/>
+      <c r="AM52" s="10"/>
       <c r="AN52" s="33"/>
       <c r="AO52" s="34"/>
       <c r="AP52" s="33"/>
       <c r="AQ52" s="35"/>
-      <c r="AR52" s="137"/>
-      <c r="AS52" s="136"/>
-      <c r="AT52" s="9"/>
-      <c r="AU52" s="10"/>
-      <c r="AV52" s="9"/>
-      <c r="AW52" s="10"/>
+      <c r="AR52" s="32"/>
+      <c r="AS52" s="31"/>
+      <c r="AT52" s="193"/>
+      <c r="AU52" s="194"/>
+      <c r="AV52" s="193"/>
+      <c r="AW52" s="194"/>
       <c r="AX52" s="9"/>
       <c r="AY52" s="10"/>
       <c r="AZ52" s="9"/>
@@ -7238,14 +7262,14 @@
       <c r="AQ53" s="35"/>
       <c r="AR53" s="32"/>
       <c r="AS53" s="31"/>
-      <c r="AT53" s="135"/>
-      <c r="AU53" s="136"/>
-      <c r="AV53" s="135"/>
-      <c r="AW53" s="136"/>
-      <c r="AX53" s="135"/>
-      <c r="AY53" s="136"/>
-      <c r="AZ53" s="135"/>
-      <c r="BA53" s="136"/>
+      <c r="AT53" s="9"/>
+      <c r="AU53" s="10"/>
+      <c r="AV53" s="9"/>
+      <c r="AW53" s="10"/>
+      <c r="AX53" s="193"/>
+      <c r="AY53" s="194"/>
+      <c r="AZ53" s="193"/>
+      <c r="BA53" s="194"/>
       <c r="BB53" s="33"/>
       <c r="BC53" s="34"/>
       <c r="BD53" s="33"/>
@@ -11323,742 +11347,742 @@
       <c r="A108" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B108" s="203">
+      <c r="B108" s="209">
         <v>22</v>
       </c>
-      <c r="C108" s="194"/>
-      <c r="D108" s="193">
+      <c r="C108" s="200"/>
+      <c r="D108" s="199">
         <v>22</v>
       </c>
-      <c r="E108" s="194"/>
-      <c r="F108" s="193">
+      <c r="E108" s="200"/>
+      <c r="F108" s="199">
         <v>22</v>
       </c>
-      <c r="G108" s="194"/>
-      <c r="H108" s="193">
+      <c r="G108" s="200"/>
+      <c r="H108" s="199">
         <v>22</v>
       </c>
-      <c r="I108" s="194"/>
-      <c r="J108" s="193">
+      <c r="I108" s="200"/>
+      <c r="J108" s="199">
         <v>22</v>
       </c>
-      <c r="K108" s="194"/>
-      <c r="L108" s="193">
+      <c r="K108" s="200"/>
+      <c r="L108" s="199">
         <v>0</v>
       </c>
-      <c r="M108" s="194"/>
-      <c r="N108" s="193">
+      <c r="M108" s="200"/>
+      <c r="N108" s="199">
         <v>0</v>
       </c>
-      <c r="O108" s="194"/>
-      <c r="P108" s="203">
+      <c r="O108" s="200"/>
+      <c r="P108" s="209">
         <v>22</v>
       </c>
-      <c r="Q108" s="194"/>
-      <c r="R108" s="193">
+      <c r="Q108" s="200"/>
+      <c r="R108" s="199">
         <v>22</v>
       </c>
-      <c r="S108" s="194"/>
-      <c r="T108" s="193">
+      <c r="S108" s="200"/>
+      <c r="T108" s="199">
         <v>22</v>
       </c>
-      <c r="U108" s="194"/>
-      <c r="V108" s="193">
+      <c r="U108" s="200"/>
+      <c r="V108" s="199">
         <v>22</v>
       </c>
-      <c r="W108" s="194"/>
-      <c r="X108" s="193">
+      <c r="W108" s="200"/>
+      <c r="X108" s="199">
         <v>22</v>
       </c>
-      <c r="Y108" s="194"/>
-      <c r="Z108" s="193">
+      <c r="Y108" s="200"/>
+      <c r="Z108" s="199">
         <v>0</v>
       </c>
-      <c r="AA108" s="194"/>
-      <c r="AB108" s="193">
+      <c r="AA108" s="200"/>
+      <c r="AB108" s="199">
         <v>0</v>
       </c>
-      <c r="AC108" s="194"/>
-      <c r="AD108" s="203">
+      <c r="AC108" s="200"/>
+      <c r="AD108" s="209">
         <v>22</v>
       </c>
-      <c r="AE108" s="194"/>
-      <c r="AF108" s="193">
+      <c r="AE108" s="200"/>
+      <c r="AF108" s="199">
         <v>22</v>
       </c>
-      <c r="AG108" s="194"/>
-      <c r="AH108" s="193">
+      <c r="AG108" s="200"/>
+      <c r="AH108" s="199">
         <v>22</v>
       </c>
-      <c r="AI108" s="194"/>
-      <c r="AJ108" s="193">
+      <c r="AI108" s="200"/>
+      <c r="AJ108" s="199">
         <v>22</v>
       </c>
-      <c r="AK108" s="194"/>
-      <c r="AL108" s="193">
+      <c r="AK108" s="200"/>
+      <c r="AL108" s="199">
         <v>22</v>
       </c>
-      <c r="AM108" s="194"/>
-      <c r="AN108" s="193">
+      <c r="AM108" s="200"/>
+      <c r="AN108" s="199">
         <v>0</v>
       </c>
-      <c r="AO108" s="194"/>
-      <c r="AP108" s="193">
+      <c r="AO108" s="200"/>
+      <c r="AP108" s="199">
         <v>0</v>
       </c>
-      <c r="AQ108" s="194"/>
-      <c r="AR108" s="203">
+      <c r="AQ108" s="200"/>
+      <c r="AR108" s="209">
         <v>22</v>
       </c>
-      <c r="AS108" s="194"/>
-      <c r="AT108" s="193">
+      <c r="AS108" s="200"/>
+      <c r="AT108" s="199">
         <v>22</v>
       </c>
-      <c r="AU108" s="194"/>
-      <c r="AV108" s="193">
+      <c r="AU108" s="200"/>
+      <c r="AV108" s="199">
         <v>22</v>
       </c>
-      <c r="AW108" s="194"/>
-      <c r="AX108" s="193">
+      <c r="AW108" s="200"/>
+      <c r="AX108" s="199">
         <v>22</v>
       </c>
-      <c r="AY108" s="194"/>
-      <c r="AZ108" s="193">
+      <c r="AY108" s="200"/>
+      <c r="AZ108" s="199">
         <v>22</v>
       </c>
-      <c r="BA108" s="194"/>
-      <c r="BB108" s="193">
+      <c r="BA108" s="200"/>
+      <c r="BB108" s="199">
         <v>0</v>
       </c>
-      <c r="BC108" s="194"/>
-      <c r="BD108" s="193">
+      <c r="BC108" s="200"/>
+      <c r="BD108" s="199">
         <v>0</v>
       </c>
-      <c r="BE108" s="194"/>
-      <c r="BF108" s="203">
+      <c r="BE108" s="200"/>
+      <c r="BF108" s="209">
         <v>22</v>
       </c>
-      <c r="BG108" s="194"/>
-      <c r="BH108" s="193">
+      <c r="BG108" s="200"/>
+      <c r="BH108" s="199">
         <v>22</v>
       </c>
-      <c r="BI108" s="194"/>
-      <c r="BJ108" s="193">
+      <c r="BI108" s="200"/>
+      <c r="BJ108" s="199">
         <v>22</v>
       </c>
-      <c r="BK108" s="194"/>
-      <c r="BL108" s="193">
+      <c r="BK108" s="200"/>
+      <c r="BL108" s="199">
         <v>22</v>
       </c>
-      <c r="BM108" s="194"/>
-      <c r="BN108" s="193">
+      <c r="BM108" s="200"/>
+      <c r="BN108" s="199">
         <v>22</v>
       </c>
-      <c r="BO108" s="194"/>
-      <c r="BP108" s="193">
+      <c r="BO108" s="200"/>
+      <c r="BP108" s="199">
         <v>0</v>
       </c>
-      <c r="BQ108" s="194"/>
-      <c r="BR108" s="193">
+      <c r="BQ108" s="200"/>
+      <c r="BR108" s="199">
         <v>0</v>
       </c>
-      <c r="BS108" s="194"/>
+      <c r="BS108" s="200"/>
     </row>
     <row r="109" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B109" s="208"/>
-      <c r="C109" s="198"/>
-      <c r="D109" s="198"/>
-      <c r="E109" s="198"/>
-      <c r="F109" s="198"/>
-      <c r="G109" s="198"/>
-      <c r="H109" s="198"/>
-      <c r="I109" s="198"/>
-      <c r="J109" s="198"/>
-      <c r="K109" s="198"/>
-      <c r="L109" s="198"/>
-      <c r="M109" s="198"/>
-      <c r="N109" s="198"/>
-      <c r="O109" s="209"/>
-      <c r="P109" s="208"/>
-      <c r="Q109" s="198"/>
-      <c r="R109" s="198"/>
-      <c r="S109" s="198"/>
-      <c r="T109" s="198"/>
-      <c r="U109" s="198"/>
-      <c r="V109" s="198"/>
-      <c r="W109" s="198"/>
-      <c r="X109" s="198"/>
-      <c r="Y109" s="198"/>
-      <c r="Z109" s="198"/>
-      <c r="AA109" s="198"/>
-      <c r="AB109" s="198"/>
-      <c r="AC109" s="209"/>
-      <c r="AD109" s="208"/>
-      <c r="AE109" s="198"/>
-      <c r="AF109" s="198"/>
-      <c r="AG109" s="198"/>
-      <c r="AH109" s="198"/>
-      <c r="AI109" s="198"/>
-      <c r="AJ109" s="198"/>
-      <c r="AK109" s="198"/>
-      <c r="AL109" s="198"/>
-      <c r="AM109" s="198"/>
-      <c r="AN109" s="198"/>
-      <c r="AO109" s="198"/>
-      <c r="AP109" s="198"/>
-      <c r="AQ109" s="209"/>
-      <c r="AR109" s="208"/>
-      <c r="AS109" s="198"/>
-      <c r="AT109" s="198"/>
-      <c r="AU109" s="198"/>
-      <c r="AV109" s="198"/>
-      <c r="AW109" s="198"/>
-      <c r="AX109" s="198"/>
-      <c r="AY109" s="198"/>
-      <c r="AZ109" s="198"/>
-      <c r="BA109" s="198"/>
-      <c r="BB109" s="198"/>
-      <c r="BC109" s="198"/>
-      <c r="BD109" s="198"/>
-      <c r="BE109" s="209"/>
-      <c r="BF109" s="208"/>
-      <c r="BG109" s="198"/>
-      <c r="BH109" s="198"/>
-      <c r="BI109" s="198"/>
-      <c r="BJ109" s="198"/>
-      <c r="BK109" s="198"/>
-      <c r="BL109" s="198"/>
-      <c r="BM109" s="198"/>
-      <c r="BN109" s="198"/>
-      <c r="BO109" s="198"/>
-      <c r="BP109" s="198"/>
-      <c r="BQ109" s="198"/>
-      <c r="BR109" s="198"/>
-      <c r="BS109" s="209"/>
+      <c r="B109" s="214"/>
+      <c r="C109" s="204"/>
+      <c r="D109" s="204"/>
+      <c r="E109" s="204"/>
+      <c r="F109" s="204"/>
+      <c r="G109" s="204"/>
+      <c r="H109" s="204"/>
+      <c r="I109" s="204"/>
+      <c r="J109" s="204"/>
+      <c r="K109" s="204"/>
+      <c r="L109" s="204"/>
+      <c r="M109" s="204"/>
+      <c r="N109" s="204"/>
+      <c r="O109" s="215"/>
+      <c r="P109" s="214"/>
+      <c r="Q109" s="204"/>
+      <c r="R109" s="204"/>
+      <c r="S109" s="204"/>
+      <c r="T109" s="204"/>
+      <c r="U109" s="204"/>
+      <c r="V109" s="204"/>
+      <c r="W109" s="204"/>
+      <c r="X109" s="204"/>
+      <c r="Y109" s="204"/>
+      <c r="Z109" s="204"/>
+      <c r="AA109" s="204"/>
+      <c r="AB109" s="204"/>
+      <c r="AC109" s="215"/>
+      <c r="AD109" s="214"/>
+      <c r="AE109" s="204"/>
+      <c r="AF109" s="204"/>
+      <c r="AG109" s="204"/>
+      <c r="AH109" s="204"/>
+      <c r="AI109" s="204"/>
+      <c r="AJ109" s="204"/>
+      <c r="AK109" s="204"/>
+      <c r="AL109" s="204"/>
+      <c r="AM109" s="204"/>
+      <c r="AN109" s="204"/>
+      <c r="AO109" s="204"/>
+      <c r="AP109" s="204"/>
+      <c r="AQ109" s="215"/>
+      <c r="AR109" s="214"/>
+      <c r="AS109" s="204"/>
+      <c r="AT109" s="204"/>
+      <c r="AU109" s="204"/>
+      <c r="AV109" s="204"/>
+      <c r="AW109" s="204"/>
+      <c r="AX109" s="204"/>
+      <c r="AY109" s="204"/>
+      <c r="AZ109" s="204"/>
+      <c r="BA109" s="204"/>
+      <c r="BB109" s="204"/>
+      <c r="BC109" s="204"/>
+      <c r="BD109" s="204"/>
+      <c r="BE109" s="215"/>
+      <c r="BF109" s="214"/>
+      <c r="BG109" s="204"/>
+      <c r="BH109" s="204"/>
+      <c r="BI109" s="204"/>
+      <c r="BJ109" s="204"/>
+      <c r="BK109" s="204"/>
+      <c r="BL109" s="204"/>
+      <c r="BM109" s="204"/>
+      <c r="BN109" s="204"/>
+      <c r="BO109" s="204"/>
+      <c r="BP109" s="204"/>
+      <c r="BQ109" s="204"/>
+      <c r="BR109" s="204"/>
+      <c r="BS109" s="215"/>
     </row>
     <row r="110" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="227"/>
-      <c r="B110" s="210" t="s">
+      <c r="A110" s="233"/>
+      <c r="B110" s="216" t="s">
         <v>111</v>
       </c>
-      <c r="C110" s="211"/>
-      <c r="D110" s="211"/>
-      <c r="E110" s="211"/>
-      <c r="F110" s="211"/>
-      <c r="G110" s="211"/>
-      <c r="H110" s="211"/>
-      <c r="I110" s="211"/>
-      <c r="J110" s="211"/>
-      <c r="K110" s="211"/>
-      <c r="L110" s="211"/>
-      <c r="M110" s="211"/>
-      <c r="N110" s="211"/>
-      <c r="O110" s="212"/>
-      <c r="P110" s="210" t="s">
+      <c r="C110" s="217"/>
+      <c r="D110" s="217"/>
+      <c r="E110" s="217"/>
+      <c r="F110" s="217"/>
+      <c r="G110" s="217"/>
+      <c r="H110" s="217"/>
+      <c r="I110" s="217"/>
+      <c r="J110" s="217"/>
+      <c r="K110" s="217"/>
+      <c r="L110" s="217"/>
+      <c r="M110" s="217"/>
+      <c r="N110" s="217"/>
+      <c r="O110" s="218"/>
+      <c r="P110" s="216" t="s">
         <v>112</v>
       </c>
-      <c r="Q110" s="211"/>
-      <c r="R110" s="211"/>
-      <c r="S110" s="211"/>
-      <c r="T110" s="211"/>
-      <c r="U110" s="211"/>
-      <c r="V110" s="211"/>
-      <c r="W110" s="211"/>
-      <c r="X110" s="211"/>
-      <c r="Y110" s="211"/>
-      <c r="Z110" s="211"/>
-      <c r="AA110" s="211"/>
-      <c r="AB110" s="211"/>
-      <c r="AC110" s="212"/>
-      <c r="AD110" s="210" t="s">
+      <c r="Q110" s="217"/>
+      <c r="R110" s="217"/>
+      <c r="S110" s="217"/>
+      <c r="T110" s="217"/>
+      <c r="U110" s="217"/>
+      <c r="V110" s="217"/>
+      <c r="W110" s="217"/>
+      <c r="X110" s="217"/>
+      <c r="Y110" s="217"/>
+      <c r="Z110" s="217"/>
+      <c r="AA110" s="217"/>
+      <c r="AB110" s="217"/>
+      <c r="AC110" s="218"/>
+      <c r="AD110" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="AE110" s="211"/>
-      <c r="AF110" s="211"/>
-      <c r="AG110" s="211"/>
-      <c r="AH110" s="211"/>
-      <c r="AI110" s="211"/>
-      <c r="AJ110" s="211"/>
-      <c r="AK110" s="211"/>
-      <c r="AL110" s="211"/>
-      <c r="AM110" s="211"/>
-      <c r="AN110" s="211"/>
-      <c r="AO110" s="211"/>
-      <c r="AP110" s="211"/>
-      <c r="AQ110" s="212"/>
-      <c r="AR110" s="210" t="s">
+      <c r="AE110" s="217"/>
+      <c r="AF110" s="217"/>
+      <c r="AG110" s="217"/>
+      <c r="AH110" s="217"/>
+      <c r="AI110" s="217"/>
+      <c r="AJ110" s="217"/>
+      <c r="AK110" s="217"/>
+      <c r="AL110" s="217"/>
+      <c r="AM110" s="217"/>
+      <c r="AN110" s="217"/>
+      <c r="AO110" s="217"/>
+      <c r="AP110" s="217"/>
+      <c r="AQ110" s="218"/>
+      <c r="AR110" s="216" t="s">
         <v>114</v>
       </c>
-      <c r="AS110" s="211"/>
-      <c r="AT110" s="211"/>
-      <c r="AU110" s="211"/>
-      <c r="AV110" s="211"/>
-      <c r="AW110" s="211"/>
-      <c r="AX110" s="211"/>
-      <c r="AY110" s="211"/>
-      <c r="AZ110" s="211"/>
-      <c r="BA110" s="211"/>
-      <c r="BB110" s="211"/>
-      <c r="BC110" s="211"/>
-      <c r="BD110" s="211"/>
-      <c r="BE110" s="212"/>
-      <c r="BF110" s="210" t="s">
+      <c r="AS110" s="217"/>
+      <c r="AT110" s="217"/>
+      <c r="AU110" s="217"/>
+      <c r="AV110" s="217"/>
+      <c r="AW110" s="217"/>
+      <c r="AX110" s="217"/>
+      <c r="AY110" s="217"/>
+      <c r="AZ110" s="217"/>
+      <c r="BA110" s="217"/>
+      <c r="BB110" s="217"/>
+      <c r="BC110" s="217"/>
+      <c r="BD110" s="217"/>
+      <c r="BE110" s="218"/>
+      <c r="BF110" s="216" t="s">
         <v>115</v>
       </c>
-      <c r="BG110" s="211"/>
-      <c r="BH110" s="211"/>
-      <c r="BI110" s="211"/>
-      <c r="BJ110" s="211"/>
-      <c r="BK110" s="211"/>
-      <c r="BL110" s="211"/>
-      <c r="BM110" s="211"/>
-      <c r="BN110" s="211"/>
-      <c r="BO110" s="211"/>
-      <c r="BP110" s="211"/>
-      <c r="BQ110" s="211"/>
-      <c r="BR110" s="211"/>
-      <c r="BS110" s="212"/>
+      <c r="BG110" s="217"/>
+      <c r="BH110" s="217"/>
+      <c r="BI110" s="217"/>
+      <c r="BJ110" s="217"/>
+      <c r="BK110" s="217"/>
+      <c r="BL110" s="217"/>
+      <c r="BM110" s="217"/>
+      <c r="BN110" s="217"/>
+      <c r="BO110" s="217"/>
+      <c r="BP110" s="217"/>
+      <c r="BQ110" s="217"/>
+      <c r="BR110" s="217"/>
+      <c r="BS110" s="218"/>
     </row>
     <row r="111" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A111" s="228"/>
-      <c r="B111" s="213"/>
-      <c r="C111" s="214"/>
-      <c r="D111" s="214"/>
-      <c r="E111" s="214"/>
-      <c r="F111" s="214"/>
-      <c r="G111" s="214"/>
-      <c r="H111" s="214"/>
-      <c r="I111" s="214"/>
-      <c r="J111" s="214"/>
-      <c r="K111" s="214"/>
-      <c r="L111" s="214"/>
-      <c r="M111" s="214"/>
-      <c r="N111" s="214"/>
-      <c r="O111" s="215"/>
-      <c r="P111" s="213"/>
-      <c r="Q111" s="214"/>
-      <c r="R111" s="214"/>
-      <c r="S111" s="214"/>
-      <c r="T111" s="214"/>
-      <c r="U111" s="214"/>
-      <c r="V111" s="214"/>
-      <c r="W111" s="214"/>
-      <c r="X111" s="214"/>
-      <c r="Y111" s="214"/>
-      <c r="Z111" s="214"/>
-      <c r="AA111" s="214"/>
-      <c r="AB111" s="214"/>
-      <c r="AC111" s="215"/>
-      <c r="AD111" s="213"/>
-      <c r="AE111" s="214"/>
-      <c r="AF111" s="214"/>
-      <c r="AG111" s="214"/>
-      <c r="AH111" s="214"/>
-      <c r="AI111" s="214"/>
-      <c r="AJ111" s="214"/>
-      <c r="AK111" s="214"/>
-      <c r="AL111" s="214"/>
-      <c r="AM111" s="214"/>
-      <c r="AN111" s="214"/>
-      <c r="AO111" s="214"/>
-      <c r="AP111" s="214"/>
-      <c r="AQ111" s="215"/>
-      <c r="AR111" s="213"/>
-      <c r="AS111" s="214"/>
-      <c r="AT111" s="214"/>
-      <c r="AU111" s="214"/>
-      <c r="AV111" s="214"/>
-      <c r="AW111" s="214"/>
-      <c r="AX111" s="214"/>
-      <c r="AY111" s="214"/>
-      <c r="AZ111" s="214"/>
-      <c r="BA111" s="214"/>
-      <c r="BB111" s="214"/>
-      <c r="BC111" s="214"/>
-      <c r="BD111" s="214"/>
-      <c r="BE111" s="215"/>
-      <c r="BF111" s="213"/>
-      <c r="BG111" s="214"/>
-      <c r="BH111" s="214"/>
-      <c r="BI111" s="214"/>
-      <c r="BJ111" s="214"/>
-      <c r="BK111" s="214"/>
-      <c r="BL111" s="214"/>
-      <c r="BM111" s="214"/>
-      <c r="BN111" s="214"/>
-      <c r="BO111" s="214"/>
-      <c r="BP111" s="214"/>
-      <c r="BQ111" s="214"/>
-      <c r="BR111" s="214"/>
-      <c r="BS111" s="215"/>
+      <c r="A111" s="234"/>
+      <c r="B111" s="219"/>
+      <c r="C111" s="220"/>
+      <c r="D111" s="220"/>
+      <c r="E111" s="220"/>
+      <c r="F111" s="220"/>
+      <c r="G111" s="220"/>
+      <c r="H111" s="220"/>
+      <c r="I111" s="220"/>
+      <c r="J111" s="220"/>
+      <c r="K111" s="220"/>
+      <c r="L111" s="220"/>
+      <c r="M111" s="220"/>
+      <c r="N111" s="220"/>
+      <c r="O111" s="221"/>
+      <c r="P111" s="219"/>
+      <c r="Q111" s="220"/>
+      <c r="R111" s="220"/>
+      <c r="S111" s="220"/>
+      <c r="T111" s="220"/>
+      <c r="U111" s="220"/>
+      <c r="V111" s="220"/>
+      <c r="W111" s="220"/>
+      <c r="X111" s="220"/>
+      <c r="Y111" s="220"/>
+      <c r="Z111" s="220"/>
+      <c r="AA111" s="220"/>
+      <c r="AB111" s="220"/>
+      <c r="AC111" s="221"/>
+      <c r="AD111" s="219"/>
+      <c r="AE111" s="220"/>
+      <c r="AF111" s="220"/>
+      <c r="AG111" s="220"/>
+      <c r="AH111" s="220"/>
+      <c r="AI111" s="220"/>
+      <c r="AJ111" s="220"/>
+      <c r="AK111" s="220"/>
+      <c r="AL111" s="220"/>
+      <c r="AM111" s="220"/>
+      <c r="AN111" s="220"/>
+      <c r="AO111" s="220"/>
+      <c r="AP111" s="220"/>
+      <c r="AQ111" s="221"/>
+      <c r="AR111" s="219"/>
+      <c r="AS111" s="220"/>
+      <c r="AT111" s="220"/>
+      <c r="AU111" s="220"/>
+      <c r="AV111" s="220"/>
+      <c r="AW111" s="220"/>
+      <c r="AX111" s="220"/>
+      <c r="AY111" s="220"/>
+      <c r="AZ111" s="220"/>
+      <c r="BA111" s="220"/>
+      <c r="BB111" s="220"/>
+      <c r="BC111" s="220"/>
+      <c r="BD111" s="220"/>
+      <c r="BE111" s="221"/>
+      <c r="BF111" s="219"/>
+      <c r="BG111" s="220"/>
+      <c r="BH111" s="220"/>
+      <c r="BI111" s="220"/>
+      <c r="BJ111" s="220"/>
+      <c r="BK111" s="220"/>
+      <c r="BL111" s="220"/>
+      <c r="BM111" s="220"/>
+      <c r="BN111" s="220"/>
+      <c r="BO111" s="220"/>
+      <c r="BP111" s="220"/>
+      <c r="BQ111" s="220"/>
+      <c r="BR111" s="220"/>
+      <c r="BS111" s="221"/>
     </row>
     <row r="112" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A112" s="228"/>
-      <c r="B112" s="213"/>
-      <c r="C112" s="214"/>
-      <c r="D112" s="214"/>
-      <c r="E112" s="214"/>
-      <c r="F112" s="214"/>
-      <c r="G112" s="214"/>
-      <c r="H112" s="214"/>
-      <c r="I112" s="214"/>
-      <c r="J112" s="214"/>
-      <c r="K112" s="214"/>
-      <c r="L112" s="214"/>
-      <c r="M112" s="214"/>
-      <c r="N112" s="214"/>
-      <c r="O112" s="215"/>
-      <c r="P112" s="213"/>
-      <c r="Q112" s="214"/>
-      <c r="R112" s="214"/>
-      <c r="S112" s="214"/>
-      <c r="T112" s="214"/>
-      <c r="U112" s="214"/>
-      <c r="V112" s="214"/>
-      <c r="W112" s="214"/>
-      <c r="X112" s="214"/>
-      <c r="Y112" s="214"/>
-      <c r="Z112" s="214"/>
-      <c r="AA112" s="214"/>
-      <c r="AB112" s="214"/>
-      <c r="AC112" s="215"/>
-      <c r="AD112" s="213"/>
-      <c r="AE112" s="214"/>
-      <c r="AF112" s="214"/>
-      <c r="AG112" s="214"/>
-      <c r="AH112" s="214"/>
-      <c r="AI112" s="214"/>
-      <c r="AJ112" s="214"/>
-      <c r="AK112" s="214"/>
-      <c r="AL112" s="214"/>
-      <c r="AM112" s="214"/>
-      <c r="AN112" s="214"/>
-      <c r="AO112" s="214"/>
-      <c r="AP112" s="214"/>
-      <c r="AQ112" s="215"/>
-      <c r="AR112" s="213"/>
-      <c r="AS112" s="214"/>
-      <c r="AT112" s="214"/>
-      <c r="AU112" s="214"/>
-      <c r="AV112" s="214"/>
-      <c r="AW112" s="214"/>
-      <c r="AX112" s="214"/>
-      <c r="AY112" s="214"/>
-      <c r="AZ112" s="214"/>
-      <c r="BA112" s="214"/>
-      <c r="BB112" s="214"/>
-      <c r="BC112" s="214"/>
-      <c r="BD112" s="214"/>
-      <c r="BE112" s="215"/>
-      <c r="BF112" s="213"/>
-      <c r="BG112" s="214"/>
-      <c r="BH112" s="214"/>
-      <c r="BI112" s="214"/>
-      <c r="BJ112" s="214"/>
-      <c r="BK112" s="214"/>
-      <c r="BL112" s="214"/>
-      <c r="BM112" s="214"/>
-      <c r="BN112" s="214"/>
-      <c r="BO112" s="214"/>
-      <c r="BP112" s="214"/>
-      <c r="BQ112" s="214"/>
-      <c r="BR112" s="214"/>
-      <c r="BS112" s="215"/>
+      <c r="A112" s="234"/>
+      <c r="B112" s="219"/>
+      <c r="C112" s="220"/>
+      <c r="D112" s="220"/>
+      <c r="E112" s="220"/>
+      <c r="F112" s="220"/>
+      <c r="G112" s="220"/>
+      <c r="H112" s="220"/>
+      <c r="I112" s="220"/>
+      <c r="J112" s="220"/>
+      <c r="K112" s="220"/>
+      <c r="L112" s="220"/>
+      <c r="M112" s="220"/>
+      <c r="N112" s="220"/>
+      <c r="O112" s="221"/>
+      <c r="P112" s="219"/>
+      <c r="Q112" s="220"/>
+      <c r="R112" s="220"/>
+      <c r="S112" s="220"/>
+      <c r="T112" s="220"/>
+      <c r="U112" s="220"/>
+      <c r="V112" s="220"/>
+      <c r="W112" s="220"/>
+      <c r="X112" s="220"/>
+      <c r="Y112" s="220"/>
+      <c r="Z112" s="220"/>
+      <c r="AA112" s="220"/>
+      <c r="AB112" s="220"/>
+      <c r="AC112" s="221"/>
+      <c r="AD112" s="219"/>
+      <c r="AE112" s="220"/>
+      <c r="AF112" s="220"/>
+      <c r="AG112" s="220"/>
+      <c r="AH112" s="220"/>
+      <c r="AI112" s="220"/>
+      <c r="AJ112" s="220"/>
+      <c r="AK112" s="220"/>
+      <c r="AL112" s="220"/>
+      <c r="AM112" s="220"/>
+      <c r="AN112" s="220"/>
+      <c r="AO112" s="220"/>
+      <c r="AP112" s="220"/>
+      <c r="AQ112" s="221"/>
+      <c r="AR112" s="219"/>
+      <c r="AS112" s="220"/>
+      <c r="AT112" s="220"/>
+      <c r="AU112" s="220"/>
+      <c r="AV112" s="220"/>
+      <c r="AW112" s="220"/>
+      <c r="AX112" s="220"/>
+      <c r="AY112" s="220"/>
+      <c r="AZ112" s="220"/>
+      <c r="BA112" s="220"/>
+      <c r="BB112" s="220"/>
+      <c r="BC112" s="220"/>
+      <c r="BD112" s="220"/>
+      <c r="BE112" s="221"/>
+      <c r="BF112" s="219"/>
+      <c r="BG112" s="220"/>
+      <c r="BH112" s="220"/>
+      <c r="BI112" s="220"/>
+      <c r="BJ112" s="220"/>
+      <c r="BK112" s="220"/>
+      <c r="BL112" s="220"/>
+      <c r="BM112" s="220"/>
+      <c r="BN112" s="220"/>
+      <c r="BO112" s="220"/>
+      <c r="BP112" s="220"/>
+      <c r="BQ112" s="220"/>
+      <c r="BR112" s="220"/>
+      <c r="BS112" s="221"/>
     </row>
     <row r="113" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A113" s="228"/>
-      <c r="B113" s="213"/>
-      <c r="C113" s="214"/>
-      <c r="D113" s="214"/>
-      <c r="E113" s="214"/>
-      <c r="F113" s="214"/>
-      <c r="G113" s="214"/>
-      <c r="H113" s="214"/>
-      <c r="I113" s="214"/>
-      <c r="J113" s="214"/>
-      <c r="K113" s="214"/>
-      <c r="L113" s="214"/>
-      <c r="M113" s="214"/>
-      <c r="N113" s="214"/>
-      <c r="O113" s="215"/>
-      <c r="P113" s="213"/>
-      <c r="Q113" s="214"/>
-      <c r="R113" s="214"/>
-      <c r="S113" s="214"/>
-      <c r="T113" s="214"/>
-      <c r="U113" s="214"/>
-      <c r="V113" s="214"/>
-      <c r="W113" s="214"/>
-      <c r="X113" s="214"/>
-      <c r="Y113" s="214"/>
-      <c r="Z113" s="214"/>
-      <c r="AA113" s="214"/>
-      <c r="AB113" s="214"/>
-      <c r="AC113" s="215"/>
-      <c r="AD113" s="213"/>
-      <c r="AE113" s="214"/>
-      <c r="AF113" s="214"/>
-      <c r="AG113" s="214"/>
-      <c r="AH113" s="214"/>
-      <c r="AI113" s="214"/>
-      <c r="AJ113" s="214"/>
-      <c r="AK113" s="214"/>
-      <c r="AL113" s="214"/>
-      <c r="AM113" s="214"/>
-      <c r="AN113" s="214"/>
-      <c r="AO113" s="214"/>
-      <c r="AP113" s="214"/>
-      <c r="AQ113" s="215"/>
-      <c r="AR113" s="213"/>
-      <c r="AS113" s="214"/>
-      <c r="AT113" s="214"/>
-      <c r="AU113" s="214"/>
-      <c r="AV113" s="214"/>
-      <c r="AW113" s="214"/>
-      <c r="AX113" s="214"/>
-      <c r="AY113" s="214"/>
-      <c r="AZ113" s="214"/>
-      <c r="BA113" s="214"/>
-      <c r="BB113" s="214"/>
-      <c r="BC113" s="214"/>
-      <c r="BD113" s="214"/>
-      <c r="BE113" s="215"/>
-      <c r="BF113" s="213"/>
-      <c r="BG113" s="214"/>
-      <c r="BH113" s="214"/>
-      <c r="BI113" s="214"/>
-      <c r="BJ113" s="214"/>
-      <c r="BK113" s="214"/>
-      <c r="BL113" s="214"/>
-      <c r="BM113" s="214"/>
-      <c r="BN113" s="214"/>
-      <c r="BO113" s="214"/>
-      <c r="BP113" s="214"/>
-      <c r="BQ113" s="214"/>
-      <c r="BR113" s="214"/>
-      <c r="BS113" s="215"/>
+      <c r="A113" s="234"/>
+      <c r="B113" s="219"/>
+      <c r="C113" s="220"/>
+      <c r="D113" s="220"/>
+      <c r="E113" s="220"/>
+      <c r="F113" s="220"/>
+      <c r="G113" s="220"/>
+      <c r="H113" s="220"/>
+      <c r="I113" s="220"/>
+      <c r="J113" s="220"/>
+      <c r="K113" s="220"/>
+      <c r="L113" s="220"/>
+      <c r="M113" s="220"/>
+      <c r="N113" s="220"/>
+      <c r="O113" s="221"/>
+      <c r="P113" s="219"/>
+      <c r="Q113" s="220"/>
+      <c r="R113" s="220"/>
+      <c r="S113" s="220"/>
+      <c r="T113" s="220"/>
+      <c r="U113" s="220"/>
+      <c r="V113" s="220"/>
+      <c r="W113" s="220"/>
+      <c r="X113" s="220"/>
+      <c r="Y113" s="220"/>
+      <c r="Z113" s="220"/>
+      <c r="AA113" s="220"/>
+      <c r="AB113" s="220"/>
+      <c r="AC113" s="221"/>
+      <c r="AD113" s="219"/>
+      <c r="AE113" s="220"/>
+      <c r="AF113" s="220"/>
+      <c r="AG113" s="220"/>
+      <c r="AH113" s="220"/>
+      <c r="AI113" s="220"/>
+      <c r="AJ113" s="220"/>
+      <c r="AK113" s="220"/>
+      <c r="AL113" s="220"/>
+      <c r="AM113" s="220"/>
+      <c r="AN113" s="220"/>
+      <c r="AO113" s="220"/>
+      <c r="AP113" s="220"/>
+      <c r="AQ113" s="221"/>
+      <c r="AR113" s="219"/>
+      <c r="AS113" s="220"/>
+      <c r="AT113" s="220"/>
+      <c r="AU113" s="220"/>
+      <c r="AV113" s="220"/>
+      <c r="AW113" s="220"/>
+      <c r="AX113" s="220"/>
+      <c r="AY113" s="220"/>
+      <c r="AZ113" s="220"/>
+      <c r="BA113" s="220"/>
+      <c r="BB113" s="220"/>
+      <c r="BC113" s="220"/>
+      <c r="BD113" s="220"/>
+      <c r="BE113" s="221"/>
+      <c r="BF113" s="219"/>
+      <c r="BG113" s="220"/>
+      <c r="BH113" s="220"/>
+      <c r="BI113" s="220"/>
+      <c r="BJ113" s="220"/>
+      <c r="BK113" s="220"/>
+      <c r="BL113" s="220"/>
+      <c r="BM113" s="220"/>
+      <c r="BN113" s="220"/>
+      <c r="BO113" s="220"/>
+      <c r="BP113" s="220"/>
+      <c r="BQ113" s="220"/>
+      <c r="BR113" s="220"/>
+      <c r="BS113" s="221"/>
     </row>
     <row r="114" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A114" s="228"/>
-      <c r="B114" s="213"/>
-      <c r="C114" s="214"/>
-      <c r="D114" s="214"/>
-      <c r="E114" s="214"/>
-      <c r="F114" s="214"/>
-      <c r="G114" s="214"/>
-      <c r="H114" s="214"/>
-      <c r="I114" s="214"/>
-      <c r="J114" s="214"/>
-      <c r="K114" s="214"/>
-      <c r="L114" s="214"/>
-      <c r="M114" s="214"/>
-      <c r="N114" s="214"/>
-      <c r="O114" s="215"/>
-      <c r="P114" s="213"/>
-      <c r="Q114" s="214"/>
-      <c r="R114" s="214"/>
-      <c r="S114" s="214"/>
-      <c r="T114" s="214"/>
-      <c r="U114" s="214"/>
-      <c r="V114" s="214"/>
-      <c r="W114" s="214"/>
-      <c r="X114" s="214"/>
-      <c r="Y114" s="214"/>
-      <c r="Z114" s="214"/>
-      <c r="AA114" s="214"/>
-      <c r="AB114" s="214"/>
-      <c r="AC114" s="215"/>
-      <c r="AD114" s="213"/>
-      <c r="AE114" s="214"/>
-      <c r="AF114" s="214"/>
-      <c r="AG114" s="214"/>
-      <c r="AH114" s="214"/>
-      <c r="AI114" s="214"/>
-      <c r="AJ114" s="214"/>
-      <c r="AK114" s="214"/>
-      <c r="AL114" s="214"/>
-      <c r="AM114" s="214"/>
-      <c r="AN114" s="214"/>
-      <c r="AO114" s="214"/>
-      <c r="AP114" s="214"/>
-      <c r="AQ114" s="215"/>
-      <c r="AR114" s="213"/>
-      <c r="AS114" s="214"/>
-      <c r="AT114" s="214"/>
-      <c r="AU114" s="214"/>
-      <c r="AV114" s="214"/>
-      <c r="AW114" s="214"/>
-      <c r="AX114" s="214"/>
-      <c r="AY114" s="214"/>
-      <c r="AZ114" s="214"/>
-      <c r="BA114" s="214"/>
-      <c r="BB114" s="214"/>
-      <c r="BC114" s="214"/>
-      <c r="BD114" s="214"/>
-      <c r="BE114" s="215"/>
-      <c r="BF114" s="213"/>
-      <c r="BG114" s="214"/>
-      <c r="BH114" s="214"/>
-      <c r="BI114" s="214"/>
-      <c r="BJ114" s="214"/>
-      <c r="BK114" s="214"/>
-      <c r="BL114" s="214"/>
-      <c r="BM114" s="214"/>
-      <c r="BN114" s="214"/>
-      <c r="BO114" s="214"/>
-      <c r="BP114" s="214"/>
-      <c r="BQ114" s="214"/>
-      <c r="BR114" s="214"/>
-      <c r="BS114" s="215"/>
+      <c r="A114" s="234"/>
+      <c r="B114" s="219"/>
+      <c r="C114" s="220"/>
+      <c r="D114" s="220"/>
+      <c r="E114" s="220"/>
+      <c r="F114" s="220"/>
+      <c r="G114" s="220"/>
+      <c r="H114" s="220"/>
+      <c r="I114" s="220"/>
+      <c r="J114" s="220"/>
+      <c r="K114" s="220"/>
+      <c r="L114" s="220"/>
+      <c r="M114" s="220"/>
+      <c r="N114" s="220"/>
+      <c r="O114" s="221"/>
+      <c r="P114" s="219"/>
+      <c r="Q114" s="220"/>
+      <c r="R114" s="220"/>
+      <c r="S114" s="220"/>
+      <c r="T114" s="220"/>
+      <c r="U114" s="220"/>
+      <c r="V114" s="220"/>
+      <c r="W114" s="220"/>
+      <c r="X114" s="220"/>
+      <c r="Y114" s="220"/>
+      <c r="Z114" s="220"/>
+      <c r="AA114" s="220"/>
+      <c r="AB114" s="220"/>
+      <c r="AC114" s="221"/>
+      <c r="AD114" s="219"/>
+      <c r="AE114" s="220"/>
+      <c r="AF114" s="220"/>
+      <c r="AG114" s="220"/>
+      <c r="AH114" s="220"/>
+      <c r="AI114" s="220"/>
+      <c r="AJ114" s="220"/>
+      <c r="AK114" s="220"/>
+      <c r="AL114" s="220"/>
+      <c r="AM114" s="220"/>
+      <c r="AN114" s="220"/>
+      <c r="AO114" s="220"/>
+      <c r="AP114" s="220"/>
+      <c r="AQ114" s="221"/>
+      <c r="AR114" s="219"/>
+      <c r="AS114" s="220"/>
+      <c r="AT114" s="220"/>
+      <c r="AU114" s="220"/>
+      <c r="AV114" s="220"/>
+      <c r="AW114" s="220"/>
+      <c r="AX114" s="220"/>
+      <c r="AY114" s="220"/>
+      <c r="AZ114" s="220"/>
+      <c r="BA114" s="220"/>
+      <c r="BB114" s="220"/>
+      <c r="BC114" s="220"/>
+      <c r="BD114" s="220"/>
+      <c r="BE114" s="221"/>
+      <c r="BF114" s="219"/>
+      <c r="BG114" s="220"/>
+      <c r="BH114" s="220"/>
+      <c r="BI114" s="220"/>
+      <c r="BJ114" s="220"/>
+      <c r="BK114" s="220"/>
+      <c r="BL114" s="220"/>
+      <c r="BM114" s="220"/>
+      <c r="BN114" s="220"/>
+      <c r="BO114" s="220"/>
+      <c r="BP114" s="220"/>
+      <c r="BQ114" s="220"/>
+      <c r="BR114" s="220"/>
+      <c r="BS114" s="221"/>
     </row>
     <row r="115" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A115" s="228"/>
-      <c r="B115" s="213"/>
-      <c r="C115" s="214"/>
-      <c r="D115" s="214"/>
-      <c r="E115" s="214"/>
-      <c r="F115" s="214"/>
-      <c r="G115" s="214"/>
-      <c r="H115" s="214"/>
-      <c r="I115" s="214"/>
-      <c r="J115" s="214"/>
-      <c r="K115" s="214"/>
-      <c r="L115" s="214"/>
-      <c r="M115" s="214"/>
-      <c r="N115" s="214"/>
-      <c r="O115" s="215"/>
-      <c r="P115" s="213"/>
-      <c r="Q115" s="214"/>
-      <c r="R115" s="214"/>
-      <c r="S115" s="214"/>
-      <c r="T115" s="214"/>
-      <c r="U115" s="214"/>
-      <c r="V115" s="214"/>
-      <c r="W115" s="214"/>
-      <c r="X115" s="214"/>
-      <c r="Y115" s="214"/>
-      <c r="Z115" s="214"/>
-      <c r="AA115" s="214"/>
-      <c r="AB115" s="214"/>
-      <c r="AC115" s="215"/>
-      <c r="AD115" s="213"/>
-      <c r="AE115" s="214"/>
-      <c r="AF115" s="214"/>
-      <c r="AG115" s="214"/>
-      <c r="AH115" s="214"/>
-      <c r="AI115" s="214"/>
-      <c r="AJ115" s="214"/>
-      <c r="AK115" s="214"/>
-      <c r="AL115" s="214"/>
-      <c r="AM115" s="214"/>
-      <c r="AN115" s="214"/>
-      <c r="AO115" s="214"/>
-      <c r="AP115" s="214"/>
-      <c r="AQ115" s="215"/>
-      <c r="AR115" s="213"/>
-      <c r="AS115" s="214"/>
-      <c r="AT115" s="214"/>
-      <c r="AU115" s="214"/>
-      <c r="AV115" s="214"/>
-      <c r="AW115" s="214"/>
-      <c r="AX115" s="214"/>
-      <c r="AY115" s="214"/>
-      <c r="AZ115" s="214"/>
-      <c r="BA115" s="214"/>
-      <c r="BB115" s="214"/>
-      <c r="BC115" s="214"/>
-      <c r="BD115" s="214"/>
-      <c r="BE115" s="215"/>
-      <c r="BF115" s="213"/>
-      <c r="BG115" s="214"/>
-      <c r="BH115" s="214"/>
-      <c r="BI115" s="214"/>
-      <c r="BJ115" s="214"/>
-      <c r="BK115" s="214"/>
-      <c r="BL115" s="214"/>
-      <c r="BM115" s="214"/>
-      <c r="BN115" s="214"/>
-      <c r="BO115" s="214"/>
-      <c r="BP115" s="214"/>
-      <c r="BQ115" s="214"/>
-      <c r="BR115" s="214"/>
-      <c r="BS115" s="215"/>
+      <c r="A115" s="234"/>
+      <c r="B115" s="219"/>
+      <c r="C115" s="220"/>
+      <c r="D115" s="220"/>
+      <c r="E115" s="220"/>
+      <c r="F115" s="220"/>
+      <c r="G115" s="220"/>
+      <c r="H115" s="220"/>
+      <c r="I115" s="220"/>
+      <c r="J115" s="220"/>
+      <c r="K115" s="220"/>
+      <c r="L115" s="220"/>
+      <c r="M115" s="220"/>
+      <c r="N115" s="220"/>
+      <c r="O115" s="221"/>
+      <c r="P115" s="219"/>
+      <c r="Q115" s="220"/>
+      <c r="R115" s="220"/>
+      <c r="S115" s="220"/>
+      <c r="T115" s="220"/>
+      <c r="U115" s="220"/>
+      <c r="V115" s="220"/>
+      <c r="W115" s="220"/>
+      <c r="X115" s="220"/>
+      <c r="Y115" s="220"/>
+      <c r="Z115" s="220"/>
+      <c r="AA115" s="220"/>
+      <c r="AB115" s="220"/>
+      <c r="AC115" s="221"/>
+      <c r="AD115" s="219"/>
+      <c r="AE115" s="220"/>
+      <c r="AF115" s="220"/>
+      <c r="AG115" s="220"/>
+      <c r="AH115" s="220"/>
+      <c r="AI115" s="220"/>
+      <c r="AJ115" s="220"/>
+      <c r="AK115" s="220"/>
+      <c r="AL115" s="220"/>
+      <c r="AM115" s="220"/>
+      <c r="AN115" s="220"/>
+      <c r="AO115" s="220"/>
+      <c r="AP115" s="220"/>
+      <c r="AQ115" s="221"/>
+      <c r="AR115" s="219"/>
+      <c r="AS115" s="220"/>
+      <c r="AT115" s="220"/>
+      <c r="AU115" s="220"/>
+      <c r="AV115" s="220"/>
+      <c r="AW115" s="220"/>
+      <c r="AX115" s="220"/>
+      <c r="AY115" s="220"/>
+      <c r="AZ115" s="220"/>
+      <c r="BA115" s="220"/>
+      <c r="BB115" s="220"/>
+      <c r="BC115" s="220"/>
+      <c r="BD115" s="220"/>
+      <c r="BE115" s="221"/>
+      <c r="BF115" s="219"/>
+      <c r="BG115" s="220"/>
+      <c r="BH115" s="220"/>
+      <c r="BI115" s="220"/>
+      <c r="BJ115" s="220"/>
+      <c r="BK115" s="220"/>
+      <c r="BL115" s="220"/>
+      <c r="BM115" s="220"/>
+      <c r="BN115" s="220"/>
+      <c r="BO115" s="220"/>
+      <c r="BP115" s="220"/>
+      <c r="BQ115" s="220"/>
+      <c r="BR115" s="220"/>
+      <c r="BS115" s="221"/>
     </row>
     <row r="116" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="229"/>
-      <c r="B116" s="216"/>
-      <c r="C116" s="217"/>
-      <c r="D116" s="217"/>
-      <c r="E116" s="217"/>
-      <c r="F116" s="217"/>
-      <c r="G116" s="217"/>
-      <c r="H116" s="217"/>
-      <c r="I116" s="217"/>
-      <c r="J116" s="217"/>
-      <c r="K116" s="217"/>
-      <c r="L116" s="217"/>
-      <c r="M116" s="217"/>
-      <c r="N116" s="217"/>
-      <c r="O116" s="218"/>
-      <c r="P116" s="216"/>
-      <c r="Q116" s="217"/>
-      <c r="R116" s="217"/>
-      <c r="S116" s="217"/>
-      <c r="T116" s="217"/>
-      <c r="U116" s="217"/>
-      <c r="V116" s="217"/>
-      <c r="W116" s="217"/>
-      <c r="X116" s="217"/>
-      <c r="Y116" s="217"/>
-      <c r="Z116" s="217"/>
-      <c r="AA116" s="217"/>
-      <c r="AB116" s="217"/>
-      <c r="AC116" s="218"/>
-      <c r="AD116" s="216"/>
-      <c r="AE116" s="217"/>
-      <c r="AF116" s="217"/>
-      <c r="AG116" s="217"/>
-      <c r="AH116" s="217"/>
-      <c r="AI116" s="217"/>
-      <c r="AJ116" s="217"/>
-      <c r="AK116" s="217"/>
-      <c r="AL116" s="217"/>
-      <c r="AM116" s="217"/>
-      <c r="AN116" s="217"/>
-      <c r="AO116" s="217"/>
-      <c r="AP116" s="217"/>
-      <c r="AQ116" s="218"/>
-      <c r="AR116" s="216"/>
-      <c r="AS116" s="217"/>
-      <c r="AT116" s="217"/>
-      <c r="AU116" s="217"/>
-      <c r="AV116" s="217"/>
-      <c r="AW116" s="217"/>
-      <c r="AX116" s="217"/>
-      <c r="AY116" s="217"/>
-      <c r="AZ116" s="217"/>
-      <c r="BA116" s="217"/>
-      <c r="BB116" s="217"/>
-      <c r="BC116" s="217"/>
-      <c r="BD116" s="217"/>
-      <c r="BE116" s="218"/>
-      <c r="BF116" s="216"/>
-      <c r="BG116" s="217"/>
-      <c r="BH116" s="217"/>
-      <c r="BI116" s="217"/>
-      <c r="BJ116" s="217"/>
-      <c r="BK116" s="217"/>
-      <c r="BL116" s="217"/>
-      <c r="BM116" s="217"/>
-      <c r="BN116" s="217"/>
-      <c r="BO116" s="217"/>
-      <c r="BP116" s="217"/>
-      <c r="BQ116" s="217"/>
-      <c r="BR116" s="217"/>
-      <c r="BS116" s="218"/>
+      <c r="A116" s="235"/>
+      <c r="B116" s="222"/>
+      <c r="C116" s="223"/>
+      <c r="D116" s="223"/>
+      <c r="E116" s="223"/>
+      <c r="F116" s="223"/>
+      <c r="G116" s="223"/>
+      <c r="H116" s="223"/>
+      <c r="I116" s="223"/>
+      <c r="J116" s="223"/>
+      <c r="K116" s="223"/>
+      <c r="L116" s="223"/>
+      <c r="M116" s="223"/>
+      <c r="N116" s="223"/>
+      <c r="O116" s="224"/>
+      <c r="P116" s="222"/>
+      <c r="Q116" s="223"/>
+      <c r="R116" s="223"/>
+      <c r="S116" s="223"/>
+      <c r="T116" s="223"/>
+      <c r="U116" s="223"/>
+      <c r="V116" s="223"/>
+      <c r="W116" s="223"/>
+      <c r="X116" s="223"/>
+      <c r="Y116" s="223"/>
+      <c r="Z116" s="223"/>
+      <c r="AA116" s="223"/>
+      <c r="AB116" s="223"/>
+      <c r="AC116" s="224"/>
+      <c r="AD116" s="222"/>
+      <c r="AE116" s="223"/>
+      <c r="AF116" s="223"/>
+      <c r="AG116" s="223"/>
+      <c r="AH116" s="223"/>
+      <c r="AI116" s="223"/>
+      <c r="AJ116" s="223"/>
+      <c r="AK116" s="223"/>
+      <c r="AL116" s="223"/>
+      <c r="AM116" s="223"/>
+      <c r="AN116" s="223"/>
+      <c r="AO116" s="223"/>
+      <c r="AP116" s="223"/>
+      <c r="AQ116" s="224"/>
+      <c r="AR116" s="222"/>
+      <c r="AS116" s="223"/>
+      <c r="AT116" s="223"/>
+      <c r="AU116" s="223"/>
+      <c r="AV116" s="223"/>
+      <c r="AW116" s="223"/>
+      <c r="AX116" s="223"/>
+      <c r="AY116" s="223"/>
+      <c r="AZ116" s="223"/>
+      <c r="BA116" s="223"/>
+      <c r="BB116" s="223"/>
+      <c r="BC116" s="223"/>
+      <c r="BD116" s="223"/>
+      <c r="BE116" s="224"/>
+      <c r="BF116" s="222"/>
+      <c r="BG116" s="223"/>
+      <c r="BH116" s="223"/>
+      <c r="BI116" s="223"/>
+      <c r="BJ116" s="223"/>
+      <c r="BK116" s="223"/>
+      <c r="BL116" s="223"/>
+      <c r="BM116" s="223"/>
+      <c r="BN116" s="223"/>
+      <c r="BO116" s="223"/>
+      <c r="BP116" s="223"/>
+      <c r="BQ116" s="223"/>
+      <c r="BR116" s="223"/>
+      <c r="BS116" s="224"/>
     </row>
     <row r="117" spans="1:71" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="118" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12844,20 +12868,20 @@
     <mergeCell ref="BF5:BG5"/>
     <mergeCell ref="AB108:AC108"/>
     <mergeCell ref="AV5:AW5"/>
+    <mergeCell ref="AX5:AY5"/>
     <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="AX5:AY5"/>
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="L108:M108"/>
     <mergeCell ref="AR3:BE3"/>
-    <mergeCell ref="L108:M108"/>
     <mergeCell ref="N108:O108"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="BR108:BS108"/>
     <mergeCell ref="AD3:AQ3"/>
     <mergeCell ref="BH108:BI108"/>
     <mergeCell ref="Z108:AA108"/>
-    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="P4:Q4"/>
     <mergeCell ref="BH4:BI4"/>
     <mergeCell ref="B109:O109"/>
     <mergeCell ref="BJ4:BK4"/>
@@ -12925,8 +12949,8 @@
     <mergeCell ref="BJ5:BK5"/>
     <mergeCell ref="AD4:AE4"/>
     <mergeCell ref="BL5:BM5"/>
+    <mergeCell ref="N4:O4"/>
     <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="N4:O4"/>
     <mergeCell ref="F108:G108"/>
     <mergeCell ref="AB5:AC5"/>
     <mergeCell ref="B3:O3"/>
@@ -12945,8 +12969,8 @@
     <mergeCell ref="P2:AC2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="P3:AC3"/>
+    <mergeCell ref="AX4:AY4"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="P4:Q4"/>
     <mergeCell ref="BF3:BS3"/>
     <mergeCell ref="B1:E2"/>
     <mergeCell ref="AR1:BE2"/>
@@ -12973,15 +12997,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="231" t="s">
+      <c r="A1" s="237" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="234">
+      <c r="B1" s="240">
         <v>46160</v>
       </c>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -12994,71 +13018,71 @@
       <c r="O1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200" t="s">
+      <c r="P1" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="201"/>
-      <c r="Y1" s="201"/>
-      <c r="Z1" s="201"/>
-      <c r="AA1" s="201"/>
-      <c r="AB1" s="201"/>
-      <c r="AC1" s="201"/>
-      <c r="AD1" s="223"/>
-      <c r="AE1" s="201"/>
-      <c r="AF1" s="201"/>
-      <c r="AG1" s="201"/>
-      <c r="AH1" s="201"/>
-      <c r="AI1" s="201"/>
-      <c r="AJ1" s="201"/>
-      <c r="AK1" s="201"/>
-      <c r="AL1" s="201"/>
-      <c r="AM1" s="201"/>
-      <c r="AN1" s="201"/>
-      <c r="AO1" s="201"/>
-      <c r="AP1" s="201"/>
-      <c r="AQ1" s="201"/>
-      <c r="AR1" s="223"/>
-      <c r="AS1" s="201"/>
-      <c r="AT1" s="201"/>
-      <c r="AU1" s="201"/>
-      <c r="AV1" s="201"/>
-      <c r="AW1" s="201"/>
-      <c r="AX1" s="201"/>
-      <c r="AY1" s="201"/>
-      <c r="AZ1" s="201"/>
-      <c r="BA1" s="201"/>
-      <c r="BB1" s="201"/>
-      <c r="BC1" s="201"/>
-      <c r="BD1" s="201"/>
-      <c r="BE1" s="201"/>
-      <c r="BF1" s="224"/>
-      <c r="BG1" s="201"/>
-      <c r="BH1" s="201"/>
-      <c r="BI1" s="201"/>
-      <c r="BJ1" s="201"/>
-      <c r="BK1" s="201"/>
-      <c r="BL1" s="201"/>
-      <c r="BM1" s="201"/>
-      <c r="BN1" s="201"/>
-      <c r="BO1" s="201"/>
-      <c r="BP1" s="201"/>
-      <c r="BQ1" s="201"/>
-      <c r="BR1" s="201"/>
-      <c r="BS1" s="225"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
+      <c r="Y1" s="207"/>
+      <c r="Z1" s="207"/>
+      <c r="AA1" s="207"/>
+      <c r="AB1" s="207"/>
+      <c r="AC1" s="207"/>
+      <c r="AD1" s="229"/>
+      <c r="AE1" s="207"/>
+      <c r="AF1" s="207"/>
+      <c r="AG1" s="207"/>
+      <c r="AH1" s="207"/>
+      <c r="AI1" s="207"/>
+      <c r="AJ1" s="207"/>
+      <c r="AK1" s="207"/>
+      <c r="AL1" s="207"/>
+      <c r="AM1" s="207"/>
+      <c r="AN1" s="207"/>
+      <c r="AO1" s="207"/>
+      <c r="AP1" s="207"/>
+      <c r="AQ1" s="207"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="207"/>
+      <c r="AT1" s="207"/>
+      <c r="AU1" s="207"/>
+      <c r="AV1" s="207"/>
+      <c r="AW1" s="207"/>
+      <c r="AX1" s="207"/>
+      <c r="AY1" s="207"/>
+      <c r="AZ1" s="207"/>
+      <c r="BA1" s="207"/>
+      <c r="BB1" s="207"/>
+      <c r="BC1" s="207"/>
+      <c r="BD1" s="207"/>
+      <c r="BE1" s="207"/>
+      <c r="BF1" s="230"/>
+      <c r="BG1" s="207"/>
+      <c r="BH1" s="207"/>
+      <c r="BI1" s="207"/>
+      <c r="BJ1" s="207"/>
+      <c r="BK1" s="207"/>
+      <c r="BL1" s="207"/>
+      <c r="BM1" s="207"/>
+      <c r="BN1" s="207"/>
+      <c r="BO1" s="207"/>
+      <c r="BP1" s="207"/>
+      <c r="BQ1" s="207"/>
+      <c r="BR1" s="207"/>
+      <c r="BS1" s="231"/>
     </row>
     <row r="2" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="232"/>
-      <c r="B2" s="217"/>
-      <c r="C2" s="217"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="217"/>
+      <c r="A2" s="238"/>
+      <c r="B2" s="223"/>
+      <c r="C2" s="223"/>
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
@@ -13071,479 +13095,479 @@
       <c r="O2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="204" t="s">
+      <c r="P2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="205"/>
-      <c r="R2" s="205"/>
-      <c r="S2" s="205"/>
-      <c r="T2" s="205"/>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
-      <c r="W2" s="205"/>
-      <c r="X2" s="205"/>
-      <c r="Y2" s="205"/>
-      <c r="Z2" s="205"/>
-      <c r="AA2" s="205"/>
-      <c r="AB2" s="205"/>
-      <c r="AC2" s="205"/>
-      <c r="AD2" s="205"/>
-      <c r="AE2" s="205"/>
-      <c r="AF2" s="205"/>
-      <c r="AG2" s="205"/>
-      <c r="AH2" s="205"/>
-      <c r="AI2" s="205"/>
-      <c r="AJ2" s="205"/>
-      <c r="AK2" s="205"/>
-      <c r="AL2" s="205"/>
-      <c r="AM2" s="205"/>
-      <c r="AN2" s="205"/>
-      <c r="AO2" s="205"/>
-      <c r="AP2" s="205"/>
-      <c r="AQ2" s="205"/>
-      <c r="AR2" s="205"/>
-      <c r="AS2" s="205"/>
-      <c r="AT2" s="205"/>
-      <c r="AU2" s="205"/>
-      <c r="AV2" s="205"/>
-      <c r="AW2" s="205"/>
-      <c r="AX2" s="205"/>
-      <c r="AY2" s="205"/>
-      <c r="AZ2" s="205"/>
-      <c r="BA2" s="205"/>
-      <c r="BB2" s="205"/>
-      <c r="BC2" s="205"/>
-      <c r="BD2" s="205"/>
-      <c r="BE2" s="205"/>
-      <c r="BF2" s="205"/>
-      <c r="BG2" s="205"/>
-      <c r="BH2" s="205"/>
-      <c r="BI2" s="205"/>
-      <c r="BJ2" s="205"/>
-      <c r="BK2" s="205"/>
-      <c r="BL2" s="205"/>
-      <c r="BM2" s="205"/>
-      <c r="BN2" s="205"/>
-      <c r="BO2" s="205"/>
-      <c r="BP2" s="205"/>
-      <c r="BQ2" s="205"/>
-      <c r="BR2" s="205"/>
-      <c r="BS2" s="226"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
+      <c r="AA2" s="211"/>
+      <c r="AB2" s="211"/>
+      <c r="AC2" s="211"/>
+      <c r="AD2" s="211"/>
+      <c r="AE2" s="211"/>
+      <c r="AF2" s="211"/>
+      <c r="AG2" s="211"/>
+      <c r="AH2" s="211"/>
+      <c r="AI2" s="211"/>
+      <c r="AJ2" s="211"/>
+      <c r="AK2" s="211"/>
+      <c r="AL2" s="211"/>
+      <c r="AM2" s="211"/>
+      <c r="AN2" s="211"/>
+      <c r="AO2" s="211"/>
+      <c r="AP2" s="211"/>
+      <c r="AQ2" s="211"/>
+      <c r="AR2" s="211"/>
+      <c r="AS2" s="211"/>
+      <c r="AT2" s="211"/>
+      <c r="AU2" s="211"/>
+      <c r="AV2" s="211"/>
+      <c r="AW2" s="211"/>
+      <c r="AX2" s="211"/>
+      <c r="AY2" s="211"/>
+      <c r="AZ2" s="211"/>
+      <c r="BA2" s="211"/>
+      <c r="BB2" s="211"/>
+      <c r="BC2" s="211"/>
+      <c r="BD2" s="211"/>
+      <c r="BE2" s="211"/>
+      <c r="BF2" s="211"/>
+      <c r="BG2" s="211"/>
+      <c r="BH2" s="211"/>
+      <c r="BI2" s="211"/>
+      <c r="BJ2" s="211"/>
+      <c r="BK2" s="211"/>
+      <c r="BL2" s="211"/>
+      <c r="BM2" s="211"/>
+      <c r="BN2" s="211"/>
+      <c r="BO2" s="211"/>
+      <c r="BP2" s="211"/>
+      <c r="BQ2" s="211"/>
+      <c r="BR2" s="211"/>
+      <c r="BS2" s="232"/>
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="197" t="str">
+      <c r="B3" s="203" t="str">
         <f>"Woche " &amp; WEEKNUM(B4)</f>
         <v>Woche 21</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="198"/>
-      <c r="O3" s="199"/>
-      <c r="P3" s="219" t="str">
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="204"/>
+      <c r="J3" s="204"/>
+      <c r="K3" s="204"/>
+      <c r="L3" s="204"/>
+      <c r="M3" s="204"/>
+      <c r="N3" s="204"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(P4)</f>
         <v>Woche 22</v>
       </c>
-      <c r="Q3" s="198"/>
-      <c r="R3" s="198"/>
-      <c r="S3" s="198"/>
-      <c r="T3" s="198"/>
-      <c r="U3" s="198"/>
-      <c r="V3" s="198"/>
-      <c r="W3" s="198"/>
-      <c r="X3" s="198"/>
-      <c r="Y3" s="198"/>
-      <c r="Z3" s="198"/>
-      <c r="AA3" s="198"/>
-      <c r="AB3" s="198"/>
-      <c r="AC3" s="199"/>
-      <c r="AD3" s="219" t="str">
+      <c r="Q3" s="204"/>
+      <c r="R3" s="204"/>
+      <c r="S3" s="204"/>
+      <c r="T3" s="204"/>
+      <c r="U3" s="204"/>
+      <c r="V3" s="204"/>
+      <c r="W3" s="204"/>
+      <c r="X3" s="204"/>
+      <c r="Y3" s="204"/>
+      <c r="Z3" s="204"/>
+      <c r="AA3" s="204"/>
+      <c r="AB3" s="204"/>
+      <c r="AC3" s="205"/>
+      <c r="AD3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(AD4)</f>
         <v>Woche 23</v>
       </c>
-      <c r="AE3" s="198"/>
-      <c r="AF3" s="198"/>
-      <c r="AG3" s="198"/>
-      <c r="AH3" s="198"/>
-      <c r="AI3" s="198"/>
-      <c r="AJ3" s="198"/>
-      <c r="AK3" s="198"/>
-      <c r="AL3" s="198"/>
-      <c r="AM3" s="198"/>
-      <c r="AN3" s="198"/>
-      <c r="AO3" s="198"/>
-      <c r="AP3" s="198"/>
-      <c r="AQ3" s="199"/>
-      <c r="AR3" s="219" t="str">
+      <c r="AE3" s="204"/>
+      <c r="AF3" s="204"/>
+      <c r="AG3" s="204"/>
+      <c r="AH3" s="204"/>
+      <c r="AI3" s="204"/>
+      <c r="AJ3" s="204"/>
+      <c r="AK3" s="204"/>
+      <c r="AL3" s="204"/>
+      <c r="AM3" s="204"/>
+      <c r="AN3" s="204"/>
+      <c r="AO3" s="204"/>
+      <c r="AP3" s="204"/>
+      <c r="AQ3" s="205"/>
+      <c r="AR3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(AR4)</f>
         <v>Woche 24</v>
       </c>
-      <c r="AS3" s="198"/>
-      <c r="AT3" s="198"/>
-      <c r="AU3" s="198"/>
-      <c r="AV3" s="198"/>
-      <c r="AW3" s="198"/>
-      <c r="AX3" s="198"/>
-      <c r="AY3" s="198"/>
-      <c r="AZ3" s="198"/>
-      <c r="BA3" s="198"/>
-      <c r="BB3" s="198"/>
-      <c r="BC3" s="198"/>
-      <c r="BD3" s="198"/>
-      <c r="BE3" s="199"/>
-      <c r="BF3" s="219" t="str">
+      <c r="AS3" s="204"/>
+      <c r="AT3" s="204"/>
+      <c r="AU3" s="204"/>
+      <c r="AV3" s="204"/>
+      <c r="AW3" s="204"/>
+      <c r="AX3" s="204"/>
+      <c r="AY3" s="204"/>
+      <c r="AZ3" s="204"/>
+      <c r="BA3" s="204"/>
+      <c r="BB3" s="204"/>
+      <c r="BC3" s="204"/>
+      <c r="BD3" s="204"/>
+      <c r="BE3" s="205"/>
+      <c r="BF3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(BF4)</f>
         <v>Woche 25</v>
       </c>
-      <c r="BG3" s="198"/>
-      <c r="BH3" s="198"/>
-      <c r="BI3" s="198"/>
-      <c r="BJ3" s="198"/>
-      <c r="BK3" s="198"/>
-      <c r="BL3" s="198"/>
-      <c r="BM3" s="198"/>
-      <c r="BN3" s="198"/>
-      <c r="BO3" s="198"/>
-      <c r="BP3" s="198"/>
-      <c r="BQ3" s="198"/>
-      <c r="BR3" s="198"/>
-      <c r="BS3" s="199"/>
+      <c r="BG3" s="204"/>
+      <c r="BH3" s="204"/>
+      <c r="BI3" s="204"/>
+      <c r="BJ3" s="204"/>
+      <c r="BK3" s="204"/>
+      <c r="BL3" s="204"/>
+      <c r="BM3" s="204"/>
+      <c r="BN3" s="204"/>
+      <c r="BO3" s="204"/>
+      <c r="BP3" s="204"/>
+      <c r="BQ3" s="204"/>
+      <c r="BR3" s="204"/>
+      <c r="BS3" s="205"/>
     </row>
     <row r="4" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="206">
+      <c r="B4" s="212">
         <f>B1</f>
         <v>46160</v>
       </c>
-      <c r="C4" s="207"/>
-      <c r="D4" s="206">
+      <c r="C4" s="213"/>
+      <c r="D4" s="212">
         <f>B4+1</f>
         <v>46161</v>
       </c>
-      <c r="E4" s="207"/>
-      <c r="F4" s="206">
+      <c r="E4" s="213"/>
+      <c r="F4" s="212">
         <f>D4+1</f>
         <v>46162</v>
       </c>
-      <c r="G4" s="207"/>
-      <c r="H4" s="206">
+      <c r="G4" s="213"/>
+      <c r="H4" s="212">
         <f>F4+1</f>
         <v>46163</v>
       </c>
-      <c r="I4" s="207"/>
-      <c r="J4" s="206">
+      <c r="I4" s="213"/>
+      <c r="J4" s="212">
         <f>H4+1</f>
         <v>46164</v>
       </c>
-      <c r="K4" s="207"/>
-      <c r="L4" s="206">
+      <c r="K4" s="213"/>
+      <c r="L4" s="212">
         <f>J4+1</f>
         <v>46165</v>
       </c>
-      <c r="M4" s="207"/>
-      <c r="N4" s="206">
+      <c r="M4" s="213"/>
+      <c r="N4" s="212">
         <f>L4+1</f>
         <v>46166</v>
       </c>
-      <c r="O4" s="207"/>
-      <c r="P4" s="206">
+      <c r="O4" s="213"/>
+      <c r="P4" s="212">
         <f>N4+1</f>
         <v>46167</v>
       </c>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="206">
+      <c r="Q4" s="213"/>
+      <c r="R4" s="212">
         <f>P4+1</f>
         <v>46168</v>
       </c>
-      <c r="S4" s="207"/>
-      <c r="T4" s="206">
+      <c r="S4" s="213"/>
+      <c r="T4" s="212">
         <f>R4+1</f>
         <v>46169</v>
       </c>
-      <c r="U4" s="207"/>
-      <c r="V4" s="206">
+      <c r="U4" s="213"/>
+      <c r="V4" s="212">
         <f>T4+1</f>
         <v>46170</v>
       </c>
-      <c r="W4" s="207"/>
-      <c r="X4" s="206">
+      <c r="W4" s="213"/>
+      <c r="X4" s="212">
         <f>V4+1</f>
         <v>46171</v>
       </c>
-      <c r="Y4" s="207"/>
-      <c r="Z4" s="206">
+      <c r="Y4" s="213"/>
+      <c r="Z4" s="212">
         <f>X4+1</f>
         <v>46172</v>
       </c>
-      <c r="AA4" s="207"/>
-      <c r="AB4" s="220">
+      <c r="AA4" s="213"/>
+      <c r="AB4" s="226">
         <f>Z4+1</f>
         <v>46173</v>
       </c>
-      <c r="AC4" s="207"/>
-      <c r="AD4" s="220">
+      <c r="AC4" s="213"/>
+      <c r="AD4" s="226">
         <f>AB4+1</f>
         <v>46174</v>
       </c>
-      <c r="AE4" s="207"/>
-      <c r="AF4" s="206">
+      <c r="AE4" s="213"/>
+      <c r="AF4" s="212">
         <f>AD4+1</f>
         <v>46175</v>
       </c>
-      <c r="AG4" s="207"/>
-      <c r="AH4" s="206">
+      <c r="AG4" s="213"/>
+      <c r="AH4" s="212">
         <f>AF4+1</f>
         <v>46176</v>
       </c>
-      <c r="AI4" s="207"/>
-      <c r="AJ4" s="206">
+      <c r="AI4" s="213"/>
+      <c r="AJ4" s="212">
         <f>AH4+1</f>
         <v>46177</v>
       </c>
-      <c r="AK4" s="207"/>
-      <c r="AL4" s="206">
+      <c r="AK4" s="213"/>
+      <c r="AL4" s="212">
         <f>AJ4+1</f>
         <v>46178</v>
       </c>
-      <c r="AM4" s="207"/>
-      <c r="AN4" s="206">
+      <c r="AM4" s="213"/>
+      <c r="AN4" s="212">
         <f>AL4+1</f>
         <v>46179</v>
       </c>
-      <c r="AO4" s="207"/>
-      <c r="AP4" s="206">
+      <c r="AO4" s="213"/>
+      <c r="AP4" s="212">
         <f>AN4+1</f>
         <v>46180</v>
       </c>
-      <c r="AQ4" s="207"/>
-      <c r="AR4" s="206">
+      <c r="AQ4" s="213"/>
+      <c r="AR4" s="212">
         <f>AP4+1</f>
         <v>46181</v>
       </c>
-      <c r="AS4" s="207"/>
-      <c r="AT4" s="206">
+      <c r="AS4" s="213"/>
+      <c r="AT4" s="212">
         <f>AR4+1</f>
         <v>46182</v>
       </c>
-      <c r="AU4" s="207"/>
-      <c r="AV4" s="206">
+      <c r="AU4" s="213"/>
+      <c r="AV4" s="212">
         <f>AT4+1</f>
         <v>46183</v>
       </c>
-      <c r="AW4" s="207"/>
-      <c r="AX4" s="206">
+      <c r="AW4" s="213"/>
+      <c r="AX4" s="212">
         <f>AV4+1</f>
         <v>46184</v>
       </c>
-      <c r="AY4" s="207"/>
-      <c r="AZ4" s="206">
+      <c r="AY4" s="213"/>
+      <c r="AZ4" s="212">
         <f>AX4+1</f>
         <v>46185</v>
       </c>
-      <c r="BA4" s="207"/>
-      <c r="BB4" s="206">
+      <c r="BA4" s="213"/>
+      <c r="BB4" s="212">
         <f>AZ4+1</f>
         <v>46186</v>
       </c>
-      <c r="BC4" s="207"/>
-      <c r="BD4" s="206">
+      <c r="BC4" s="213"/>
+      <c r="BD4" s="212">
         <f>BB4+1</f>
         <v>46187</v>
       </c>
-      <c r="BE4" s="207"/>
-      <c r="BF4" s="206">
+      <c r="BE4" s="213"/>
+      <c r="BF4" s="212">
         <f>BD4+1</f>
         <v>46188</v>
       </c>
-      <c r="BG4" s="207"/>
-      <c r="BH4" s="206">
+      <c r="BG4" s="213"/>
+      <c r="BH4" s="212">
         <f>BF4+1</f>
         <v>46189</v>
       </c>
-      <c r="BI4" s="207"/>
-      <c r="BJ4" s="206">
+      <c r="BI4" s="213"/>
+      <c r="BJ4" s="212">
         <f>BH4+1</f>
         <v>46190</v>
       </c>
-      <c r="BK4" s="207"/>
-      <c r="BL4" s="206">
+      <c r="BK4" s="213"/>
+      <c r="BL4" s="212">
         <f>BJ4+1</f>
         <v>46191</v>
       </c>
-      <c r="BM4" s="207"/>
-      <c r="BN4" s="206">
+      <c r="BM4" s="213"/>
+      <c r="BN4" s="212">
         <f>BL4+1</f>
         <v>46192</v>
       </c>
-      <c r="BO4" s="207"/>
-      <c r="BP4" s="206">
+      <c r="BO4" s="213"/>
+      <c r="BP4" s="212">
         <f>BN4+1</f>
         <v>46193</v>
       </c>
-      <c r="BQ4" s="207"/>
-      <c r="BR4" s="206">
+      <c r="BQ4" s="213"/>
+      <c r="BR4" s="212">
         <f>BP4+1</f>
         <v>46194</v>
       </c>
-      <c r="BS4" s="207"/>
+      <c r="BS4" s="213"/>
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A5" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="230" t="s">
+      <c r="B5" s="236" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="196"/>
-      <c r="D5" s="195" t="s">
+      <c r="C5" s="202"/>
+      <c r="D5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="196"/>
-      <c r="F5" s="195" t="s">
+      <c r="E5" s="202"/>
+      <c r="F5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="196"/>
-      <c r="H5" s="195" t="s">
+      <c r="G5" s="202"/>
+      <c r="H5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="196"/>
-      <c r="J5" s="195" t="s">
+      <c r="I5" s="202"/>
+      <c r="J5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="196"/>
-      <c r="L5" s="195" t="s">
+      <c r="K5" s="202"/>
+      <c r="L5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="196"/>
-      <c r="N5" s="195" t="s">
+      <c r="M5" s="202"/>
+      <c r="N5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="196"/>
-      <c r="P5" s="202" t="s">
+      <c r="O5" s="202"/>
+      <c r="P5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="196"/>
-      <c r="R5" s="195" t="s">
+      <c r="Q5" s="202"/>
+      <c r="R5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="S5" s="196"/>
-      <c r="T5" s="195" t="s">
+      <c r="S5" s="202"/>
+      <c r="T5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="U5" s="196"/>
-      <c r="V5" s="195" t="s">
+      <c r="U5" s="202"/>
+      <c r="V5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="196"/>
-      <c r="X5" s="195" t="s">
+      <c r="W5" s="202"/>
+      <c r="X5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="Y5" s="196"/>
-      <c r="Z5" s="195" t="s">
+      <c r="Y5" s="202"/>
+      <c r="Z5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="AA5" s="196"/>
-      <c r="AB5" s="195" t="s">
+      <c r="AA5" s="202"/>
+      <c r="AB5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AC5" s="196"/>
-      <c r="AD5" s="202" t="s">
+      <c r="AC5" s="202"/>
+      <c r="AD5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="AE5" s="196"/>
-      <c r="AF5" s="195" t="s">
+      <c r="AE5" s="202"/>
+      <c r="AF5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="AG5" s="196"/>
-      <c r="AH5" s="195" t="s">
+      <c r="AG5" s="202"/>
+      <c r="AH5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="AI5" s="196"/>
-      <c r="AJ5" s="195" t="s">
+      <c r="AI5" s="202"/>
+      <c r="AJ5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="AK5" s="196"/>
-      <c r="AL5" s="195" t="s">
+      <c r="AK5" s="202"/>
+      <c r="AL5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="AM5" s="196"/>
-      <c r="AN5" s="195" t="s">
+      <c r="AM5" s="202"/>
+      <c r="AN5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="AO5" s="196"/>
-      <c r="AP5" s="195" t="s">
+      <c r="AO5" s="202"/>
+      <c r="AP5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AQ5" s="196"/>
-      <c r="AR5" s="202" t="s">
+      <c r="AQ5" s="202"/>
+      <c r="AR5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="AS5" s="196"/>
-      <c r="AT5" s="195" t="s">
+      <c r="AS5" s="202"/>
+      <c r="AT5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="AU5" s="196"/>
-      <c r="AV5" s="195" t="s">
+      <c r="AU5" s="202"/>
+      <c r="AV5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="AW5" s="196"/>
-      <c r="AX5" s="195" t="s">
+      <c r="AW5" s="202"/>
+      <c r="AX5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="AY5" s="196"/>
-      <c r="AZ5" s="195" t="s">
+      <c r="AY5" s="202"/>
+      <c r="AZ5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="BA5" s="196"/>
-      <c r="BB5" s="195" t="s">
+      <c r="BA5" s="202"/>
+      <c r="BB5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="BC5" s="196"/>
-      <c r="BD5" s="195" t="s">
+      <c r="BC5" s="202"/>
+      <c r="BD5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="BE5" s="196"/>
-      <c r="BF5" s="202" t="s">
+      <c r="BE5" s="202"/>
+      <c r="BF5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="BG5" s="196"/>
-      <c r="BH5" s="195" t="s">
+      <c r="BG5" s="202"/>
+      <c r="BH5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="BI5" s="196"/>
-      <c r="BJ5" s="195" t="s">
+      <c r="BI5" s="202"/>
+      <c r="BJ5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="BK5" s="196"/>
-      <c r="BL5" s="195" t="s">
+      <c r="BK5" s="202"/>
+      <c r="BL5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="BM5" s="196"/>
-      <c r="BN5" s="195" t="s">
+      <c r="BM5" s="202"/>
+      <c r="BN5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="BO5" s="196"/>
-      <c r="BP5" s="195" t="s">
+      <c r="BO5" s="202"/>
+      <c r="BP5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="BQ5" s="196"/>
-      <c r="BR5" s="195" t="s">
+      <c r="BQ5" s="202"/>
+      <c r="BR5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="BS5" s="196"/>
+      <c r="BS5" s="202"/>
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
@@ -22368,740 +22392,740 @@
       <c r="A122" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B122" s="203">
+      <c r="B122" s="209">
         <v>22</v>
       </c>
-      <c r="C122" s="194"/>
-      <c r="D122" s="193">
+      <c r="C122" s="200"/>
+      <c r="D122" s="199">
         <v>22</v>
       </c>
-      <c r="E122" s="194"/>
-      <c r="F122" s="193">
+      <c r="E122" s="200"/>
+      <c r="F122" s="199">
         <v>22</v>
       </c>
-      <c r="G122" s="194"/>
-      <c r="H122" s="193">
+      <c r="G122" s="200"/>
+      <c r="H122" s="199">
         <v>22</v>
       </c>
-      <c r="I122" s="194"/>
-      <c r="J122" s="193">
+      <c r="I122" s="200"/>
+      <c r="J122" s="199">
         <v>22</v>
       </c>
-      <c r="K122" s="194"/>
-      <c r="L122" s="193">
+      <c r="K122" s="200"/>
+      <c r="L122" s="199">
         <v>0</v>
       </c>
-      <c r="M122" s="194"/>
-      <c r="N122" s="193">
+      <c r="M122" s="200"/>
+      <c r="N122" s="199">
         <v>0</v>
       </c>
-      <c r="O122" s="194"/>
-      <c r="P122" s="203">
+      <c r="O122" s="200"/>
+      <c r="P122" s="209">
         <v>22</v>
       </c>
-      <c r="Q122" s="194"/>
-      <c r="R122" s="193">
+      <c r="Q122" s="200"/>
+      <c r="R122" s="199">
         <v>22</v>
       </c>
-      <c r="S122" s="194"/>
-      <c r="T122" s="193">
+      <c r="S122" s="200"/>
+      <c r="T122" s="199">
         <v>22</v>
       </c>
-      <c r="U122" s="194"/>
-      <c r="V122" s="193">
+      <c r="U122" s="200"/>
+      <c r="V122" s="199">
         <v>22</v>
       </c>
-      <c r="W122" s="194"/>
-      <c r="X122" s="193">
+      <c r="W122" s="200"/>
+      <c r="X122" s="199">
         <v>22</v>
       </c>
-      <c r="Y122" s="194"/>
-      <c r="Z122" s="193">
+      <c r="Y122" s="200"/>
+      <c r="Z122" s="199">
         <v>0</v>
       </c>
-      <c r="AA122" s="194"/>
-      <c r="AB122" s="193">
+      <c r="AA122" s="200"/>
+      <c r="AB122" s="199">
         <v>0</v>
       </c>
-      <c r="AC122" s="194"/>
-      <c r="AD122" s="203">
+      <c r="AC122" s="200"/>
+      <c r="AD122" s="209">
         <v>22</v>
       </c>
-      <c r="AE122" s="194"/>
-      <c r="AF122" s="193">
+      <c r="AE122" s="200"/>
+      <c r="AF122" s="199">
         <v>22</v>
       </c>
-      <c r="AG122" s="194"/>
-      <c r="AH122" s="193">
+      <c r="AG122" s="200"/>
+      <c r="AH122" s="199">
         <v>22</v>
       </c>
-      <c r="AI122" s="194"/>
-      <c r="AJ122" s="193">
+      <c r="AI122" s="200"/>
+      <c r="AJ122" s="199">
         <v>22</v>
       </c>
-      <c r="AK122" s="194"/>
-      <c r="AL122" s="193">
+      <c r="AK122" s="200"/>
+      <c r="AL122" s="199">
         <v>22</v>
       </c>
-      <c r="AM122" s="194"/>
-      <c r="AN122" s="193">
+      <c r="AM122" s="200"/>
+      <c r="AN122" s="199">
         <v>0</v>
       </c>
-      <c r="AO122" s="194"/>
-      <c r="AP122" s="193">
+      <c r="AO122" s="200"/>
+      <c r="AP122" s="199">
         <v>0</v>
       </c>
-      <c r="AQ122" s="194"/>
-      <c r="AR122" s="203">
+      <c r="AQ122" s="200"/>
+      <c r="AR122" s="209">
         <v>22</v>
       </c>
-      <c r="AS122" s="194"/>
-      <c r="AT122" s="193">
+      <c r="AS122" s="200"/>
+      <c r="AT122" s="199">
         <v>22</v>
       </c>
-      <c r="AU122" s="194"/>
-      <c r="AV122" s="193">
+      <c r="AU122" s="200"/>
+      <c r="AV122" s="199">
         <v>22</v>
       </c>
-      <c r="AW122" s="194"/>
-      <c r="AX122" s="193">
+      <c r="AW122" s="200"/>
+      <c r="AX122" s="199">
         <v>22</v>
       </c>
-      <c r="AY122" s="194"/>
-      <c r="AZ122" s="193">
+      <c r="AY122" s="200"/>
+      <c r="AZ122" s="199">
         <v>22</v>
       </c>
-      <c r="BA122" s="194"/>
-      <c r="BB122" s="193">
+      <c r="BA122" s="200"/>
+      <c r="BB122" s="199">
         <v>0</v>
       </c>
-      <c r="BC122" s="194"/>
-      <c r="BD122" s="193">
+      <c r="BC122" s="200"/>
+      <c r="BD122" s="199">
         <v>0</v>
       </c>
-      <c r="BE122" s="194"/>
-      <c r="BF122" s="203">
+      <c r="BE122" s="200"/>
+      <c r="BF122" s="209">
         <v>22</v>
       </c>
-      <c r="BG122" s="194"/>
-      <c r="BH122" s="193">
+      <c r="BG122" s="200"/>
+      <c r="BH122" s="199">
         <v>22</v>
       </c>
-      <c r="BI122" s="194"/>
-      <c r="BJ122" s="193">
+      <c r="BI122" s="200"/>
+      <c r="BJ122" s="199">
         <v>22</v>
       </c>
-      <c r="BK122" s="194"/>
-      <c r="BL122" s="193">
+      <c r="BK122" s="200"/>
+      <c r="BL122" s="199">
         <v>22</v>
       </c>
-      <c r="BM122" s="194"/>
-      <c r="BN122" s="193">
+      <c r="BM122" s="200"/>
+      <c r="BN122" s="199">
         <v>22</v>
       </c>
-      <c r="BO122" s="194"/>
-      <c r="BP122" s="193">
+      <c r="BO122" s="200"/>
+      <c r="BP122" s="199">
         <v>0</v>
       </c>
-      <c r="BQ122" s="194"/>
-      <c r="BR122" s="193">
+      <c r="BQ122" s="200"/>
+      <c r="BR122" s="199">
         <v>0</v>
       </c>
-      <c r="BS122" s="194"/>
+      <c r="BS122" s="200"/>
     </row>
     <row r="123" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B123" s="208"/>
-      <c r="C123" s="198"/>
-      <c r="D123" s="198"/>
-      <c r="E123" s="198"/>
-      <c r="F123" s="198"/>
-      <c r="G123" s="198"/>
-      <c r="H123" s="198"/>
-      <c r="I123" s="198"/>
-      <c r="J123" s="198"/>
-      <c r="K123" s="198"/>
-      <c r="L123" s="198"/>
-      <c r="M123" s="198"/>
-      <c r="N123" s="198"/>
-      <c r="O123" s="209"/>
-      <c r="P123" s="208"/>
-      <c r="Q123" s="198"/>
-      <c r="R123" s="198"/>
-      <c r="S123" s="198"/>
-      <c r="T123" s="198"/>
-      <c r="U123" s="198"/>
-      <c r="V123" s="198"/>
-      <c r="W123" s="198"/>
-      <c r="X123" s="198"/>
-      <c r="Y123" s="198"/>
-      <c r="Z123" s="198"/>
-      <c r="AA123" s="198"/>
-      <c r="AB123" s="198"/>
-      <c r="AC123" s="209"/>
-      <c r="AD123" s="208"/>
-      <c r="AE123" s="198"/>
-      <c r="AF123" s="198"/>
-      <c r="AG123" s="198"/>
-      <c r="AH123" s="198"/>
-      <c r="AI123" s="198"/>
-      <c r="AJ123" s="198"/>
-      <c r="AK123" s="198"/>
-      <c r="AL123" s="198"/>
-      <c r="AM123" s="198"/>
-      <c r="AN123" s="198"/>
-      <c r="AO123" s="198"/>
-      <c r="AP123" s="198"/>
-      <c r="AQ123" s="209"/>
-      <c r="AR123" s="208"/>
-      <c r="AS123" s="198"/>
-      <c r="AT123" s="198"/>
-      <c r="AU123" s="198"/>
-      <c r="AV123" s="198"/>
-      <c r="AW123" s="198"/>
-      <c r="AX123" s="198"/>
-      <c r="AY123" s="198"/>
-      <c r="AZ123" s="198"/>
-      <c r="BA123" s="198"/>
-      <c r="BB123" s="198"/>
-      <c r="BC123" s="198"/>
-      <c r="BD123" s="198"/>
-      <c r="BE123" s="209"/>
-      <c r="BF123" s="208"/>
-      <c r="BG123" s="198"/>
-      <c r="BH123" s="198"/>
-      <c r="BI123" s="198"/>
-      <c r="BJ123" s="198"/>
-      <c r="BK123" s="198"/>
-      <c r="BL123" s="198"/>
-      <c r="BM123" s="198"/>
-      <c r="BN123" s="198"/>
-      <c r="BO123" s="198"/>
-      <c r="BP123" s="198"/>
-      <c r="BQ123" s="198"/>
-      <c r="BR123" s="198"/>
-      <c r="BS123" s="209"/>
+      <c r="B123" s="214"/>
+      <c r="C123" s="204"/>
+      <c r="D123" s="204"/>
+      <c r="E123" s="204"/>
+      <c r="F123" s="204"/>
+      <c r="G123" s="204"/>
+      <c r="H123" s="204"/>
+      <c r="I123" s="204"/>
+      <c r="J123" s="204"/>
+      <c r="K123" s="204"/>
+      <c r="L123" s="204"/>
+      <c r="M123" s="204"/>
+      <c r="N123" s="204"/>
+      <c r="O123" s="215"/>
+      <c r="P123" s="214"/>
+      <c r="Q123" s="204"/>
+      <c r="R123" s="204"/>
+      <c r="S123" s="204"/>
+      <c r="T123" s="204"/>
+      <c r="U123" s="204"/>
+      <c r="V123" s="204"/>
+      <c r="W123" s="204"/>
+      <c r="X123" s="204"/>
+      <c r="Y123" s="204"/>
+      <c r="Z123" s="204"/>
+      <c r="AA123" s="204"/>
+      <c r="AB123" s="204"/>
+      <c r="AC123" s="215"/>
+      <c r="AD123" s="214"/>
+      <c r="AE123" s="204"/>
+      <c r="AF123" s="204"/>
+      <c r="AG123" s="204"/>
+      <c r="AH123" s="204"/>
+      <c r="AI123" s="204"/>
+      <c r="AJ123" s="204"/>
+      <c r="AK123" s="204"/>
+      <c r="AL123" s="204"/>
+      <c r="AM123" s="204"/>
+      <c r="AN123" s="204"/>
+      <c r="AO123" s="204"/>
+      <c r="AP123" s="204"/>
+      <c r="AQ123" s="215"/>
+      <c r="AR123" s="214"/>
+      <c r="AS123" s="204"/>
+      <c r="AT123" s="204"/>
+      <c r="AU123" s="204"/>
+      <c r="AV123" s="204"/>
+      <c r="AW123" s="204"/>
+      <c r="AX123" s="204"/>
+      <c r="AY123" s="204"/>
+      <c r="AZ123" s="204"/>
+      <c r="BA123" s="204"/>
+      <c r="BB123" s="204"/>
+      <c r="BC123" s="204"/>
+      <c r="BD123" s="204"/>
+      <c r="BE123" s="215"/>
+      <c r="BF123" s="214"/>
+      <c r="BG123" s="204"/>
+      <c r="BH123" s="204"/>
+      <c r="BI123" s="204"/>
+      <c r="BJ123" s="204"/>
+      <c r="BK123" s="204"/>
+      <c r="BL123" s="204"/>
+      <c r="BM123" s="204"/>
+      <c r="BN123" s="204"/>
+      <c r="BO123" s="204"/>
+      <c r="BP123" s="204"/>
+      <c r="BQ123" s="204"/>
+      <c r="BR123" s="204"/>
+      <c r="BS123" s="215"/>
     </row>
     <row r="124" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="227"/>
-      <c r="B124" s="233" t="s">
+      <c r="A124" s="233"/>
+      <c r="B124" s="239" t="s">
         <v>203</v>
       </c>
-      <c r="C124" s="211"/>
-      <c r="D124" s="211"/>
-      <c r="E124" s="211"/>
-      <c r="F124" s="211"/>
-      <c r="G124" s="211"/>
-      <c r="H124" s="211"/>
-      <c r="I124" s="211"/>
-      <c r="J124" s="211"/>
-      <c r="K124" s="211"/>
-      <c r="L124" s="211"/>
-      <c r="M124" s="211"/>
-      <c r="N124" s="211"/>
-      <c r="O124" s="212"/>
-      <c r="P124" s="233" t="s">
+      <c r="C124" s="217"/>
+      <c r="D124" s="217"/>
+      <c r="E124" s="217"/>
+      <c r="F124" s="217"/>
+      <c r="G124" s="217"/>
+      <c r="H124" s="217"/>
+      <c r="I124" s="217"/>
+      <c r="J124" s="217"/>
+      <c r="K124" s="217"/>
+      <c r="L124" s="217"/>
+      <c r="M124" s="217"/>
+      <c r="N124" s="217"/>
+      <c r="O124" s="218"/>
+      <c r="P124" s="239" t="s">
         <v>204</v>
       </c>
-      <c r="Q124" s="211"/>
-      <c r="R124" s="211"/>
-      <c r="S124" s="211"/>
-      <c r="T124" s="211"/>
-      <c r="U124" s="211"/>
-      <c r="V124" s="211"/>
-      <c r="W124" s="211"/>
-      <c r="X124" s="211"/>
-      <c r="Y124" s="211"/>
-      <c r="Z124" s="211"/>
-      <c r="AA124" s="211"/>
-      <c r="AB124" s="211"/>
-      <c r="AC124" s="212"/>
-      <c r="AD124" s="233"/>
-      <c r="AE124" s="211"/>
-      <c r="AF124" s="211"/>
-      <c r="AG124" s="211"/>
-      <c r="AH124" s="211"/>
-      <c r="AI124" s="211"/>
-      <c r="AJ124" s="211"/>
-      <c r="AK124" s="211"/>
-      <c r="AL124" s="211"/>
-      <c r="AM124" s="211"/>
-      <c r="AN124" s="211"/>
-      <c r="AO124" s="211"/>
-      <c r="AP124" s="211"/>
-      <c r="AQ124" s="212"/>
-      <c r="AR124" s="233" t="s">
+      <c r="Q124" s="217"/>
+      <c r="R124" s="217"/>
+      <c r="S124" s="217"/>
+      <c r="T124" s="217"/>
+      <c r="U124" s="217"/>
+      <c r="V124" s="217"/>
+      <c r="W124" s="217"/>
+      <c r="X124" s="217"/>
+      <c r="Y124" s="217"/>
+      <c r="Z124" s="217"/>
+      <c r="AA124" s="217"/>
+      <c r="AB124" s="217"/>
+      <c r="AC124" s="218"/>
+      <c r="AD124" s="239"/>
+      <c r="AE124" s="217"/>
+      <c r="AF124" s="217"/>
+      <c r="AG124" s="217"/>
+      <c r="AH124" s="217"/>
+      <c r="AI124" s="217"/>
+      <c r="AJ124" s="217"/>
+      <c r="AK124" s="217"/>
+      <c r="AL124" s="217"/>
+      <c r="AM124" s="217"/>
+      <c r="AN124" s="217"/>
+      <c r="AO124" s="217"/>
+      <c r="AP124" s="217"/>
+      <c r="AQ124" s="218"/>
+      <c r="AR124" s="239" t="s">
         <v>205</v>
       </c>
-      <c r="AS124" s="211"/>
-      <c r="AT124" s="211"/>
-      <c r="AU124" s="211"/>
-      <c r="AV124" s="211"/>
-      <c r="AW124" s="211"/>
-      <c r="AX124" s="211"/>
-      <c r="AY124" s="211"/>
-      <c r="AZ124" s="211"/>
-      <c r="BA124" s="211"/>
-      <c r="BB124" s="211"/>
-      <c r="BC124" s="211"/>
-      <c r="BD124" s="211"/>
-      <c r="BE124" s="212"/>
-      <c r="BF124" s="233" t="s">
+      <c r="AS124" s="217"/>
+      <c r="AT124" s="217"/>
+      <c r="AU124" s="217"/>
+      <c r="AV124" s="217"/>
+      <c r="AW124" s="217"/>
+      <c r="AX124" s="217"/>
+      <c r="AY124" s="217"/>
+      <c r="AZ124" s="217"/>
+      <c r="BA124" s="217"/>
+      <c r="BB124" s="217"/>
+      <c r="BC124" s="217"/>
+      <c r="BD124" s="217"/>
+      <c r="BE124" s="218"/>
+      <c r="BF124" s="239" t="s">
         <v>205</v>
       </c>
-      <c r="BG124" s="211"/>
-      <c r="BH124" s="211"/>
-      <c r="BI124" s="211"/>
-      <c r="BJ124" s="211"/>
-      <c r="BK124" s="211"/>
-      <c r="BL124" s="211"/>
-      <c r="BM124" s="211"/>
-      <c r="BN124" s="211"/>
-      <c r="BO124" s="211"/>
-      <c r="BP124" s="211"/>
-      <c r="BQ124" s="211"/>
-      <c r="BR124" s="211"/>
-      <c r="BS124" s="212"/>
+      <c r="BG124" s="217"/>
+      <c r="BH124" s="217"/>
+      <c r="BI124" s="217"/>
+      <c r="BJ124" s="217"/>
+      <c r="BK124" s="217"/>
+      <c r="BL124" s="217"/>
+      <c r="BM124" s="217"/>
+      <c r="BN124" s="217"/>
+      <c r="BO124" s="217"/>
+      <c r="BP124" s="217"/>
+      <c r="BQ124" s="217"/>
+      <c r="BR124" s="217"/>
+      <c r="BS124" s="218"/>
     </row>
     <row r="125" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A125" s="228"/>
-      <c r="B125" s="213"/>
-      <c r="C125" s="214"/>
-      <c r="D125" s="214"/>
-      <c r="E125" s="214"/>
-      <c r="F125" s="214"/>
-      <c r="G125" s="214"/>
-      <c r="H125" s="214"/>
-      <c r="I125" s="214"/>
-      <c r="J125" s="214"/>
-      <c r="K125" s="214"/>
-      <c r="L125" s="214"/>
-      <c r="M125" s="214"/>
-      <c r="N125" s="214"/>
-      <c r="O125" s="215"/>
-      <c r="P125" s="213"/>
-      <c r="Q125" s="214"/>
-      <c r="R125" s="214"/>
-      <c r="S125" s="214"/>
-      <c r="T125" s="214"/>
-      <c r="U125" s="214"/>
-      <c r="V125" s="214"/>
-      <c r="W125" s="214"/>
-      <c r="X125" s="214"/>
-      <c r="Y125" s="214"/>
-      <c r="Z125" s="214"/>
-      <c r="AA125" s="214"/>
-      <c r="AB125" s="214"/>
-      <c r="AC125" s="215"/>
-      <c r="AD125" s="213"/>
-      <c r="AE125" s="214"/>
-      <c r="AF125" s="214"/>
-      <c r="AG125" s="214"/>
-      <c r="AH125" s="214"/>
-      <c r="AI125" s="214"/>
-      <c r="AJ125" s="214"/>
-      <c r="AK125" s="214"/>
-      <c r="AL125" s="214"/>
-      <c r="AM125" s="214"/>
-      <c r="AN125" s="214"/>
-      <c r="AO125" s="214"/>
-      <c r="AP125" s="214"/>
-      <c r="AQ125" s="215"/>
-      <c r="AR125" s="213"/>
-      <c r="AS125" s="214"/>
-      <c r="AT125" s="214"/>
-      <c r="AU125" s="214"/>
-      <c r="AV125" s="214"/>
-      <c r="AW125" s="214"/>
-      <c r="AX125" s="214"/>
-      <c r="AY125" s="214"/>
-      <c r="AZ125" s="214"/>
-      <c r="BA125" s="214"/>
-      <c r="BB125" s="214"/>
-      <c r="BC125" s="214"/>
-      <c r="BD125" s="214"/>
-      <c r="BE125" s="215"/>
-      <c r="BF125" s="213"/>
-      <c r="BG125" s="214"/>
-      <c r="BH125" s="214"/>
-      <c r="BI125" s="214"/>
-      <c r="BJ125" s="214"/>
-      <c r="BK125" s="214"/>
-      <c r="BL125" s="214"/>
-      <c r="BM125" s="214"/>
-      <c r="BN125" s="214"/>
-      <c r="BO125" s="214"/>
-      <c r="BP125" s="214"/>
-      <c r="BQ125" s="214"/>
-      <c r="BR125" s="214"/>
-      <c r="BS125" s="215"/>
+      <c r="A125" s="234"/>
+      <c r="B125" s="219"/>
+      <c r="C125" s="220"/>
+      <c r="D125" s="220"/>
+      <c r="E125" s="220"/>
+      <c r="F125" s="220"/>
+      <c r="G125" s="220"/>
+      <c r="H125" s="220"/>
+      <c r="I125" s="220"/>
+      <c r="J125" s="220"/>
+      <c r="K125" s="220"/>
+      <c r="L125" s="220"/>
+      <c r="M125" s="220"/>
+      <c r="N125" s="220"/>
+      <c r="O125" s="221"/>
+      <c r="P125" s="219"/>
+      <c r="Q125" s="220"/>
+      <c r="R125" s="220"/>
+      <c r="S125" s="220"/>
+      <c r="T125" s="220"/>
+      <c r="U125" s="220"/>
+      <c r="V125" s="220"/>
+      <c r="W125" s="220"/>
+      <c r="X125" s="220"/>
+      <c r="Y125" s="220"/>
+      <c r="Z125" s="220"/>
+      <c r="AA125" s="220"/>
+      <c r="AB125" s="220"/>
+      <c r="AC125" s="221"/>
+      <c r="AD125" s="219"/>
+      <c r="AE125" s="220"/>
+      <c r="AF125" s="220"/>
+      <c r="AG125" s="220"/>
+      <c r="AH125" s="220"/>
+      <c r="AI125" s="220"/>
+      <c r="AJ125" s="220"/>
+      <c r="AK125" s="220"/>
+      <c r="AL125" s="220"/>
+      <c r="AM125" s="220"/>
+      <c r="AN125" s="220"/>
+      <c r="AO125" s="220"/>
+      <c r="AP125" s="220"/>
+      <c r="AQ125" s="221"/>
+      <c r="AR125" s="219"/>
+      <c r="AS125" s="220"/>
+      <c r="AT125" s="220"/>
+      <c r="AU125" s="220"/>
+      <c r="AV125" s="220"/>
+      <c r="AW125" s="220"/>
+      <c r="AX125" s="220"/>
+      <c r="AY125" s="220"/>
+      <c r="AZ125" s="220"/>
+      <c r="BA125" s="220"/>
+      <c r="BB125" s="220"/>
+      <c r="BC125" s="220"/>
+      <c r="BD125" s="220"/>
+      <c r="BE125" s="221"/>
+      <c r="BF125" s="219"/>
+      <c r="BG125" s="220"/>
+      <c r="BH125" s="220"/>
+      <c r="BI125" s="220"/>
+      <c r="BJ125" s="220"/>
+      <c r="BK125" s="220"/>
+      <c r="BL125" s="220"/>
+      <c r="BM125" s="220"/>
+      <c r="BN125" s="220"/>
+      <c r="BO125" s="220"/>
+      <c r="BP125" s="220"/>
+      <c r="BQ125" s="220"/>
+      <c r="BR125" s="220"/>
+      <c r="BS125" s="221"/>
     </row>
     <row r="126" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A126" s="228"/>
-      <c r="B126" s="213"/>
-      <c r="C126" s="214"/>
-      <c r="D126" s="214"/>
-      <c r="E126" s="214"/>
-      <c r="F126" s="214"/>
-      <c r="G126" s="214"/>
-      <c r="H126" s="214"/>
-      <c r="I126" s="214"/>
-      <c r="J126" s="214"/>
-      <c r="K126" s="214"/>
-      <c r="L126" s="214"/>
-      <c r="M126" s="214"/>
-      <c r="N126" s="214"/>
-      <c r="O126" s="215"/>
-      <c r="P126" s="213"/>
-      <c r="Q126" s="214"/>
-      <c r="R126" s="214"/>
-      <c r="S126" s="214"/>
-      <c r="T126" s="214"/>
-      <c r="U126" s="214"/>
-      <c r="V126" s="214"/>
-      <c r="W126" s="214"/>
-      <c r="X126" s="214"/>
-      <c r="Y126" s="214"/>
-      <c r="Z126" s="214"/>
-      <c r="AA126" s="214"/>
-      <c r="AB126" s="214"/>
-      <c r="AC126" s="215"/>
-      <c r="AD126" s="213"/>
-      <c r="AE126" s="214"/>
-      <c r="AF126" s="214"/>
-      <c r="AG126" s="214"/>
-      <c r="AH126" s="214"/>
-      <c r="AI126" s="214"/>
-      <c r="AJ126" s="214"/>
-      <c r="AK126" s="214"/>
-      <c r="AL126" s="214"/>
-      <c r="AM126" s="214"/>
-      <c r="AN126" s="214"/>
-      <c r="AO126" s="214"/>
-      <c r="AP126" s="214"/>
-      <c r="AQ126" s="215"/>
-      <c r="AR126" s="213"/>
-      <c r="AS126" s="214"/>
-      <c r="AT126" s="214"/>
-      <c r="AU126" s="214"/>
-      <c r="AV126" s="214"/>
-      <c r="AW126" s="214"/>
-      <c r="AX126" s="214"/>
-      <c r="AY126" s="214"/>
-      <c r="AZ126" s="214"/>
-      <c r="BA126" s="214"/>
-      <c r="BB126" s="214"/>
-      <c r="BC126" s="214"/>
-      <c r="BD126" s="214"/>
-      <c r="BE126" s="215"/>
-      <c r="BF126" s="213"/>
-      <c r="BG126" s="214"/>
-      <c r="BH126" s="214"/>
-      <c r="BI126" s="214"/>
-      <c r="BJ126" s="214"/>
-      <c r="BK126" s="214"/>
-      <c r="BL126" s="214"/>
-      <c r="BM126" s="214"/>
-      <c r="BN126" s="214"/>
-      <c r="BO126" s="214"/>
-      <c r="BP126" s="214"/>
-      <c r="BQ126" s="214"/>
-      <c r="BR126" s="214"/>
-      <c r="BS126" s="215"/>
+      <c r="A126" s="234"/>
+      <c r="B126" s="219"/>
+      <c r="C126" s="220"/>
+      <c r="D126" s="220"/>
+      <c r="E126" s="220"/>
+      <c r="F126" s="220"/>
+      <c r="G126" s="220"/>
+      <c r="H126" s="220"/>
+      <c r="I126" s="220"/>
+      <c r="J126" s="220"/>
+      <c r="K126" s="220"/>
+      <c r="L126" s="220"/>
+      <c r="M126" s="220"/>
+      <c r="N126" s="220"/>
+      <c r="O126" s="221"/>
+      <c r="P126" s="219"/>
+      <c r="Q126" s="220"/>
+      <c r="R126" s="220"/>
+      <c r="S126" s="220"/>
+      <c r="T126" s="220"/>
+      <c r="U126" s="220"/>
+      <c r="V126" s="220"/>
+      <c r="W126" s="220"/>
+      <c r="X126" s="220"/>
+      <c r="Y126" s="220"/>
+      <c r="Z126" s="220"/>
+      <c r="AA126" s="220"/>
+      <c r="AB126" s="220"/>
+      <c r="AC126" s="221"/>
+      <c r="AD126" s="219"/>
+      <c r="AE126" s="220"/>
+      <c r="AF126" s="220"/>
+      <c r="AG126" s="220"/>
+      <c r="AH126" s="220"/>
+      <c r="AI126" s="220"/>
+      <c r="AJ126" s="220"/>
+      <c r="AK126" s="220"/>
+      <c r="AL126" s="220"/>
+      <c r="AM126" s="220"/>
+      <c r="AN126" s="220"/>
+      <c r="AO126" s="220"/>
+      <c r="AP126" s="220"/>
+      <c r="AQ126" s="221"/>
+      <c r="AR126" s="219"/>
+      <c r="AS126" s="220"/>
+      <c r="AT126" s="220"/>
+      <c r="AU126" s="220"/>
+      <c r="AV126" s="220"/>
+      <c r="AW126" s="220"/>
+      <c r="AX126" s="220"/>
+      <c r="AY126" s="220"/>
+      <c r="AZ126" s="220"/>
+      <c r="BA126" s="220"/>
+      <c r="BB126" s="220"/>
+      <c r="BC126" s="220"/>
+      <c r="BD126" s="220"/>
+      <c r="BE126" s="221"/>
+      <c r="BF126" s="219"/>
+      <c r="BG126" s="220"/>
+      <c r="BH126" s="220"/>
+      <c r="BI126" s="220"/>
+      <c r="BJ126" s="220"/>
+      <c r="BK126" s="220"/>
+      <c r="BL126" s="220"/>
+      <c r="BM126" s="220"/>
+      <c r="BN126" s="220"/>
+      <c r="BO126" s="220"/>
+      <c r="BP126" s="220"/>
+      <c r="BQ126" s="220"/>
+      <c r="BR126" s="220"/>
+      <c r="BS126" s="221"/>
     </row>
     <row r="127" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A127" s="228"/>
-      <c r="B127" s="213"/>
-      <c r="C127" s="214"/>
-      <c r="D127" s="214"/>
-      <c r="E127" s="214"/>
-      <c r="F127" s="214"/>
-      <c r="G127" s="214"/>
-      <c r="H127" s="214"/>
-      <c r="I127" s="214"/>
-      <c r="J127" s="214"/>
-      <c r="K127" s="214"/>
-      <c r="L127" s="214"/>
-      <c r="M127" s="214"/>
-      <c r="N127" s="214"/>
-      <c r="O127" s="215"/>
-      <c r="P127" s="213"/>
-      <c r="Q127" s="214"/>
-      <c r="R127" s="214"/>
-      <c r="S127" s="214"/>
-      <c r="T127" s="214"/>
-      <c r="U127" s="214"/>
-      <c r="V127" s="214"/>
-      <c r="W127" s="214"/>
-      <c r="X127" s="214"/>
-      <c r="Y127" s="214"/>
-      <c r="Z127" s="214"/>
-      <c r="AA127" s="214"/>
-      <c r="AB127" s="214"/>
-      <c r="AC127" s="215"/>
-      <c r="AD127" s="213"/>
-      <c r="AE127" s="214"/>
-      <c r="AF127" s="214"/>
-      <c r="AG127" s="214"/>
-      <c r="AH127" s="214"/>
-      <c r="AI127" s="214"/>
-      <c r="AJ127" s="214"/>
-      <c r="AK127" s="214"/>
-      <c r="AL127" s="214"/>
-      <c r="AM127" s="214"/>
-      <c r="AN127" s="214"/>
-      <c r="AO127" s="214"/>
-      <c r="AP127" s="214"/>
-      <c r="AQ127" s="215"/>
-      <c r="AR127" s="213"/>
-      <c r="AS127" s="214"/>
-      <c r="AT127" s="214"/>
-      <c r="AU127" s="214"/>
-      <c r="AV127" s="214"/>
-      <c r="AW127" s="214"/>
-      <c r="AX127" s="214"/>
-      <c r="AY127" s="214"/>
-      <c r="AZ127" s="214"/>
-      <c r="BA127" s="214"/>
-      <c r="BB127" s="214"/>
-      <c r="BC127" s="214"/>
-      <c r="BD127" s="214"/>
-      <c r="BE127" s="215"/>
-      <c r="BF127" s="213"/>
-      <c r="BG127" s="214"/>
-      <c r="BH127" s="214"/>
-      <c r="BI127" s="214"/>
-      <c r="BJ127" s="214"/>
-      <c r="BK127" s="214"/>
-      <c r="BL127" s="214"/>
-      <c r="BM127" s="214"/>
-      <c r="BN127" s="214"/>
-      <c r="BO127" s="214"/>
-      <c r="BP127" s="214"/>
-      <c r="BQ127" s="214"/>
-      <c r="BR127" s="214"/>
-      <c r="BS127" s="215"/>
+      <c r="A127" s="234"/>
+      <c r="B127" s="219"/>
+      <c r="C127" s="220"/>
+      <c r="D127" s="220"/>
+      <c r="E127" s="220"/>
+      <c r="F127" s="220"/>
+      <c r="G127" s="220"/>
+      <c r="H127" s="220"/>
+      <c r="I127" s="220"/>
+      <c r="J127" s="220"/>
+      <c r="K127" s="220"/>
+      <c r="L127" s="220"/>
+      <c r="M127" s="220"/>
+      <c r="N127" s="220"/>
+      <c r="O127" s="221"/>
+      <c r="P127" s="219"/>
+      <c r="Q127" s="220"/>
+      <c r="R127" s="220"/>
+      <c r="S127" s="220"/>
+      <c r="T127" s="220"/>
+      <c r="U127" s="220"/>
+      <c r="V127" s="220"/>
+      <c r="W127" s="220"/>
+      <c r="X127" s="220"/>
+      <c r="Y127" s="220"/>
+      <c r="Z127" s="220"/>
+      <c r="AA127" s="220"/>
+      <c r="AB127" s="220"/>
+      <c r="AC127" s="221"/>
+      <c r="AD127" s="219"/>
+      <c r="AE127" s="220"/>
+      <c r="AF127" s="220"/>
+      <c r="AG127" s="220"/>
+      <c r="AH127" s="220"/>
+      <c r="AI127" s="220"/>
+      <c r="AJ127" s="220"/>
+      <c r="AK127" s="220"/>
+      <c r="AL127" s="220"/>
+      <c r="AM127" s="220"/>
+      <c r="AN127" s="220"/>
+      <c r="AO127" s="220"/>
+      <c r="AP127" s="220"/>
+      <c r="AQ127" s="221"/>
+      <c r="AR127" s="219"/>
+      <c r="AS127" s="220"/>
+      <c r="AT127" s="220"/>
+      <c r="AU127" s="220"/>
+      <c r="AV127" s="220"/>
+      <c r="AW127" s="220"/>
+      <c r="AX127" s="220"/>
+      <c r="AY127" s="220"/>
+      <c r="AZ127" s="220"/>
+      <c r="BA127" s="220"/>
+      <c r="BB127" s="220"/>
+      <c r="BC127" s="220"/>
+      <c r="BD127" s="220"/>
+      <c r="BE127" s="221"/>
+      <c r="BF127" s="219"/>
+      <c r="BG127" s="220"/>
+      <c r="BH127" s="220"/>
+      <c r="BI127" s="220"/>
+      <c r="BJ127" s="220"/>
+      <c r="BK127" s="220"/>
+      <c r="BL127" s="220"/>
+      <c r="BM127" s="220"/>
+      <c r="BN127" s="220"/>
+      <c r="BO127" s="220"/>
+      <c r="BP127" s="220"/>
+      <c r="BQ127" s="220"/>
+      <c r="BR127" s="220"/>
+      <c r="BS127" s="221"/>
     </row>
     <row r="128" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A128" s="228"/>
-      <c r="B128" s="213"/>
-      <c r="C128" s="214"/>
-      <c r="D128" s="214"/>
-      <c r="E128" s="214"/>
-      <c r="F128" s="214"/>
-      <c r="G128" s="214"/>
-      <c r="H128" s="214"/>
-      <c r="I128" s="214"/>
-      <c r="J128" s="214"/>
-      <c r="K128" s="214"/>
-      <c r="L128" s="214"/>
-      <c r="M128" s="214"/>
-      <c r="N128" s="214"/>
-      <c r="O128" s="215"/>
-      <c r="P128" s="213"/>
-      <c r="Q128" s="214"/>
-      <c r="R128" s="214"/>
-      <c r="S128" s="214"/>
-      <c r="T128" s="214"/>
-      <c r="U128" s="214"/>
-      <c r="V128" s="214"/>
-      <c r="W128" s="214"/>
-      <c r="X128" s="214"/>
-      <c r="Y128" s="214"/>
-      <c r="Z128" s="214"/>
-      <c r="AA128" s="214"/>
-      <c r="AB128" s="214"/>
-      <c r="AC128" s="215"/>
-      <c r="AD128" s="213"/>
-      <c r="AE128" s="214"/>
-      <c r="AF128" s="214"/>
-      <c r="AG128" s="214"/>
-      <c r="AH128" s="214"/>
-      <c r="AI128" s="214"/>
-      <c r="AJ128" s="214"/>
-      <c r="AK128" s="214"/>
-      <c r="AL128" s="214"/>
-      <c r="AM128" s="214"/>
-      <c r="AN128" s="214"/>
-      <c r="AO128" s="214"/>
-      <c r="AP128" s="214"/>
-      <c r="AQ128" s="215"/>
-      <c r="AR128" s="213"/>
-      <c r="AS128" s="214"/>
-      <c r="AT128" s="214"/>
-      <c r="AU128" s="214"/>
-      <c r="AV128" s="214"/>
-      <c r="AW128" s="214"/>
-      <c r="AX128" s="214"/>
-      <c r="AY128" s="214"/>
-      <c r="AZ128" s="214"/>
-      <c r="BA128" s="214"/>
-      <c r="BB128" s="214"/>
-      <c r="BC128" s="214"/>
-      <c r="BD128" s="214"/>
-      <c r="BE128" s="215"/>
-      <c r="BF128" s="213"/>
-      <c r="BG128" s="214"/>
-      <c r="BH128" s="214"/>
-      <c r="BI128" s="214"/>
-      <c r="BJ128" s="214"/>
-      <c r="BK128" s="214"/>
-      <c r="BL128" s="214"/>
-      <c r="BM128" s="214"/>
-      <c r="BN128" s="214"/>
-      <c r="BO128" s="214"/>
-      <c r="BP128" s="214"/>
-      <c r="BQ128" s="214"/>
-      <c r="BR128" s="214"/>
-      <c r="BS128" s="215"/>
+      <c r="A128" s="234"/>
+      <c r="B128" s="219"/>
+      <c r="C128" s="220"/>
+      <c r="D128" s="220"/>
+      <c r="E128" s="220"/>
+      <c r="F128" s="220"/>
+      <c r="G128" s="220"/>
+      <c r="H128" s="220"/>
+      <c r="I128" s="220"/>
+      <c r="J128" s="220"/>
+      <c r="K128" s="220"/>
+      <c r="L128" s="220"/>
+      <c r="M128" s="220"/>
+      <c r="N128" s="220"/>
+      <c r="O128" s="221"/>
+      <c r="P128" s="219"/>
+      <c r="Q128" s="220"/>
+      <c r="R128" s="220"/>
+      <c r="S128" s="220"/>
+      <c r="T128" s="220"/>
+      <c r="U128" s="220"/>
+      <c r="V128" s="220"/>
+      <c r="W128" s="220"/>
+      <c r="X128" s="220"/>
+      <c r="Y128" s="220"/>
+      <c r="Z128" s="220"/>
+      <c r="AA128" s="220"/>
+      <c r="AB128" s="220"/>
+      <c r="AC128" s="221"/>
+      <c r="AD128" s="219"/>
+      <c r="AE128" s="220"/>
+      <c r="AF128" s="220"/>
+      <c r="AG128" s="220"/>
+      <c r="AH128" s="220"/>
+      <c r="AI128" s="220"/>
+      <c r="AJ128" s="220"/>
+      <c r="AK128" s="220"/>
+      <c r="AL128" s="220"/>
+      <c r="AM128" s="220"/>
+      <c r="AN128" s="220"/>
+      <c r="AO128" s="220"/>
+      <c r="AP128" s="220"/>
+      <c r="AQ128" s="221"/>
+      <c r="AR128" s="219"/>
+      <c r="AS128" s="220"/>
+      <c r="AT128" s="220"/>
+      <c r="AU128" s="220"/>
+      <c r="AV128" s="220"/>
+      <c r="AW128" s="220"/>
+      <c r="AX128" s="220"/>
+      <c r="AY128" s="220"/>
+      <c r="AZ128" s="220"/>
+      <c r="BA128" s="220"/>
+      <c r="BB128" s="220"/>
+      <c r="BC128" s="220"/>
+      <c r="BD128" s="220"/>
+      <c r="BE128" s="221"/>
+      <c r="BF128" s="219"/>
+      <c r="BG128" s="220"/>
+      <c r="BH128" s="220"/>
+      <c r="BI128" s="220"/>
+      <c r="BJ128" s="220"/>
+      <c r="BK128" s="220"/>
+      <c r="BL128" s="220"/>
+      <c r="BM128" s="220"/>
+      <c r="BN128" s="220"/>
+      <c r="BO128" s="220"/>
+      <c r="BP128" s="220"/>
+      <c r="BQ128" s="220"/>
+      <c r="BR128" s="220"/>
+      <c r="BS128" s="221"/>
     </row>
     <row r="129" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A129" s="228"/>
-      <c r="B129" s="213"/>
-      <c r="C129" s="214"/>
-      <c r="D129" s="214"/>
-      <c r="E129" s="214"/>
-      <c r="F129" s="214"/>
-      <c r="G129" s="214"/>
-      <c r="H129" s="214"/>
-      <c r="I129" s="214"/>
-      <c r="J129" s="214"/>
-      <c r="K129" s="214"/>
-      <c r="L129" s="214"/>
-      <c r="M129" s="214"/>
-      <c r="N129" s="214"/>
-      <c r="O129" s="215"/>
-      <c r="P129" s="213"/>
-      <c r="Q129" s="214"/>
-      <c r="R129" s="214"/>
-      <c r="S129" s="214"/>
-      <c r="T129" s="214"/>
-      <c r="U129" s="214"/>
-      <c r="V129" s="214"/>
-      <c r="W129" s="214"/>
-      <c r="X129" s="214"/>
-      <c r="Y129" s="214"/>
-      <c r="Z129" s="214"/>
-      <c r="AA129" s="214"/>
-      <c r="AB129" s="214"/>
-      <c r="AC129" s="215"/>
-      <c r="AD129" s="213"/>
-      <c r="AE129" s="214"/>
-      <c r="AF129" s="214"/>
-      <c r="AG129" s="214"/>
-      <c r="AH129" s="214"/>
-      <c r="AI129" s="214"/>
-      <c r="AJ129" s="214"/>
-      <c r="AK129" s="214"/>
-      <c r="AL129" s="214"/>
-      <c r="AM129" s="214"/>
-      <c r="AN129" s="214"/>
-      <c r="AO129" s="214"/>
-      <c r="AP129" s="214"/>
-      <c r="AQ129" s="215"/>
-      <c r="AR129" s="213"/>
-      <c r="AS129" s="214"/>
-      <c r="AT129" s="214"/>
-      <c r="AU129" s="214"/>
-      <c r="AV129" s="214"/>
-      <c r="AW129" s="214"/>
-      <c r="AX129" s="214"/>
-      <c r="AY129" s="214"/>
-      <c r="AZ129" s="214"/>
-      <c r="BA129" s="214"/>
-      <c r="BB129" s="214"/>
-      <c r="BC129" s="214"/>
-      <c r="BD129" s="214"/>
-      <c r="BE129" s="215"/>
-      <c r="BF129" s="213"/>
-      <c r="BG129" s="214"/>
-      <c r="BH129" s="214"/>
-      <c r="BI129" s="214"/>
-      <c r="BJ129" s="214"/>
-      <c r="BK129" s="214"/>
-      <c r="BL129" s="214"/>
-      <c r="BM129" s="214"/>
-      <c r="BN129" s="214"/>
-      <c r="BO129" s="214"/>
-      <c r="BP129" s="214"/>
-      <c r="BQ129" s="214"/>
-      <c r="BR129" s="214"/>
-      <c r="BS129" s="215"/>
+      <c r="A129" s="234"/>
+      <c r="B129" s="219"/>
+      <c r="C129" s="220"/>
+      <c r="D129" s="220"/>
+      <c r="E129" s="220"/>
+      <c r="F129" s="220"/>
+      <c r="G129" s="220"/>
+      <c r="H129" s="220"/>
+      <c r="I129" s="220"/>
+      <c r="J129" s="220"/>
+      <c r="K129" s="220"/>
+      <c r="L129" s="220"/>
+      <c r="M129" s="220"/>
+      <c r="N129" s="220"/>
+      <c r="O129" s="221"/>
+      <c r="P129" s="219"/>
+      <c r="Q129" s="220"/>
+      <c r="R129" s="220"/>
+      <c r="S129" s="220"/>
+      <c r="T129" s="220"/>
+      <c r="U129" s="220"/>
+      <c r="V129" s="220"/>
+      <c r="W129" s="220"/>
+      <c r="X129" s="220"/>
+      <c r="Y129" s="220"/>
+      <c r="Z129" s="220"/>
+      <c r="AA129" s="220"/>
+      <c r="AB129" s="220"/>
+      <c r="AC129" s="221"/>
+      <c r="AD129" s="219"/>
+      <c r="AE129" s="220"/>
+      <c r="AF129" s="220"/>
+      <c r="AG129" s="220"/>
+      <c r="AH129" s="220"/>
+      <c r="AI129" s="220"/>
+      <c r="AJ129" s="220"/>
+      <c r="AK129" s="220"/>
+      <c r="AL129" s="220"/>
+      <c r="AM129" s="220"/>
+      <c r="AN129" s="220"/>
+      <c r="AO129" s="220"/>
+      <c r="AP129" s="220"/>
+      <c r="AQ129" s="221"/>
+      <c r="AR129" s="219"/>
+      <c r="AS129" s="220"/>
+      <c r="AT129" s="220"/>
+      <c r="AU129" s="220"/>
+      <c r="AV129" s="220"/>
+      <c r="AW129" s="220"/>
+      <c r="AX129" s="220"/>
+      <c r="AY129" s="220"/>
+      <c r="AZ129" s="220"/>
+      <c r="BA129" s="220"/>
+      <c r="BB129" s="220"/>
+      <c r="BC129" s="220"/>
+      <c r="BD129" s="220"/>
+      <c r="BE129" s="221"/>
+      <c r="BF129" s="219"/>
+      <c r="BG129" s="220"/>
+      <c r="BH129" s="220"/>
+      <c r="BI129" s="220"/>
+      <c r="BJ129" s="220"/>
+      <c r="BK129" s="220"/>
+      <c r="BL129" s="220"/>
+      <c r="BM129" s="220"/>
+      <c r="BN129" s="220"/>
+      <c r="BO129" s="220"/>
+      <c r="BP129" s="220"/>
+      <c r="BQ129" s="220"/>
+      <c r="BR129" s="220"/>
+      <c r="BS129" s="221"/>
     </row>
     <row r="130" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="229"/>
-      <c r="B130" s="216"/>
-      <c r="C130" s="217"/>
-      <c r="D130" s="217"/>
-      <c r="E130" s="217"/>
-      <c r="F130" s="217"/>
-      <c r="G130" s="217"/>
-      <c r="H130" s="217"/>
-      <c r="I130" s="217"/>
-      <c r="J130" s="217"/>
-      <c r="K130" s="217"/>
-      <c r="L130" s="217"/>
-      <c r="M130" s="217"/>
-      <c r="N130" s="217"/>
-      <c r="O130" s="218"/>
-      <c r="P130" s="216"/>
-      <c r="Q130" s="217"/>
-      <c r="R130" s="217"/>
-      <c r="S130" s="217"/>
-      <c r="T130" s="217"/>
-      <c r="U130" s="217"/>
-      <c r="V130" s="217"/>
-      <c r="W130" s="217"/>
-      <c r="X130" s="217"/>
-      <c r="Y130" s="217"/>
-      <c r="Z130" s="217"/>
-      <c r="AA130" s="217"/>
-      <c r="AB130" s="217"/>
-      <c r="AC130" s="218"/>
-      <c r="AD130" s="216"/>
-      <c r="AE130" s="217"/>
-      <c r="AF130" s="217"/>
-      <c r="AG130" s="217"/>
-      <c r="AH130" s="217"/>
-      <c r="AI130" s="217"/>
-      <c r="AJ130" s="217"/>
-      <c r="AK130" s="217"/>
-      <c r="AL130" s="217"/>
-      <c r="AM130" s="217"/>
-      <c r="AN130" s="217"/>
-      <c r="AO130" s="217"/>
-      <c r="AP130" s="217"/>
-      <c r="AQ130" s="218"/>
-      <c r="AR130" s="216"/>
-      <c r="AS130" s="217"/>
-      <c r="AT130" s="217"/>
-      <c r="AU130" s="217"/>
-      <c r="AV130" s="217"/>
-      <c r="AW130" s="217"/>
-      <c r="AX130" s="217"/>
-      <c r="AY130" s="217"/>
-      <c r="AZ130" s="217"/>
-      <c r="BA130" s="217"/>
-      <c r="BB130" s="217"/>
-      <c r="BC130" s="217"/>
-      <c r="BD130" s="217"/>
-      <c r="BE130" s="218"/>
-      <c r="BF130" s="216"/>
-      <c r="BG130" s="217"/>
-      <c r="BH130" s="217"/>
-      <c r="BI130" s="217"/>
-      <c r="BJ130" s="217"/>
-      <c r="BK130" s="217"/>
-      <c r="BL130" s="217"/>
-      <c r="BM130" s="217"/>
-      <c r="BN130" s="217"/>
-      <c r="BO130" s="217"/>
-      <c r="BP130" s="217"/>
-      <c r="BQ130" s="217"/>
-      <c r="BR130" s="217"/>
-      <c r="BS130" s="218"/>
+      <c r="A130" s="235"/>
+      <c r="B130" s="222"/>
+      <c r="C130" s="223"/>
+      <c r="D130" s="223"/>
+      <c r="E130" s="223"/>
+      <c r="F130" s="223"/>
+      <c r="G130" s="223"/>
+      <c r="H130" s="223"/>
+      <c r="I130" s="223"/>
+      <c r="J130" s="223"/>
+      <c r="K130" s="223"/>
+      <c r="L130" s="223"/>
+      <c r="M130" s="223"/>
+      <c r="N130" s="223"/>
+      <c r="O130" s="224"/>
+      <c r="P130" s="222"/>
+      <c r="Q130" s="223"/>
+      <c r="R130" s="223"/>
+      <c r="S130" s="223"/>
+      <c r="T130" s="223"/>
+      <c r="U130" s="223"/>
+      <c r="V130" s="223"/>
+      <c r="W130" s="223"/>
+      <c r="X130" s="223"/>
+      <c r="Y130" s="223"/>
+      <c r="Z130" s="223"/>
+      <c r="AA130" s="223"/>
+      <c r="AB130" s="223"/>
+      <c r="AC130" s="224"/>
+      <c r="AD130" s="222"/>
+      <c r="AE130" s="223"/>
+      <c r="AF130" s="223"/>
+      <c r="AG130" s="223"/>
+      <c r="AH130" s="223"/>
+      <c r="AI130" s="223"/>
+      <c r="AJ130" s="223"/>
+      <c r="AK130" s="223"/>
+      <c r="AL130" s="223"/>
+      <c r="AM130" s="223"/>
+      <c r="AN130" s="223"/>
+      <c r="AO130" s="223"/>
+      <c r="AP130" s="223"/>
+      <c r="AQ130" s="224"/>
+      <c r="AR130" s="222"/>
+      <c r="AS130" s="223"/>
+      <c r="AT130" s="223"/>
+      <c r="AU130" s="223"/>
+      <c r="AV130" s="223"/>
+      <c r="AW130" s="223"/>
+      <c r="AX130" s="223"/>
+      <c r="AY130" s="223"/>
+      <c r="AZ130" s="223"/>
+      <c r="BA130" s="223"/>
+      <c r="BB130" s="223"/>
+      <c r="BC130" s="223"/>
+      <c r="BD130" s="223"/>
+      <c r="BE130" s="224"/>
+      <c r="BF130" s="222"/>
+      <c r="BG130" s="223"/>
+      <c r="BH130" s="223"/>
+      <c r="BI130" s="223"/>
+      <c r="BJ130" s="223"/>
+      <c r="BK130" s="223"/>
+      <c r="BL130" s="223"/>
+      <c r="BM130" s="223"/>
+      <c r="BN130" s="223"/>
+      <c r="BO130" s="223"/>
+      <c r="BP130" s="223"/>
+      <c r="BQ130" s="223"/>
+      <c r="BR130" s="223"/>
+      <c r="BS130" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="128">
@@ -23149,8 +23173,8 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="BF5:BG5"/>
     <mergeCell ref="AV5:AW5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="AX5:AY5"/>
-    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="BR5:BS5"/>
@@ -23256,15 +23280,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="231" t="s">
+      <c r="A1" s="237" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="234">
+      <c r="B1" s="240">
         <v>46216</v>
       </c>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -23277,71 +23301,71 @@
       <c r="O1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="200" t="s">
+      <c r="P1" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="201"/>
-      <c r="Y1" s="201"/>
-      <c r="Z1" s="201"/>
-      <c r="AA1" s="201"/>
-      <c r="AB1" s="201"/>
-      <c r="AC1" s="201"/>
-      <c r="AD1" s="223"/>
-      <c r="AE1" s="201"/>
-      <c r="AF1" s="201"/>
-      <c r="AG1" s="201"/>
-      <c r="AH1" s="201"/>
-      <c r="AI1" s="201"/>
-      <c r="AJ1" s="201"/>
-      <c r="AK1" s="201"/>
-      <c r="AL1" s="201"/>
-      <c r="AM1" s="201"/>
-      <c r="AN1" s="201"/>
-      <c r="AO1" s="201"/>
-      <c r="AP1" s="201"/>
-      <c r="AQ1" s="201"/>
-      <c r="AR1" s="223"/>
-      <c r="AS1" s="201"/>
-      <c r="AT1" s="201"/>
-      <c r="AU1" s="201"/>
-      <c r="AV1" s="201"/>
-      <c r="AW1" s="201"/>
-      <c r="AX1" s="201"/>
-      <c r="AY1" s="201"/>
-      <c r="AZ1" s="201"/>
-      <c r="BA1" s="201"/>
-      <c r="BB1" s="201"/>
-      <c r="BC1" s="201"/>
-      <c r="BD1" s="201"/>
-      <c r="BE1" s="201"/>
-      <c r="BF1" s="224"/>
-      <c r="BG1" s="201"/>
-      <c r="BH1" s="201"/>
-      <c r="BI1" s="201"/>
-      <c r="BJ1" s="201"/>
-      <c r="BK1" s="201"/>
-      <c r="BL1" s="201"/>
-      <c r="BM1" s="201"/>
-      <c r="BN1" s="201"/>
-      <c r="BO1" s="201"/>
-      <c r="BP1" s="201"/>
-      <c r="BQ1" s="201"/>
-      <c r="BR1" s="201"/>
-      <c r="BS1" s="225"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
+      <c r="T1" s="207"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
+      <c r="W1" s="207"/>
+      <c r="X1" s="207"/>
+      <c r="Y1" s="207"/>
+      <c r="Z1" s="207"/>
+      <c r="AA1" s="207"/>
+      <c r="AB1" s="207"/>
+      <c r="AC1" s="207"/>
+      <c r="AD1" s="229"/>
+      <c r="AE1" s="207"/>
+      <c r="AF1" s="207"/>
+      <c r="AG1" s="207"/>
+      <c r="AH1" s="207"/>
+      <c r="AI1" s="207"/>
+      <c r="AJ1" s="207"/>
+      <c r="AK1" s="207"/>
+      <c r="AL1" s="207"/>
+      <c r="AM1" s="207"/>
+      <c r="AN1" s="207"/>
+      <c r="AO1" s="207"/>
+      <c r="AP1" s="207"/>
+      <c r="AQ1" s="207"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="207"/>
+      <c r="AT1" s="207"/>
+      <c r="AU1" s="207"/>
+      <c r="AV1" s="207"/>
+      <c r="AW1" s="207"/>
+      <c r="AX1" s="207"/>
+      <c r="AY1" s="207"/>
+      <c r="AZ1" s="207"/>
+      <c r="BA1" s="207"/>
+      <c r="BB1" s="207"/>
+      <c r="BC1" s="207"/>
+      <c r="BD1" s="207"/>
+      <c r="BE1" s="207"/>
+      <c r="BF1" s="230"/>
+      <c r="BG1" s="207"/>
+      <c r="BH1" s="207"/>
+      <c r="BI1" s="207"/>
+      <c r="BJ1" s="207"/>
+      <c r="BK1" s="207"/>
+      <c r="BL1" s="207"/>
+      <c r="BM1" s="207"/>
+      <c r="BN1" s="207"/>
+      <c r="BO1" s="207"/>
+      <c r="BP1" s="207"/>
+      <c r="BQ1" s="207"/>
+      <c r="BR1" s="207"/>
+      <c r="BS1" s="231"/>
     </row>
     <row r="2" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="232"/>
-      <c r="B2" s="217"/>
-      <c r="C2" s="217"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="217"/>
+      <c r="A2" s="238"/>
+      <c r="B2" s="223"/>
+      <c r="C2" s="223"/>
+      <c r="D2" s="223"/>
+      <c r="E2" s="223"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
@@ -23354,473 +23378,473 @@
       <c r="O2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="204" t="s">
+      <c r="P2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="205"/>
-      <c r="R2" s="205"/>
-      <c r="S2" s="205"/>
-      <c r="T2" s="205"/>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
-      <c r="W2" s="205"/>
-      <c r="X2" s="205"/>
-      <c r="Y2" s="205"/>
-      <c r="Z2" s="205"/>
-      <c r="AA2" s="205"/>
-      <c r="AB2" s="205"/>
-      <c r="AC2" s="205"/>
-      <c r="AD2" s="205"/>
-      <c r="AE2" s="205"/>
-      <c r="AF2" s="205"/>
-      <c r="AG2" s="205"/>
-      <c r="AH2" s="205"/>
-      <c r="AI2" s="205"/>
-      <c r="AJ2" s="205"/>
-      <c r="AK2" s="205"/>
-      <c r="AL2" s="205"/>
-      <c r="AM2" s="205"/>
-      <c r="AN2" s="205"/>
-      <c r="AO2" s="205"/>
-      <c r="AP2" s="205"/>
-      <c r="AQ2" s="205"/>
-      <c r="AR2" s="205"/>
-      <c r="AS2" s="205"/>
-      <c r="AT2" s="205"/>
-      <c r="AU2" s="205"/>
-      <c r="AV2" s="205"/>
-      <c r="AW2" s="205"/>
-      <c r="AX2" s="205"/>
-      <c r="AY2" s="205"/>
-      <c r="AZ2" s="205"/>
-      <c r="BA2" s="205"/>
-      <c r="BB2" s="205"/>
-      <c r="BC2" s="205"/>
-      <c r="BD2" s="205"/>
-      <c r="BE2" s="205"/>
-      <c r="BF2" s="205"/>
-      <c r="BG2" s="205"/>
-      <c r="BH2" s="205"/>
-      <c r="BI2" s="205"/>
-      <c r="BJ2" s="205"/>
-      <c r="BK2" s="205"/>
-      <c r="BL2" s="205"/>
-      <c r="BM2" s="205"/>
-      <c r="BN2" s="205"/>
-      <c r="BO2" s="205"/>
-      <c r="BP2" s="205"/>
-      <c r="BQ2" s="205"/>
-      <c r="BR2" s="205"/>
-      <c r="BS2" s="226"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
+      <c r="AA2" s="211"/>
+      <c r="AB2" s="211"/>
+      <c r="AC2" s="211"/>
+      <c r="AD2" s="211"/>
+      <c r="AE2" s="211"/>
+      <c r="AF2" s="211"/>
+      <c r="AG2" s="211"/>
+      <c r="AH2" s="211"/>
+      <c r="AI2" s="211"/>
+      <c r="AJ2" s="211"/>
+      <c r="AK2" s="211"/>
+      <c r="AL2" s="211"/>
+      <c r="AM2" s="211"/>
+      <c r="AN2" s="211"/>
+      <c r="AO2" s="211"/>
+      <c r="AP2" s="211"/>
+      <c r="AQ2" s="211"/>
+      <c r="AR2" s="211"/>
+      <c r="AS2" s="211"/>
+      <c r="AT2" s="211"/>
+      <c r="AU2" s="211"/>
+      <c r="AV2" s="211"/>
+      <c r="AW2" s="211"/>
+      <c r="AX2" s="211"/>
+      <c r="AY2" s="211"/>
+      <c r="AZ2" s="211"/>
+      <c r="BA2" s="211"/>
+      <c r="BB2" s="211"/>
+      <c r="BC2" s="211"/>
+      <c r="BD2" s="211"/>
+      <c r="BE2" s="211"/>
+      <c r="BF2" s="211"/>
+      <c r="BG2" s="211"/>
+      <c r="BH2" s="211"/>
+      <c r="BI2" s="211"/>
+      <c r="BJ2" s="211"/>
+      <c r="BK2" s="211"/>
+      <c r="BL2" s="211"/>
+      <c r="BM2" s="211"/>
+      <c r="BN2" s="211"/>
+      <c r="BO2" s="211"/>
+      <c r="BP2" s="211"/>
+      <c r="BQ2" s="211"/>
+      <c r="BR2" s="211"/>
+      <c r="BS2" s="232"/>
     </row>
     <row r="3" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
-      <c r="B3" s="197" t="str">
+      <c r="B3" s="203" t="str">
         <f>"Woche " &amp; WEEKNUM(B4)</f>
         <v>Woche 29</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="198"/>
-      <c r="O3" s="199"/>
-      <c r="P3" s="219" t="str">
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="204"/>
+      <c r="J3" s="204"/>
+      <c r="K3" s="204"/>
+      <c r="L3" s="204"/>
+      <c r="M3" s="204"/>
+      <c r="N3" s="204"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(P4)</f>
         <v>Woche 30</v>
       </c>
-      <c r="Q3" s="198"/>
-      <c r="R3" s="198"/>
-      <c r="S3" s="198"/>
-      <c r="T3" s="198"/>
-      <c r="U3" s="198"/>
-      <c r="V3" s="198"/>
-      <c r="W3" s="198"/>
-      <c r="X3" s="198"/>
-      <c r="Y3" s="198"/>
-      <c r="Z3" s="198"/>
-      <c r="AA3" s="198"/>
-      <c r="AB3" s="198"/>
-      <c r="AC3" s="199"/>
-      <c r="AD3" s="219" t="str">
+      <c r="Q3" s="204"/>
+      <c r="R3" s="204"/>
+      <c r="S3" s="204"/>
+      <c r="T3" s="204"/>
+      <c r="U3" s="204"/>
+      <c r="V3" s="204"/>
+      <c r="W3" s="204"/>
+      <c r="X3" s="204"/>
+      <c r="Y3" s="204"/>
+      <c r="Z3" s="204"/>
+      <c r="AA3" s="204"/>
+      <c r="AB3" s="204"/>
+      <c r="AC3" s="205"/>
+      <c r="AD3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(AD4)</f>
         <v>Woche 31</v>
       </c>
-      <c r="AE3" s="198"/>
-      <c r="AF3" s="198"/>
-      <c r="AG3" s="198"/>
-      <c r="AH3" s="198"/>
-      <c r="AI3" s="198"/>
-      <c r="AJ3" s="198"/>
-      <c r="AK3" s="198"/>
-      <c r="AL3" s="198"/>
-      <c r="AM3" s="198"/>
-      <c r="AN3" s="198"/>
-      <c r="AO3" s="198"/>
-      <c r="AP3" s="198"/>
-      <c r="AQ3" s="199"/>
-      <c r="AR3" s="219" t="str">
+      <c r="AE3" s="204"/>
+      <c r="AF3" s="204"/>
+      <c r="AG3" s="204"/>
+      <c r="AH3" s="204"/>
+      <c r="AI3" s="204"/>
+      <c r="AJ3" s="204"/>
+      <c r="AK3" s="204"/>
+      <c r="AL3" s="204"/>
+      <c r="AM3" s="204"/>
+      <c r="AN3" s="204"/>
+      <c r="AO3" s="204"/>
+      <c r="AP3" s="204"/>
+      <c r="AQ3" s="205"/>
+      <c r="AR3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(AR4)</f>
         <v>Woche 32</v>
       </c>
-      <c r="AS3" s="198"/>
-      <c r="AT3" s="198"/>
-      <c r="AU3" s="198"/>
-      <c r="AV3" s="198"/>
-      <c r="AW3" s="198"/>
-      <c r="AX3" s="198"/>
-      <c r="AY3" s="198"/>
-      <c r="AZ3" s="198"/>
-      <c r="BA3" s="198"/>
-      <c r="BB3" s="198"/>
-      <c r="BC3" s="198"/>
-      <c r="BD3" s="198"/>
-      <c r="BE3" s="199"/>
-      <c r="BF3" s="219" t="str">
+      <c r="AS3" s="204"/>
+      <c r="AT3" s="204"/>
+      <c r="AU3" s="204"/>
+      <c r="AV3" s="204"/>
+      <c r="AW3" s="204"/>
+      <c r="AX3" s="204"/>
+      <c r="AY3" s="204"/>
+      <c r="AZ3" s="204"/>
+      <c r="BA3" s="204"/>
+      <c r="BB3" s="204"/>
+      <c r="BC3" s="204"/>
+      <c r="BD3" s="204"/>
+      <c r="BE3" s="205"/>
+      <c r="BF3" s="225" t="str">
         <f>"Woche " &amp; WEEKNUM(BF4)</f>
         <v>Woche 33</v>
       </c>
-      <c r="BG3" s="198"/>
-      <c r="BH3" s="198"/>
-      <c r="BI3" s="198"/>
-      <c r="BJ3" s="198"/>
-      <c r="BK3" s="198"/>
-      <c r="BL3" s="198"/>
-      <c r="BM3" s="198"/>
-      <c r="BN3" s="198"/>
-      <c r="BO3" s="198"/>
-      <c r="BP3" s="198"/>
-      <c r="BQ3" s="198"/>
-      <c r="BR3" s="198"/>
-      <c r="BS3" s="199"/>
+      <c r="BG3" s="204"/>
+      <c r="BH3" s="204"/>
+      <c r="BI3" s="204"/>
+      <c r="BJ3" s="204"/>
+      <c r="BK3" s="204"/>
+      <c r="BL3" s="204"/>
+      <c r="BM3" s="204"/>
+      <c r="BN3" s="204"/>
+      <c r="BO3" s="204"/>
+      <c r="BP3" s="204"/>
+      <c r="BQ3" s="204"/>
+      <c r="BR3" s="204"/>
+      <c r="BS3" s="205"/>
     </row>
     <row r="4" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A4" s="13"/>
-      <c r="B4" s="206">
+      <c r="B4" s="212">
         <f>B1</f>
         <v>46216</v>
       </c>
-      <c r="C4" s="207"/>
-      <c r="D4" s="206">
+      <c r="C4" s="213"/>
+      <c r="D4" s="212">
         <f>B4+1</f>
         <v>46217</v>
       </c>
-      <c r="E4" s="207"/>
-      <c r="F4" s="206">
+      <c r="E4" s="213"/>
+      <c r="F4" s="212">
         <f>D4+1</f>
         <v>46218</v>
       </c>
-      <c r="G4" s="207"/>
-      <c r="H4" s="206">
+      <c r="G4" s="213"/>
+      <c r="H4" s="212">
         <f>F4+1</f>
         <v>46219</v>
       </c>
-      <c r="I4" s="207"/>
-      <c r="J4" s="206">
+      <c r="I4" s="213"/>
+      <c r="J4" s="212">
         <f>H4+1</f>
         <v>46220</v>
       </c>
-      <c r="K4" s="207"/>
-      <c r="L4" s="206">
+      <c r="K4" s="213"/>
+      <c r="L4" s="212">
         <f>J4+1</f>
         <v>46221</v>
       </c>
-      <c r="M4" s="207"/>
-      <c r="N4" s="206">
+      <c r="M4" s="213"/>
+      <c r="N4" s="212">
         <f>L4+1</f>
         <v>46222</v>
       </c>
-      <c r="O4" s="207"/>
-      <c r="P4" s="206">
+      <c r="O4" s="213"/>
+      <c r="P4" s="212">
         <f>N4+1</f>
         <v>46223</v>
       </c>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="206">
+      <c r="Q4" s="213"/>
+      <c r="R4" s="212">
         <f>P4+1</f>
         <v>46224</v>
       </c>
-      <c r="S4" s="207"/>
-      <c r="T4" s="206">
+      <c r="S4" s="213"/>
+      <c r="T4" s="212">
         <f>R4+1</f>
         <v>46225</v>
       </c>
-      <c r="U4" s="207"/>
-      <c r="V4" s="206">
+      <c r="U4" s="213"/>
+      <c r="V4" s="212">
         <f>T4+1</f>
         <v>46226</v>
       </c>
-      <c r="W4" s="207"/>
-      <c r="X4" s="206">
+      <c r="W4" s="213"/>
+      <c r="X4" s="212">
         <f>V4+1</f>
         <v>46227</v>
       </c>
-      <c r="Y4" s="207"/>
-      <c r="Z4" s="206">
+      <c r="Y4" s="213"/>
+      <c r="Z4" s="212">
         <f>X4+1</f>
         <v>46228</v>
       </c>
-      <c r="AA4" s="207"/>
-      <c r="AB4" s="220">
+      <c r="AA4" s="213"/>
+      <c r="AB4" s="226">
         <f>Z4+1</f>
         <v>46229</v>
       </c>
-      <c r="AC4" s="207"/>
-      <c r="AD4" s="220">
+      <c r="AC4" s="213"/>
+      <c r="AD4" s="226">
         <f>AB4+1</f>
         <v>46230</v>
       </c>
-      <c r="AE4" s="207"/>
-      <c r="AF4" s="206">
+      <c r="AE4" s="213"/>
+      <c r="AF4" s="212">
         <f>AD4+1</f>
         <v>46231</v>
       </c>
-      <c r="AG4" s="207"/>
-      <c r="AH4" s="206">
+      <c r="AG4" s="213"/>
+      <c r="AH4" s="212">
         <f>AF4+1</f>
         <v>46232</v>
       </c>
-      <c r="AI4" s="207"/>
-      <c r="AJ4" s="206">
+      <c r="AI4" s="213"/>
+      <c r="AJ4" s="212">
         <f>AH4+1</f>
         <v>46233</v>
       </c>
-      <c r="AK4" s="207"/>
-      <c r="AL4" s="206">
+      <c r="AK4" s="213"/>
+      <c r="AL4" s="212">
         <f>AJ4+1</f>
         <v>46234</v>
       </c>
-      <c r="AM4" s="207"/>
-      <c r="AN4" s="206">
+      <c r="AM4" s="213"/>
+      <c r="AN4" s="212">
         <f>AL4+1</f>
         <v>46235</v>
       </c>
-      <c r="AO4" s="207"/>
-      <c r="AP4" s="206">
+      <c r="AO4" s="213"/>
+      <c r="AP4" s="212">
         <f>AN4+1</f>
         <v>46236</v>
       </c>
-      <c r="AQ4" s="207"/>
-      <c r="AR4" s="206">
+      <c r="AQ4" s="213"/>
+      <c r="AR4" s="212">
         <f>AP4+1</f>
         <v>46237</v>
       </c>
-      <c r="AS4" s="207"/>
-      <c r="AT4" s="206">
+      <c r="AS4" s="213"/>
+      <c r="AT4" s="212">
         <f>AR4+1</f>
         <v>46238</v>
       </c>
-      <c r="AU4" s="207"/>
-      <c r="AV4" s="206">
+      <c r="AU4" s="213"/>
+      <c r="AV4" s="212">
         <f>AT4+1</f>
         <v>46239</v>
       </c>
-      <c r="AW4" s="207"/>
-      <c r="AX4" s="206">
+      <c r="AW4" s="213"/>
+      <c r="AX4" s="212">
         <f>AV4+1</f>
         <v>46240</v>
       </c>
-      <c r="AY4" s="207"/>
-      <c r="AZ4" s="206">
+      <c r="AY4" s="213"/>
+      <c r="AZ4" s="212">
         <f>AX4+1</f>
         <v>46241</v>
       </c>
-      <c r="BA4" s="207"/>
-      <c r="BB4" s="206">
+      <c r="BA4" s="213"/>
+      <c r="BB4" s="212">
         <f>AZ4+1</f>
         <v>46242</v>
       </c>
-      <c r="BC4" s="207"/>
-      <c r="BD4" s="206">
+      <c r="BC4" s="213"/>
+      <c r="BD4" s="212">
         <f>BB4+1</f>
         <v>46243</v>
       </c>
-      <c r="BE4" s="207"/>
-      <c r="BF4" s="206">
+      <c r="BE4" s="213"/>
+      <c r="BF4" s="212">
         <f>BD4+1</f>
         <v>46244</v>
       </c>
-      <c r="BG4" s="207"/>
-      <c r="BH4" s="206">
+      <c r="BG4" s="213"/>
+      <c r="BH4" s="212">
         <f>BF4+1</f>
         <v>46245</v>
       </c>
-      <c r="BI4" s="207"/>
-      <c r="BJ4" s="206">
+      <c r="BI4" s="213"/>
+      <c r="BJ4" s="212">
         <f>BH4+1</f>
         <v>46246</v>
       </c>
-      <c r="BK4" s="207"/>
-      <c r="BL4" s="206">
+      <c r="BK4" s="213"/>
+      <c r="BL4" s="212">
         <f>BJ4+1</f>
         <v>46247</v>
       </c>
-      <c r="BM4" s="207"/>
-      <c r="BN4" s="206">
+      <c r="BM4" s="213"/>
+      <c r="BN4" s="212">
         <f>BL4+1</f>
         <v>46248</v>
       </c>
-      <c r="BO4" s="207"/>
-      <c r="BP4" s="206">
+      <c r="BO4" s="213"/>
+      <c r="BP4" s="212">
         <f>BN4+1</f>
         <v>46249</v>
       </c>
-      <c r="BQ4" s="207"/>
-      <c r="BR4" s="206">
+      <c r="BQ4" s="213"/>
+      <c r="BR4" s="212">
         <f>BP4+1</f>
         <v>46250</v>
       </c>
-      <c r="BS4" s="207"/>
+      <c r="BS4" s="213"/>
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A5" s="75"/>
-      <c r="B5" s="230" t="s">
+      <c r="B5" s="236" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="196"/>
-      <c r="D5" s="195" t="s">
+      <c r="C5" s="202"/>
+      <c r="D5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="196"/>
-      <c r="F5" s="195" t="s">
+      <c r="E5" s="202"/>
+      <c r="F5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="196"/>
-      <c r="H5" s="195" t="s">
+      <c r="G5" s="202"/>
+      <c r="H5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="196"/>
-      <c r="J5" s="195" t="s">
+      <c r="I5" s="202"/>
+      <c r="J5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="196"/>
-      <c r="L5" s="195" t="s">
+      <c r="K5" s="202"/>
+      <c r="L5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="196"/>
-      <c r="N5" s="195" t="s">
+      <c r="M5" s="202"/>
+      <c r="N5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="196"/>
-      <c r="P5" s="202" t="s">
+      <c r="O5" s="202"/>
+      <c r="P5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="196"/>
-      <c r="R5" s="195" t="s">
+      <c r="Q5" s="202"/>
+      <c r="R5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="S5" s="196"/>
-      <c r="T5" s="195" t="s">
+      <c r="S5" s="202"/>
+      <c r="T5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="U5" s="196"/>
-      <c r="V5" s="195" t="s">
+      <c r="U5" s="202"/>
+      <c r="V5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="W5" s="196"/>
-      <c r="X5" s="195" t="s">
+      <c r="W5" s="202"/>
+      <c r="X5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="Y5" s="196"/>
-      <c r="Z5" s="195" t="s">
+      <c r="Y5" s="202"/>
+      <c r="Z5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="AA5" s="196"/>
-      <c r="AB5" s="195" t="s">
+      <c r="AA5" s="202"/>
+      <c r="AB5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AC5" s="196"/>
-      <c r="AD5" s="202" t="s">
+      <c r="AC5" s="202"/>
+      <c r="AD5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="AE5" s="196"/>
-      <c r="AF5" s="195" t="s">
+      <c r="AE5" s="202"/>
+      <c r="AF5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="AG5" s="196"/>
-      <c r="AH5" s="195" t="s">
+      <c r="AG5" s="202"/>
+      <c r="AH5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="AI5" s="196"/>
-      <c r="AJ5" s="195" t="s">
+      <c r="AI5" s="202"/>
+      <c r="AJ5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="AK5" s="196"/>
-      <c r="AL5" s="195" t="s">
+      <c r="AK5" s="202"/>
+      <c r="AL5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="AM5" s="196"/>
-      <c r="AN5" s="195" t="s">
+      <c r="AM5" s="202"/>
+      <c r="AN5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="AO5" s="196"/>
-      <c r="AP5" s="195" t="s">
+      <c r="AO5" s="202"/>
+      <c r="AP5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="AQ5" s="196"/>
-      <c r="AR5" s="202" t="s">
+      <c r="AQ5" s="202"/>
+      <c r="AR5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="AS5" s="196"/>
-      <c r="AT5" s="195" t="s">
+      <c r="AS5" s="202"/>
+      <c r="AT5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="AU5" s="196"/>
-      <c r="AV5" s="195" t="s">
+      <c r="AU5" s="202"/>
+      <c r="AV5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="AW5" s="196"/>
-      <c r="AX5" s="195" t="s">
+      <c r="AW5" s="202"/>
+      <c r="AX5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="AY5" s="196"/>
-      <c r="AZ5" s="195" t="s">
+      <c r="AY5" s="202"/>
+      <c r="AZ5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="BA5" s="196"/>
-      <c r="BB5" s="195" t="s">
+      <c r="BA5" s="202"/>
+      <c r="BB5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="BC5" s="196"/>
-      <c r="BD5" s="195" t="s">
+      <c r="BC5" s="202"/>
+      <c r="BD5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="BE5" s="196"/>
-      <c r="BF5" s="202" t="s">
+      <c r="BE5" s="202"/>
+      <c r="BF5" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="BG5" s="196"/>
-      <c r="BH5" s="195" t="s">
+      <c r="BG5" s="202"/>
+      <c r="BH5" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="BI5" s="196"/>
-      <c r="BJ5" s="195" t="s">
+      <c r="BI5" s="202"/>
+      <c r="BJ5" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="BK5" s="196"/>
-      <c r="BL5" s="195" t="s">
+      <c r="BK5" s="202"/>
+      <c r="BL5" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="BM5" s="196"/>
-      <c r="BN5" s="195" t="s">
+      <c r="BM5" s="202"/>
+      <c r="BN5" s="201" t="s">
         <v>12</v>
       </c>
-      <c r="BO5" s="196"/>
-      <c r="BP5" s="195" t="s">
+      <c r="BO5" s="202"/>
+      <c r="BP5" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="BQ5" s="196"/>
-      <c r="BR5" s="195" t="s">
+      <c r="BQ5" s="202"/>
+      <c r="BR5" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="BS5" s="196"/>
+      <c r="BS5" s="202"/>
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
@@ -28398,18 +28422,18 @@
       <c r="A66" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="B66" s="235" t="s">
+      <c r="B66" s="241" t="s">
         <v>216</v>
       </c>
-      <c r="C66" s="236"/>
-      <c r="D66" s="236"/>
-      <c r="E66" s="236"/>
-      <c r="F66" s="236"/>
-      <c r="G66" s="236"/>
-      <c r="H66" s="236"/>
-      <c r="I66" s="236"/>
-      <c r="J66" s="236"/>
-      <c r="K66" s="237"/>
+      <c r="C66" s="242"/>
+      <c r="D66" s="242"/>
+      <c r="E66" s="242"/>
+      <c r="F66" s="242"/>
+      <c r="G66" s="242"/>
+      <c r="H66" s="242"/>
+      <c r="I66" s="242"/>
+      <c r="J66" s="242"/>
+      <c r="K66" s="243"/>
       <c r="L66" s="33"/>
       <c r="M66" s="34"/>
       <c r="N66" s="33"/>
@@ -28475,16 +28499,16 @@
       <c r="A67" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="B67" s="213"/>
-      <c r="C67" s="214"/>
-      <c r="D67" s="214"/>
-      <c r="E67" s="214"/>
-      <c r="F67" s="214"/>
-      <c r="G67" s="214"/>
-      <c r="H67" s="214"/>
-      <c r="I67" s="214"/>
-      <c r="J67" s="214"/>
-      <c r="K67" s="238"/>
+      <c r="B67" s="219"/>
+      <c r="C67" s="220"/>
+      <c r="D67" s="220"/>
+      <c r="E67" s="220"/>
+      <c r="F67" s="220"/>
+      <c r="G67" s="220"/>
+      <c r="H67" s="220"/>
+      <c r="I67" s="220"/>
+      <c r="J67" s="220"/>
+      <c r="K67" s="244"/>
       <c r="L67" s="33"/>
       <c r="M67" s="34"/>
       <c r="N67" s="33"/>
@@ -28550,16 +28574,16 @@
       <c r="A68" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="B68" s="213"/>
-      <c r="C68" s="214"/>
-      <c r="D68" s="214"/>
-      <c r="E68" s="214"/>
-      <c r="F68" s="214"/>
-      <c r="G68" s="214"/>
-      <c r="H68" s="214"/>
-      <c r="I68" s="214"/>
-      <c r="J68" s="214"/>
-      <c r="K68" s="238"/>
+      <c r="B68" s="219"/>
+      <c r="C68" s="220"/>
+      <c r="D68" s="220"/>
+      <c r="E68" s="220"/>
+      <c r="F68" s="220"/>
+      <c r="G68" s="220"/>
+      <c r="H68" s="220"/>
+      <c r="I68" s="220"/>
+      <c r="J68" s="220"/>
+      <c r="K68" s="244"/>
       <c r="L68" s="33"/>
       <c r="M68" s="34"/>
       <c r="N68" s="33"/>
@@ -28625,16 +28649,16 @@
       <c r="A69" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="B69" s="239"/>
-      <c r="C69" s="240"/>
-      <c r="D69" s="240"/>
-      <c r="E69" s="240"/>
-      <c r="F69" s="240"/>
-      <c r="G69" s="240"/>
-      <c r="H69" s="240"/>
-      <c r="I69" s="240"/>
-      <c r="J69" s="240"/>
-      <c r="K69" s="241"/>
+      <c r="B69" s="245"/>
+      <c r="C69" s="246"/>
+      <c r="D69" s="246"/>
+      <c r="E69" s="246"/>
+      <c r="F69" s="246"/>
+      <c r="G69" s="246"/>
+      <c r="H69" s="246"/>
+      <c r="I69" s="246"/>
+      <c r="J69" s="246"/>
+      <c r="K69" s="247"/>
       <c r="L69" s="33"/>
       <c r="M69" s="34"/>
       <c r="N69" s="33"/>
@@ -28945,28 +28969,28 @@
       <c r="S73" s="10"/>
       <c r="T73" s="9"/>
       <c r="U73" s="10"/>
-      <c r="V73" s="242" t="s">
+      <c r="V73" s="248" t="s">
         <v>224</v>
       </c>
-      <c r="W73" s="243"/>
-      <c r="X73" s="243"/>
-      <c r="Y73" s="244"/>
+      <c r="W73" s="249"/>
+      <c r="X73" s="249"/>
+      <c r="Y73" s="250"/>
       <c r="Z73" s="33"/>
       <c r="AA73" s="34"/>
       <c r="AB73" s="33"/>
       <c r="AC73" s="35"/>
-      <c r="AD73" s="245" t="s">
+      <c r="AD73" s="251" t="s">
         <v>225</v>
       </c>
-      <c r="AE73" s="243"/>
-      <c r="AF73" s="243"/>
-      <c r="AG73" s="243"/>
-      <c r="AH73" s="243"/>
-      <c r="AI73" s="243"/>
-      <c r="AJ73" s="243"/>
-      <c r="AK73" s="243"/>
-      <c r="AL73" s="243"/>
-      <c r="AM73" s="244"/>
+      <c r="AE73" s="249"/>
+      <c r="AF73" s="249"/>
+      <c r="AG73" s="249"/>
+      <c r="AH73" s="249"/>
+      <c r="AI73" s="249"/>
+      <c r="AJ73" s="249"/>
+      <c r="AK73" s="249"/>
+      <c r="AL73" s="249"/>
+      <c r="AM73" s="250"/>
       <c r="AN73" s="33"/>
       <c r="AO73" s="34"/>
       <c r="AP73" s="33"/>
@@ -31940,738 +31964,738 @@
       <c r="A114" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B114" s="203">
+      <c r="B114" s="209">
         <v>22</v>
       </c>
-      <c r="C114" s="194"/>
-      <c r="D114" s="193">
+      <c r="C114" s="200"/>
+      <c r="D114" s="199">
         <v>22</v>
       </c>
-      <c r="E114" s="194"/>
-      <c r="F114" s="193">
+      <c r="E114" s="200"/>
+      <c r="F114" s="199">
         <v>22</v>
       </c>
-      <c r="G114" s="194"/>
-      <c r="H114" s="193">
+      <c r="G114" s="200"/>
+      <c r="H114" s="199">
         <v>22</v>
       </c>
-      <c r="I114" s="194"/>
-      <c r="J114" s="193">
+      <c r="I114" s="200"/>
+      <c r="J114" s="199">
         <v>22</v>
       </c>
-      <c r="K114" s="194"/>
-      <c r="L114" s="193">
+      <c r="K114" s="200"/>
+      <c r="L114" s="199">
         <v>0</v>
       </c>
-      <c r="M114" s="194"/>
-      <c r="N114" s="193">
+      <c r="M114" s="200"/>
+      <c r="N114" s="199">
         <v>0</v>
       </c>
-      <c r="O114" s="194"/>
-      <c r="P114" s="203">
+      <c r="O114" s="200"/>
+      <c r="P114" s="209">
         <v>22</v>
       </c>
-      <c r="Q114" s="194"/>
-      <c r="R114" s="193">
+      <c r="Q114" s="200"/>
+      <c r="R114" s="199">
         <v>22</v>
       </c>
-      <c r="S114" s="194"/>
-      <c r="T114" s="193">
+      <c r="S114" s="200"/>
+      <c r="T114" s="199">
         <v>22</v>
       </c>
-      <c r="U114" s="194"/>
-      <c r="V114" s="193">
+      <c r="U114" s="200"/>
+      <c r="V114" s="199">
         <v>22</v>
       </c>
-      <c r="W114" s="194"/>
-      <c r="X114" s="193">
+      <c r="W114" s="200"/>
+      <c r="X114" s="199">
         <v>22</v>
       </c>
-      <c r="Y114" s="194"/>
-      <c r="Z114" s="193">
+      <c r="Y114" s="200"/>
+      <c r="Z114" s="199">
         <v>0</v>
       </c>
-      <c r="AA114" s="194"/>
-      <c r="AB114" s="193">
+      <c r="AA114" s="200"/>
+      <c r="AB114" s="199">
         <v>0</v>
       </c>
-      <c r="AC114" s="194"/>
-      <c r="AD114" s="203">
+      <c r="AC114" s="200"/>
+      <c r="AD114" s="209">
         <v>22</v>
       </c>
-      <c r="AE114" s="194"/>
-      <c r="AF114" s="193">
+      <c r="AE114" s="200"/>
+      <c r="AF114" s="199">
         <v>22</v>
       </c>
-      <c r="AG114" s="194"/>
-      <c r="AH114" s="193">
+      <c r="AG114" s="200"/>
+      <c r="AH114" s="199">
         <v>22</v>
       </c>
-      <c r="AI114" s="194"/>
-      <c r="AJ114" s="193">
+      <c r="AI114" s="200"/>
+      <c r="AJ114" s="199">
         <v>22</v>
       </c>
-      <c r="AK114" s="194"/>
-      <c r="AL114" s="193">
+      <c r="AK114" s="200"/>
+      <c r="AL114" s="199">
         <v>22</v>
       </c>
-      <c r="AM114" s="194"/>
-      <c r="AN114" s="193">
+      <c r="AM114" s="200"/>
+      <c r="AN114" s="199">
         <v>0</v>
       </c>
-      <c r="AO114" s="194"/>
-      <c r="AP114" s="193">
+      <c r="AO114" s="200"/>
+      <c r="AP114" s="199">
         <v>0</v>
       </c>
-      <c r="AQ114" s="194"/>
-      <c r="AR114" s="203">
+      <c r="AQ114" s="200"/>
+      <c r="AR114" s="209">
         <v>22</v>
       </c>
-      <c r="AS114" s="194"/>
-      <c r="AT114" s="193">
+      <c r="AS114" s="200"/>
+      <c r="AT114" s="199">
         <v>22</v>
       </c>
-      <c r="AU114" s="194"/>
-      <c r="AV114" s="193">
+      <c r="AU114" s="200"/>
+      <c r="AV114" s="199">
         <v>22</v>
       </c>
-      <c r="AW114" s="194"/>
-      <c r="AX114" s="193">
+      <c r="AW114" s="200"/>
+      <c r="AX114" s="199">
         <v>22</v>
       </c>
-      <c r="AY114" s="194"/>
-      <c r="AZ114" s="193">
+      <c r="AY114" s="200"/>
+      <c r="AZ114" s="199">
         <v>22</v>
       </c>
-      <c r="BA114" s="194"/>
-      <c r="BB114" s="193">
+      <c r="BA114" s="200"/>
+      <c r="BB114" s="199">
         <v>0</v>
       </c>
-      <c r="BC114" s="194"/>
-      <c r="BD114" s="193">
+      <c r="BC114" s="200"/>
+      <c r="BD114" s="199">
         <v>0</v>
       </c>
-      <c r="BE114" s="194"/>
-      <c r="BF114" s="203">
+      <c r="BE114" s="200"/>
+      <c r="BF114" s="209">
         <v>22</v>
       </c>
-      <c r="BG114" s="194"/>
-      <c r="BH114" s="193">
+      <c r="BG114" s="200"/>
+      <c r="BH114" s="199">
         <v>22</v>
       </c>
-      <c r="BI114" s="194"/>
-      <c r="BJ114" s="193">
+      <c r="BI114" s="200"/>
+      <c r="BJ114" s="199">
         <v>22</v>
       </c>
-      <c r="BK114" s="194"/>
-      <c r="BL114" s="193">
+      <c r="BK114" s="200"/>
+      <c r="BL114" s="199">
         <v>22</v>
       </c>
-      <c r="BM114" s="194"/>
-      <c r="BN114" s="193">
+      <c r="BM114" s="200"/>
+      <c r="BN114" s="199">
         <v>22</v>
       </c>
-      <c r="BO114" s="194"/>
-      <c r="BP114" s="193">
+      <c r="BO114" s="200"/>
+      <c r="BP114" s="199">
         <v>0</v>
       </c>
-      <c r="BQ114" s="194"/>
-      <c r="BR114" s="193">
+      <c r="BQ114" s="200"/>
+      <c r="BR114" s="199">
         <v>0</v>
       </c>
-      <c r="BS114" s="194"/>
+      <c r="BS114" s="200"/>
     </row>
     <row r="115" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B115" s="208"/>
-      <c r="C115" s="198"/>
-      <c r="D115" s="198"/>
-      <c r="E115" s="198"/>
-      <c r="F115" s="198"/>
-      <c r="G115" s="198"/>
-      <c r="H115" s="198"/>
-      <c r="I115" s="198"/>
-      <c r="J115" s="198"/>
-      <c r="K115" s="198"/>
-      <c r="L115" s="198"/>
-      <c r="M115" s="198"/>
-      <c r="N115" s="198"/>
-      <c r="O115" s="209"/>
-      <c r="P115" s="208"/>
-      <c r="Q115" s="198"/>
-      <c r="R115" s="198"/>
-      <c r="S115" s="198"/>
-      <c r="T115" s="198"/>
-      <c r="U115" s="198"/>
-      <c r="V115" s="198"/>
-      <c r="W115" s="198"/>
-      <c r="X115" s="198"/>
-      <c r="Y115" s="198"/>
-      <c r="Z115" s="198"/>
-      <c r="AA115" s="198"/>
-      <c r="AB115" s="198"/>
-      <c r="AC115" s="209"/>
-      <c r="AD115" s="208"/>
-      <c r="AE115" s="198"/>
-      <c r="AF115" s="198"/>
-      <c r="AG115" s="198"/>
-      <c r="AH115" s="198"/>
-      <c r="AI115" s="198"/>
-      <c r="AJ115" s="198"/>
-      <c r="AK115" s="198"/>
-      <c r="AL115" s="198"/>
-      <c r="AM115" s="198"/>
-      <c r="AN115" s="198"/>
-      <c r="AO115" s="198"/>
-      <c r="AP115" s="198"/>
-      <c r="AQ115" s="209"/>
-      <c r="AR115" s="208"/>
-      <c r="AS115" s="198"/>
-      <c r="AT115" s="198"/>
-      <c r="AU115" s="198"/>
-      <c r="AV115" s="198"/>
-      <c r="AW115" s="198"/>
-      <c r="AX115" s="198"/>
-      <c r="AY115" s="198"/>
-      <c r="AZ115" s="198"/>
-      <c r="BA115" s="198"/>
-      <c r="BB115" s="198"/>
-      <c r="BC115" s="198"/>
-      <c r="BD115" s="198"/>
-      <c r="BE115" s="209"/>
-      <c r="BF115" s="208"/>
-      <c r="BG115" s="198"/>
-      <c r="BH115" s="198"/>
-      <c r="BI115" s="198"/>
-      <c r="BJ115" s="198"/>
-      <c r="BK115" s="198"/>
-      <c r="BL115" s="198"/>
-      <c r="BM115" s="198"/>
-      <c r="BN115" s="198"/>
-      <c r="BO115" s="198"/>
-      <c r="BP115" s="198"/>
-      <c r="BQ115" s="198"/>
-      <c r="BR115" s="198"/>
-      <c r="BS115" s="209"/>
+      <c r="B115" s="214"/>
+      <c r="C115" s="204"/>
+      <c r="D115" s="204"/>
+      <c r="E115" s="204"/>
+      <c r="F115" s="204"/>
+      <c r="G115" s="204"/>
+      <c r="H115" s="204"/>
+      <c r="I115" s="204"/>
+      <c r="J115" s="204"/>
+      <c r="K115" s="204"/>
+      <c r="L115" s="204"/>
+      <c r="M115" s="204"/>
+      <c r="N115" s="204"/>
+      <c r="O115" s="215"/>
+      <c r="P115" s="214"/>
+      <c r="Q115" s="204"/>
+      <c r="R115" s="204"/>
+      <c r="S115" s="204"/>
+      <c r="T115" s="204"/>
+      <c r="U115" s="204"/>
+      <c r="V115" s="204"/>
+      <c r="W115" s="204"/>
+      <c r="X115" s="204"/>
+      <c r="Y115" s="204"/>
+      <c r="Z115" s="204"/>
+      <c r="AA115" s="204"/>
+      <c r="AB115" s="204"/>
+      <c r="AC115" s="215"/>
+      <c r="AD115" s="214"/>
+      <c r="AE115" s="204"/>
+      <c r="AF115" s="204"/>
+      <c r="AG115" s="204"/>
+      <c r="AH115" s="204"/>
+      <c r="AI115" s="204"/>
+      <c r="AJ115" s="204"/>
+      <c r="AK115" s="204"/>
+      <c r="AL115" s="204"/>
+      <c r="AM115" s="204"/>
+      <c r="AN115" s="204"/>
+      <c r="AO115" s="204"/>
+      <c r="AP115" s="204"/>
+      <c r="AQ115" s="215"/>
+      <c r="AR115" s="214"/>
+      <c r="AS115" s="204"/>
+      <c r="AT115" s="204"/>
+      <c r="AU115" s="204"/>
+      <c r="AV115" s="204"/>
+      <c r="AW115" s="204"/>
+      <c r="AX115" s="204"/>
+      <c r="AY115" s="204"/>
+      <c r="AZ115" s="204"/>
+      <c r="BA115" s="204"/>
+      <c r="BB115" s="204"/>
+      <c r="BC115" s="204"/>
+      <c r="BD115" s="204"/>
+      <c r="BE115" s="215"/>
+      <c r="BF115" s="214"/>
+      <c r="BG115" s="204"/>
+      <c r="BH115" s="204"/>
+      <c r="BI115" s="204"/>
+      <c r="BJ115" s="204"/>
+      <c r="BK115" s="204"/>
+      <c r="BL115" s="204"/>
+      <c r="BM115" s="204"/>
+      <c r="BN115" s="204"/>
+      <c r="BO115" s="204"/>
+      <c r="BP115" s="204"/>
+      <c r="BQ115" s="204"/>
+      <c r="BR115" s="204"/>
+      <c r="BS115" s="215"/>
     </row>
     <row r="116" spans="1:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="227"/>
-      <c r="B116" s="233" t="s">
+      <c r="A116" s="233"/>
+      <c r="B116" s="239" t="s">
         <v>232</v>
       </c>
-      <c r="C116" s="211"/>
-      <c r="D116" s="211"/>
-      <c r="E116" s="211"/>
-      <c r="F116" s="211"/>
-      <c r="G116" s="211"/>
-      <c r="H116" s="211"/>
-      <c r="I116" s="211"/>
-      <c r="J116" s="211"/>
-      <c r="K116" s="211"/>
-      <c r="L116" s="211"/>
-      <c r="M116" s="211"/>
-      <c r="N116" s="211"/>
-      <c r="O116" s="212"/>
-      <c r="P116" s="233" t="s">
+      <c r="C116" s="217"/>
+      <c r="D116" s="217"/>
+      <c r="E116" s="217"/>
+      <c r="F116" s="217"/>
+      <c r="G116" s="217"/>
+      <c r="H116" s="217"/>
+      <c r="I116" s="217"/>
+      <c r="J116" s="217"/>
+      <c r="K116" s="217"/>
+      <c r="L116" s="217"/>
+      <c r="M116" s="217"/>
+      <c r="N116" s="217"/>
+      <c r="O116" s="218"/>
+      <c r="P116" s="239" t="s">
         <v>233</v>
       </c>
-      <c r="Q116" s="211"/>
-      <c r="R116" s="211"/>
-      <c r="S116" s="211"/>
-      <c r="T116" s="211"/>
-      <c r="U116" s="211"/>
-      <c r="V116" s="211"/>
-      <c r="W116" s="211"/>
-      <c r="X116" s="211"/>
-      <c r="Y116" s="211"/>
-      <c r="Z116" s="211"/>
-      <c r="AA116" s="211"/>
-      <c r="AB116" s="211"/>
-      <c r="AC116" s="212"/>
-      <c r="AD116" s="233" t="s">
+      <c r="Q116" s="217"/>
+      <c r="R116" s="217"/>
+      <c r="S116" s="217"/>
+      <c r="T116" s="217"/>
+      <c r="U116" s="217"/>
+      <c r="V116" s="217"/>
+      <c r="W116" s="217"/>
+      <c r="X116" s="217"/>
+      <c r="Y116" s="217"/>
+      <c r="Z116" s="217"/>
+      <c r="AA116" s="217"/>
+      <c r="AB116" s="217"/>
+      <c r="AC116" s="218"/>
+      <c r="AD116" s="239" t="s">
         <v>234</v>
       </c>
-      <c r="AE116" s="211"/>
-      <c r="AF116" s="211"/>
-      <c r="AG116" s="211"/>
-      <c r="AH116" s="211"/>
-      <c r="AI116" s="211"/>
-      <c r="AJ116" s="211"/>
-      <c r="AK116" s="211"/>
-      <c r="AL116" s="211"/>
-      <c r="AM116" s="211"/>
-      <c r="AN116" s="211"/>
-      <c r="AO116" s="211"/>
-      <c r="AP116" s="211"/>
-      <c r="AQ116" s="212"/>
-      <c r="AR116" s="233"/>
-      <c r="AS116" s="211"/>
-      <c r="AT116" s="211"/>
-      <c r="AU116" s="211"/>
-      <c r="AV116" s="211"/>
-      <c r="AW116" s="211"/>
-      <c r="AX116" s="211"/>
-      <c r="AY116" s="211"/>
-      <c r="AZ116" s="211"/>
-      <c r="BA116" s="211"/>
-      <c r="BB116" s="211"/>
-      <c r="BC116" s="211"/>
-      <c r="BD116" s="211"/>
-      <c r="BE116" s="212"/>
-      <c r="BF116" s="233"/>
-      <c r="BG116" s="211"/>
-      <c r="BH116" s="211"/>
-      <c r="BI116" s="211"/>
-      <c r="BJ116" s="211"/>
-      <c r="BK116" s="211"/>
-      <c r="BL116" s="211"/>
-      <c r="BM116" s="211"/>
-      <c r="BN116" s="211"/>
-      <c r="BO116" s="211"/>
-      <c r="BP116" s="211"/>
-      <c r="BQ116" s="211"/>
-      <c r="BR116" s="211"/>
-      <c r="BS116" s="212"/>
+      <c r="AE116" s="217"/>
+      <c r="AF116" s="217"/>
+      <c r="AG116" s="217"/>
+      <c r="AH116" s="217"/>
+      <c r="AI116" s="217"/>
+      <c r="AJ116" s="217"/>
+      <c r="AK116" s="217"/>
+      <c r="AL116" s="217"/>
+      <c r="AM116" s="217"/>
+      <c r="AN116" s="217"/>
+      <c r="AO116" s="217"/>
+      <c r="AP116" s="217"/>
+      <c r="AQ116" s="218"/>
+      <c r="AR116" s="239"/>
+      <c r="AS116" s="217"/>
+      <c r="AT116" s="217"/>
+      <c r="AU116" s="217"/>
+      <c r="AV116" s="217"/>
+      <c r="AW116" s="217"/>
+      <c r="AX116" s="217"/>
+      <c r="AY116" s="217"/>
+      <c r="AZ116" s="217"/>
+      <c r="BA116" s="217"/>
+      <c r="BB116" s="217"/>
+      <c r="BC116" s="217"/>
+      <c r="BD116" s="217"/>
+      <c r="BE116" s="218"/>
+      <c r="BF116" s="239"/>
+      <c r="BG116" s="217"/>
+      <c r="BH116" s="217"/>
+      <c r="BI116" s="217"/>
+      <c r="BJ116" s="217"/>
+      <c r="BK116" s="217"/>
+      <c r="BL116" s="217"/>
+      <c r="BM116" s="217"/>
+      <c r="BN116" s="217"/>
+      <c r="BO116" s="217"/>
+      <c r="BP116" s="217"/>
+      <c r="BQ116" s="217"/>
+      <c r="BR116" s="217"/>
+      <c r="BS116" s="218"/>
     </row>
     <row r="117" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A117" s="228"/>
-      <c r="B117" s="213"/>
-      <c r="C117" s="214"/>
-      <c r="D117" s="214"/>
-      <c r="E117" s="214"/>
-      <c r="F117" s="214"/>
-      <c r="G117" s="214"/>
-      <c r="H117" s="214"/>
-      <c r="I117" s="214"/>
-      <c r="J117" s="214"/>
-      <c r="K117" s="214"/>
-      <c r="L117" s="214"/>
-      <c r="M117" s="214"/>
-      <c r="N117" s="214"/>
-      <c r="O117" s="215"/>
-      <c r="P117" s="213"/>
-      <c r="Q117" s="214"/>
-      <c r="R117" s="214"/>
-      <c r="S117" s="214"/>
-      <c r="T117" s="214"/>
-      <c r="U117" s="214"/>
-      <c r="V117" s="214"/>
-      <c r="W117" s="214"/>
-      <c r="X117" s="214"/>
-      <c r="Y117" s="214"/>
-      <c r="Z117" s="214"/>
-      <c r="AA117" s="214"/>
-      <c r="AB117" s="214"/>
-      <c r="AC117" s="215"/>
-      <c r="AD117" s="213"/>
-      <c r="AE117" s="214"/>
-      <c r="AF117" s="214"/>
-      <c r="AG117" s="214"/>
-      <c r="AH117" s="214"/>
-      <c r="AI117" s="214"/>
-      <c r="AJ117" s="214"/>
-      <c r="AK117" s="214"/>
-      <c r="AL117" s="214"/>
-      <c r="AM117" s="214"/>
-      <c r="AN117" s="214"/>
-      <c r="AO117" s="214"/>
-      <c r="AP117" s="214"/>
-      <c r="AQ117" s="215"/>
-      <c r="AR117" s="213"/>
-      <c r="AS117" s="214"/>
-      <c r="AT117" s="214"/>
-      <c r="AU117" s="214"/>
-      <c r="AV117" s="214"/>
-      <c r="AW117" s="214"/>
-      <c r="AX117" s="214"/>
-      <c r="AY117" s="214"/>
-      <c r="AZ117" s="214"/>
-      <c r="BA117" s="214"/>
-      <c r="BB117" s="214"/>
-      <c r="BC117" s="214"/>
-      <c r="BD117" s="214"/>
-      <c r="BE117" s="215"/>
-      <c r="BF117" s="213"/>
-      <c r="BG117" s="214"/>
-      <c r="BH117" s="214"/>
-      <c r="BI117" s="214"/>
-      <c r="BJ117" s="214"/>
-      <c r="BK117" s="214"/>
-      <c r="BL117" s="214"/>
-      <c r="BM117" s="214"/>
-      <c r="BN117" s="214"/>
-      <c r="BO117" s="214"/>
-      <c r="BP117" s="214"/>
-      <c r="BQ117" s="214"/>
-      <c r="BR117" s="214"/>
-      <c r="BS117" s="215"/>
+      <c r="A117" s="234"/>
+      <c r="B117" s="219"/>
+      <c r="C117" s="220"/>
+      <c r="D117" s="220"/>
+      <c r="E117" s="220"/>
+      <c r="F117" s="220"/>
+      <c r="G117" s="220"/>
+      <c r="H117" s="220"/>
+      <c r="I117" s="220"/>
+      <c r="J117" s="220"/>
+      <c r="K117" s="220"/>
+      <c r="L117" s="220"/>
+      <c r="M117" s="220"/>
+      <c r="N117" s="220"/>
+      <c r="O117" s="221"/>
+      <c r="P117" s="219"/>
+      <c r="Q117" s="220"/>
+      <c r="R117" s="220"/>
+      <c r="S117" s="220"/>
+      <c r="T117" s="220"/>
+      <c r="U117" s="220"/>
+      <c r="V117" s="220"/>
+      <c r="W117" s="220"/>
+      <c r="X117" s="220"/>
+      <c r="Y117" s="220"/>
+      <c r="Z117" s="220"/>
+      <c r="AA117" s="220"/>
+      <c r="AB117" s="220"/>
+      <c r="AC117" s="221"/>
+      <c r="AD117" s="219"/>
+      <c r="AE117" s="220"/>
+      <c r="AF117" s="220"/>
+      <c r="AG117" s="220"/>
+      <c r="AH117" s="220"/>
+      <c r="AI117" s="220"/>
+      <c r="AJ117" s="220"/>
+      <c r="AK117" s="220"/>
+      <c r="AL117" s="220"/>
+      <c r="AM117" s="220"/>
+      <c r="AN117" s="220"/>
+      <c r="AO117" s="220"/>
+      <c r="AP117" s="220"/>
+      <c r="AQ117" s="221"/>
+      <c r="AR117" s="219"/>
+      <c r="AS117" s="220"/>
+      <c r="AT117" s="220"/>
+      <c r="AU117" s="220"/>
+      <c r="AV117" s="220"/>
+      <c r="AW117" s="220"/>
+      <c r="AX117" s="220"/>
+      <c r="AY117" s="220"/>
+      <c r="AZ117" s="220"/>
+      <c r="BA117" s="220"/>
+      <c r="BB117" s="220"/>
+      <c r="BC117" s="220"/>
+      <c r="BD117" s="220"/>
+      <c r="BE117" s="221"/>
+      <c r="BF117" s="219"/>
+      <c r="BG117" s="220"/>
+      <c r="BH117" s="220"/>
+      <c r="BI117" s="220"/>
+      <c r="BJ117" s="220"/>
+      <c r="BK117" s="220"/>
+      <c r="BL117" s="220"/>
+      <c r="BM117" s="220"/>
+      <c r="BN117" s="220"/>
+      <c r="BO117" s="220"/>
+      <c r="BP117" s="220"/>
+      <c r="BQ117" s="220"/>
+      <c r="BR117" s="220"/>
+      <c r="BS117" s="221"/>
     </row>
     <row r="118" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A118" s="228"/>
-      <c r="B118" s="213"/>
-      <c r="C118" s="214"/>
-      <c r="D118" s="214"/>
-      <c r="E118" s="214"/>
-      <c r="F118" s="214"/>
-      <c r="G118" s="214"/>
-      <c r="H118" s="214"/>
-      <c r="I118" s="214"/>
-      <c r="J118" s="214"/>
-      <c r="K118" s="214"/>
-      <c r="L118" s="214"/>
-      <c r="M118" s="214"/>
-      <c r="N118" s="214"/>
-      <c r="O118" s="215"/>
-      <c r="P118" s="213"/>
-      <c r="Q118" s="214"/>
-      <c r="R118" s="214"/>
-      <c r="S118" s="214"/>
-      <c r="T118" s="214"/>
-      <c r="U118" s="214"/>
-      <c r="V118" s="214"/>
-      <c r="W118" s="214"/>
-      <c r="X118" s="214"/>
-      <c r="Y118" s="214"/>
-      <c r="Z118" s="214"/>
-      <c r="AA118" s="214"/>
-      <c r="AB118" s="214"/>
-      <c r="AC118" s="215"/>
-      <c r="AD118" s="213"/>
-      <c r="AE118" s="214"/>
-      <c r="AF118" s="214"/>
-      <c r="AG118" s="214"/>
-      <c r="AH118" s="214"/>
-      <c r="AI118" s="214"/>
-      <c r="AJ118" s="214"/>
-      <c r="AK118" s="214"/>
-      <c r="AL118" s="214"/>
-      <c r="AM118" s="214"/>
-      <c r="AN118" s="214"/>
-      <c r="AO118" s="214"/>
-      <c r="AP118" s="214"/>
-      <c r="AQ118" s="215"/>
-      <c r="AR118" s="213"/>
-      <c r="AS118" s="214"/>
-      <c r="AT118" s="214"/>
-      <c r="AU118" s="214"/>
-      <c r="AV118" s="214"/>
-      <c r="AW118" s="214"/>
-      <c r="AX118" s="214"/>
-      <c r="AY118" s="214"/>
-      <c r="AZ118" s="214"/>
-      <c r="BA118" s="214"/>
-      <c r="BB118" s="214"/>
-      <c r="BC118" s="214"/>
-      <c r="BD118" s="214"/>
-      <c r="BE118" s="215"/>
-      <c r="BF118" s="213"/>
-      <c r="BG118" s="214"/>
-      <c r="BH118" s="214"/>
-      <c r="BI118" s="214"/>
-      <c r="BJ118" s="214"/>
-      <c r="BK118" s="214"/>
-      <c r="BL118" s="214"/>
-      <c r="BM118" s="214"/>
-      <c r="BN118" s="214"/>
-      <c r="BO118" s="214"/>
-      <c r="BP118" s="214"/>
-      <c r="BQ118" s="214"/>
-      <c r="BR118" s="214"/>
-      <c r="BS118" s="215"/>
+      <c r="A118" s="234"/>
+      <c r="B118" s="219"/>
+      <c r="C118" s="220"/>
+      <c r="D118" s="220"/>
+      <c r="E118" s="220"/>
+      <c r="F118" s="220"/>
+      <c r="G118" s="220"/>
+      <c r="H118" s="220"/>
+      <c r="I118" s="220"/>
+      <c r="J118" s="220"/>
+      <c r="K118" s="220"/>
+      <c r="L118" s="220"/>
+      <c r="M118" s="220"/>
+      <c r="N118" s="220"/>
+      <c r="O118" s="221"/>
+      <c r="P118" s="219"/>
+      <c r="Q118" s="220"/>
+      <c r="R118" s="220"/>
+      <c r="S118" s="220"/>
+      <c r="T118" s="220"/>
+      <c r="U118" s="220"/>
+      <c r="V118" s="220"/>
+      <c r="W118" s="220"/>
+      <c r="X118" s="220"/>
+      <c r="Y118" s="220"/>
+      <c r="Z118" s="220"/>
+      <c r="AA118" s="220"/>
+      <c r="AB118" s="220"/>
+      <c r="AC118" s="221"/>
+      <c r="AD118" s="219"/>
+      <c r="AE118" s="220"/>
+      <c r="AF118" s="220"/>
+      <c r="AG118" s="220"/>
+      <c r="AH118" s="220"/>
+      <c r="AI118" s="220"/>
+      <c r="AJ118" s="220"/>
+      <c r="AK118" s="220"/>
+      <c r="AL118" s="220"/>
+      <c r="AM118" s="220"/>
+      <c r="AN118" s="220"/>
+      <c r="AO118" s="220"/>
+      <c r="AP118" s="220"/>
+      <c r="AQ118" s="221"/>
+      <c r="AR118" s="219"/>
+      <c r="AS118" s="220"/>
+      <c r="AT118" s="220"/>
+      <c r="AU118" s="220"/>
+      <c r="AV118" s="220"/>
+      <c r="AW118" s="220"/>
+      <c r="AX118" s="220"/>
+      <c r="AY118" s="220"/>
+      <c r="AZ118" s="220"/>
+      <c r="BA118" s="220"/>
+      <c r="BB118" s="220"/>
+      <c r="BC118" s="220"/>
+      <c r="BD118" s="220"/>
+      <c r="BE118" s="221"/>
+      <c r="BF118" s="219"/>
+      <c r="BG118" s="220"/>
+      <c r="BH118" s="220"/>
+      <c r="BI118" s="220"/>
+      <c r="BJ118" s="220"/>
+      <c r="BK118" s="220"/>
+      <c r="BL118" s="220"/>
+      <c r="BM118" s="220"/>
+      <c r="BN118" s="220"/>
+      <c r="BO118" s="220"/>
+      <c r="BP118" s="220"/>
+      <c r="BQ118" s="220"/>
+      <c r="BR118" s="220"/>
+      <c r="BS118" s="221"/>
     </row>
     <row r="119" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A119" s="228"/>
-      <c r="B119" s="213"/>
-      <c r="C119" s="214"/>
-      <c r="D119" s="214"/>
-      <c r="E119" s="214"/>
-      <c r="F119" s="214"/>
-      <c r="G119" s="214"/>
-      <c r="H119" s="214"/>
-      <c r="I119" s="214"/>
-      <c r="J119" s="214"/>
-      <c r="K119" s="214"/>
-      <c r="L119" s="214"/>
-      <c r="M119" s="214"/>
-      <c r="N119" s="214"/>
-      <c r="O119" s="215"/>
-      <c r="P119" s="213"/>
-      <c r="Q119" s="214"/>
-      <c r="R119" s="214"/>
-      <c r="S119" s="214"/>
-      <c r="T119" s="214"/>
-      <c r="U119" s="214"/>
-      <c r="V119" s="214"/>
-      <c r="W119" s="214"/>
-      <c r="X119" s="214"/>
-      <c r="Y119" s="214"/>
-      <c r="Z119" s="214"/>
-      <c r="AA119" s="214"/>
-      <c r="AB119" s="214"/>
-      <c r="AC119" s="215"/>
-      <c r="AD119" s="213"/>
-      <c r="AE119" s="214"/>
-      <c r="AF119" s="214"/>
-      <c r="AG119" s="214"/>
-      <c r="AH119" s="214"/>
-      <c r="AI119" s="214"/>
-      <c r="AJ119" s="214"/>
-      <c r="AK119" s="214"/>
-      <c r="AL119" s="214"/>
-      <c r="AM119" s="214"/>
-      <c r="AN119" s="214"/>
-      <c r="AO119" s="214"/>
-      <c r="AP119" s="214"/>
-      <c r="AQ119" s="215"/>
-      <c r="AR119" s="213"/>
-      <c r="AS119" s="214"/>
-      <c r="AT119" s="214"/>
-      <c r="AU119" s="214"/>
-      <c r="AV119" s="214"/>
-      <c r="AW119" s="214"/>
-      <c r="AX119" s="214"/>
-      <c r="AY119" s="214"/>
-      <c r="AZ119" s="214"/>
-      <c r="BA119" s="214"/>
-      <c r="BB119" s="214"/>
-      <c r="BC119" s="214"/>
-      <c r="BD119" s="214"/>
-      <c r="BE119" s="215"/>
-      <c r="BF119" s="213"/>
-      <c r="BG119" s="214"/>
-      <c r="BH119" s="214"/>
-      <c r="BI119" s="214"/>
-      <c r="BJ119" s="214"/>
-      <c r="BK119" s="214"/>
-      <c r="BL119" s="214"/>
-      <c r="BM119" s="214"/>
-      <c r="BN119" s="214"/>
-      <c r="BO119" s="214"/>
-      <c r="BP119" s="214"/>
-      <c r="BQ119" s="214"/>
-      <c r="BR119" s="214"/>
-      <c r="BS119" s="215"/>
+      <c r="A119" s="234"/>
+      <c r="B119" s="219"/>
+      <c r="C119" s="220"/>
+      <c r="D119" s="220"/>
+      <c r="E119" s="220"/>
+      <c r="F119" s="220"/>
+      <c r="G119" s="220"/>
+      <c r="H119" s="220"/>
+      <c r="I119" s="220"/>
+      <c r="J119" s="220"/>
+      <c r="K119" s="220"/>
+      <c r="L119" s="220"/>
+      <c r="M119" s="220"/>
+      <c r="N119" s="220"/>
+      <c r="O119" s="221"/>
+      <c r="P119" s="219"/>
+      <c r="Q119" s="220"/>
+      <c r="R119" s="220"/>
+      <c r="S119" s="220"/>
+      <c r="T119" s="220"/>
+      <c r="U119" s="220"/>
+      <c r="V119" s="220"/>
+      <c r="W119" s="220"/>
+      <c r="X119" s="220"/>
+      <c r="Y119" s="220"/>
+      <c r="Z119" s="220"/>
+      <c r="AA119" s="220"/>
+      <c r="AB119" s="220"/>
+      <c r="AC119" s="221"/>
+      <c r="AD119" s="219"/>
+      <c r="AE119" s="220"/>
+      <c r="AF119" s="220"/>
+      <c r="AG119" s="220"/>
+      <c r="AH119" s="220"/>
+      <c r="AI119" s="220"/>
+      <c r="AJ119" s="220"/>
+      <c r="AK119" s="220"/>
+      <c r="AL119" s="220"/>
+      <c r="AM119" s="220"/>
+      <c r="AN119" s="220"/>
+      <c r="AO119" s="220"/>
+      <c r="AP119" s="220"/>
+      <c r="AQ119" s="221"/>
+      <c r="AR119" s="219"/>
+      <c r="AS119" s="220"/>
+      <c r="AT119" s="220"/>
+      <c r="AU119" s="220"/>
+      <c r="AV119" s="220"/>
+      <c r="AW119" s="220"/>
+      <c r="AX119" s="220"/>
+      <c r="AY119" s="220"/>
+      <c r="AZ119" s="220"/>
+      <c r="BA119" s="220"/>
+      <c r="BB119" s="220"/>
+      <c r="BC119" s="220"/>
+      <c r="BD119" s="220"/>
+      <c r="BE119" s="221"/>
+      <c r="BF119" s="219"/>
+      <c r="BG119" s="220"/>
+      <c r="BH119" s="220"/>
+      <c r="BI119" s="220"/>
+      <c r="BJ119" s="220"/>
+      <c r="BK119" s="220"/>
+      <c r="BL119" s="220"/>
+      <c r="BM119" s="220"/>
+      <c r="BN119" s="220"/>
+      <c r="BO119" s="220"/>
+      <c r="BP119" s="220"/>
+      <c r="BQ119" s="220"/>
+      <c r="BR119" s="220"/>
+      <c r="BS119" s="221"/>
     </row>
     <row r="120" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A120" s="228"/>
-      <c r="B120" s="213"/>
-      <c r="C120" s="214"/>
-      <c r="D120" s="214"/>
-      <c r="E120" s="214"/>
-      <c r="F120" s="214"/>
-      <c r="G120" s="214"/>
-      <c r="H120" s="214"/>
-      <c r="I120" s="214"/>
-      <c r="J120" s="214"/>
-      <c r="K120" s="214"/>
-      <c r="L120" s="214"/>
-      <c r="M120" s="214"/>
-      <c r="N120" s="214"/>
-      <c r="O120" s="215"/>
-      <c r="P120" s="213"/>
-      <c r="Q120" s="214"/>
-      <c r="R120" s="214"/>
-      <c r="S120" s="214"/>
-      <c r="T120" s="214"/>
-      <c r="U120" s="214"/>
-      <c r="V120" s="214"/>
-      <c r="W120" s="214"/>
-      <c r="X120" s="214"/>
-      <c r="Y120" s="214"/>
-      <c r="Z120" s="214"/>
-      <c r="AA120" s="214"/>
-      <c r="AB120" s="214"/>
-      <c r="AC120" s="215"/>
-      <c r="AD120" s="213"/>
-      <c r="AE120" s="214"/>
-      <c r="AF120" s="214"/>
-      <c r="AG120" s="214"/>
-      <c r="AH120" s="214"/>
-      <c r="AI120" s="214"/>
-      <c r="AJ120" s="214"/>
-      <c r="AK120" s="214"/>
-      <c r="AL120" s="214"/>
-      <c r="AM120" s="214"/>
-      <c r="AN120" s="214"/>
-      <c r="AO120" s="214"/>
-      <c r="AP120" s="214"/>
-      <c r="AQ120" s="215"/>
-      <c r="AR120" s="213"/>
-      <c r="AS120" s="214"/>
-      <c r="AT120" s="214"/>
-      <c r="AU120" s="214"/>
-      <c r="AV120" s="214"/>
-      <c r="AW120" s="214"/>
-      <c r="AX120" s="214"/>
-      <c r="AY120" s="214"/>
-      <c r="AZ120" s="214"/>
-      <c r="BA120" s="214"/>
-      <c r="BB120" s="214"/>
-      <c r="BC120" s="214"/>
-      <c r="BD120" s="214"/>
-      <c r="BE120" s="215"/>
-      <c r="BF120" s="213"/>
-      <c r="BG120" s="214"/>
-      <c r="BH120" s="214"/>
-      <c r="BI120" s="214"/>
-      <c r="BJ120" s="214"/>
-      <c r="BK120" s="214"/>
-      <c r="BL120" s="214"/>
-      <c r="BM120" s="214"/>
-      <c r="BN120" s="214"/>
-      <c r="BO120" s="214"/>
-      <c r="BP120" s="214"/>
-      <c r="BQ120" s="214"/>
-      <c r="BR120" s="214"/>
-      <c r="BS120" s="215"/>
+      <c r="A120" s="234"/>
+      <c r="B120" s="219"/>
+      <c r="C120" s="220"/>
+      <c r="D120" s="220"/>
+      <c r="E120" s="220"/>
+      <c r="F120" s="220"/>
+      <c r="G120" s="220"/>
+      <c r="H120" s="220"/>
+      <c r="I120" s="220"/>
+      <c r="J120" s="220"/>
+      <c r="K120" s="220"/>
+      <c r="L120" s="220"/>
+      <c r="M120" s="220"/>
+      <c r="N120" s="220"/>
+      <c r="O120" s="221"/>
+      <c r="P120" s="219"/>
+      <c r="Q120" s="220"/>
+      <c r="R120" s="220"/>
+      <c r="S120" s="220"/>
+      <c r="T120" s="220"/>
+      <c r="U120" s="220"/>
+      <c r="V120" s="220"/>
+      <c r="W120" s="220"/>
+      <c r="X120" s="220"/>
+      <c r="Y120" s="220"/>
+      <c r="Z120" s="220"/>
+      <c r="AA120" s="220"/>
+      <c r="AB120" s="220"/>
+      <c r="AC120" s="221"/>
+      <c r="AD120" s="219"/>
+      <c r="AE120" s="220"/>
+      <c r="AF120" s="220"/>
+      <c r="AG120" s="220"/>
+      <c r="AH120" s="220"/>
+      <c r="AI120" s="220"/>
+      <c r="AJ120" s="220"/>
+      <c r="AK120" s="220"/>
+      <c r="AL120" s="220"/>
+      <c r="AM120" s="220"/>
+      <c r="AN120" s="220"/>
+      <c r="AO120" s="220"/>
+      <c r="AP120" s="220"/>
+      <c r="AQ120" s="221"/>
+      <c r="AR120" s="219"/>
+      <c r="AS120" s="220"/>
+      <c r="AT120" s="220"/>
+      <c r="AU120" s="220"/>
+      <c r="AV120" s="220"/>
+      <c r="AW120" s="220"/>
+      <c r="AX120" s="220"/>
+      <c r="AY120" s="220"/>
+      <c r="AZ120" s="220"/>
+      <c r="BA120" s="220"/>
+      <c r="BB120" s="220"/>
+      <c r="BC120" s="220"/>
+      <c r="BD120" s="220"/>
+      <c r="BE120" s="221"/>
+      <c r="BF120" s="219"/>
+      <c r="BG120" s="220"/>
+      <c r="BH120" s="220"/>
+      <c r="BI120" s="220"/>
+      <c r="BJ120" s="220"/>
+      <c r="BK120" s="220"/>
+      <c r="BL120" s="220"/>
+      <c r="BM120" s="220"/>
+      <c r="BN120" s="220"/>
+      <c r="BO120" s="220"/>
+      <c r="BP120" s="220"/>
+      <c r="BQ120" s="220"/>
+      <c r="BR120" s="220"/>
+      <c r="BS120" s="221"/>
     </row>
     <row r="121" spans="1:71" x14ac:dyDescent="0.2">
-      <c r="A121" s="228"/>
-      <c r="B121" s="213"/>
-      <c r="C121" s="214"/>
-      <c r="D121" s="214"/>
-      <c r="E121" s="214"/>
-      <c r="F121" s="214"/>
-      <c r="G121" s="214"/>
-      <c r="H121" s="214"/>
-      <c r="I121" s="214"/>
-      <c r="J121" s="214"/>
-      <c r="K121" s="214"/>
-      <c r="L121" s="214"/>
-      <c r="M121" s="214"/>
-      <c r="N121" s="214"/>
-      <c r="O121" s="215"/>
-      <c r="P121" s="213"/>
-      <c r="Q121" s="214"/>
-      <c r="R121" s="214"/>
-      <c r="S121" s="214"/>
-      <c r="T121" s="214"/>
-      <c r="U121" s="214"/>
-      <c r="V121" s="214"/>
-      <c r="W121" s="214"/>
-      <c r="X121" s="214"/>
-      <c r="Y121" s="214"/>
-      <c r="Z121" s="214"/>
-      <c r="AA121" s="214"/>
-      <c r="AB121" s="214"/>
-      <c r="AC121" s="215"/>
-      <c r="AD121" s="213"/>
-      <c r="AE121" s="214"/>
-      <c r="AF121" s="214"/>
-      <c r="AG121" s="214"/>
-      <c r="AH121" s="214"/>
-      <c r="AI121" s="214"/>
-      <c r="AJ121" s="214"/>
-      <c r="AK121" s="214"/>
-      <c r="AL121" s="214"/>
-      <c r="AM121" s="214"/>
-      <c r="AN121" s="214"/>
-      <c r="AO121" s="214"/>
-      <c r="AP121" s="214"/>
-      <c r="AQ121" s="215"/>
-      <c r="AR121" s="213"/>
-      <c r="AS121" s="214"/>
-      <c r="AT121" s="214"/>
-      <c r="AU121" s="214"/>
-      <c r="AV121" s="214"/>
-      <c r="AW121" s="214"/>
-      <c r="AX121" s="214"/>
-      <c r="AY121" s="214"/>
-      <c r="AZ121" s="214"/>
-      <c r="BA121" s="214"/>
-      <c r="BB121" s="214"/>
-      <c r="BC121" s="214"/>
-      <c r="BD121" s="214"/>
-      <c r="BE121" s="215"/>
-      <c r="BF121" s="213"/>
-      <c r="BG121" s="214"/>
-      <c r="BH121" s="214"/>
-      <c r="BI121" s="214"/>
-      <c r="BJ121" s="214"/>
-      <c r="BK121" s="214"/>
-      <c r="BL121" s="214"/>
-      <c r="BM121" s="214"/>
-      <c r="BN121" s="214"/>
-      <c r="BO121" s="214"/>
-      <c r="BP121" s="214"/>
-      <c r="BQ121" s="214"/>
-      <c r="BR121" s="214"/>
-      <c r="BS121" s="215"/>
+      <c r="A121" s="234"/>
+      <c r="B121" s="219"/>
+      <c r="C121" s="220"/>
+      <c r="D121" s="220"/>
+      <c r="E121" s="220"/>
+      <c r="F121" s="220"/>
+      <c r="G121" s="220"/>
+      <c r="H121" s="220"/>
+      <c r="I121" s="220"/>
+      <c r="J121" s="220"/>
+      <c r="K121" s="220"/>
+      <c r="L121" s="220"/>
+      <c r="M121" s="220"/>
+      <c r="N121" s="220"/>
+      <c r="O121" s="221"/>
+      <c r="P121" s="219"/>
+      <c r="Q121" s="220"/>
+      <c r="R121" s="220"/>
+      <c r="S121" s="220"/>
+      <c r="T121" s="220"/>
+      <c r="U121" s="220"/>
+      <c r="V121" s="220"/>
+      <c r="W121" s="220"/>
+      <c r="X121" s="220"/>
+      <c r="Y121" s="220"/>
+      <c r="Z121" s="220"/>
+      <c r="AA121" s="220"/>
+      <c r="AB121" s="220"/>
+      <c r="AC121" s="221"/>
+      <c r="AD121" s="219"/>
+      <c r="AE121" s="220"/>
+      <c r="AF121" s="220"/>
+      <c r="AG121" s="220"/>
+      <c r="AH121" s="220"/>
+      <c r="AI121" s="220"/>
+      <c r="AJ121" s="220"/>
+      <c r="AK121" s="220"/>
+      <c r="AL121" s="220"/>
+      <c r="AM121" s="220"/>
+      <c r="AN121" s="220"/>
+      <c r="AO121" s="220"/>
+      <c r="AP121" s="220"/>
+      <c r="AQ121" s="221"/>
+      <c r="AR121" s="219"/>
+      <c r="AS121" s="220"/>
+      <c r="AT121" s="220"/>
+      <c r="AU121" s="220"/>
+      <c r="AV121" s="220"/>
+      <c r="AW121" s="220"/>
+      <c r="AX121" s="220"/>
+      <c r="AY121" s="220"/>
+      <c r="AZ121" s="220"/>
+      <c r="BA121" s="220"/>
+      <c r="BB121" s="220"/>
+      <c r="BC121" s="220"/>
+      <c r="BD121" s="220"/>
+      <c r="BE121" s="221"/>
+      <c r="BF121" s="219"/>
+      <c r="BG121" s="220"/>
+      <c r="BH121" s="220"/>
+      <c r="BI121" s="220"/>
+      <c r="BJ121" s="220"/>
+      <c r="BK121" s="220"/>
+      <c r="BL121" s="220"/>
+      <c r="BM121" s="220"/>
+      <c r="BN121" s="220"/>
+      <c r="BO121" s="220"/>
+      <c r="BP121" s="220"/>
+      <c r="BQ121" s="220"/>
+      <c r="BR121" s="220"/>
+      <c r="BS121" s="221"/>
     </row>
     <row r="122" spans="1:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="229"/>
-      <c r="B122" s="216"/>
-      <c r="C122" s="217"/>
-      <c r="D122" s="217"/>
-      <c r="E122" s="217"/>
-      <c r="F122" s="217"/>
-      <c r="G122" s="217"/>
-      <c r="H122" s="217"/>
-      <c r="I122" s="217"/>
-      <c r="J122" s="217"/>
-      <c r="K122" s="217"/>
-      <c r="L122" s="217"/>
-      <c r="M122" s="217"/>
-      <c r="N122" s="217"/>
-      <c r="O122" s="218"/>
-      <c r="P122" s="216"/>
-      <c r="Q122" s="217"/>
-      <c r="R122" s="217"/>
-      <c r="S122" s="217"/>
-      <c r="T122" s="217"/>
-      <c r="U122" s="217"/>
-      <c r="V122" s="217"/>
-      <c r="W122" s="217"/>
-      <c r="X122" s="217"/>
-      <c r="Y122" s="217"/>
-      <c r="Z122" s="217"/>
-      <c r="AA122" s="217"/>
-      <c r="AB122" s="217"/>
-      <c r="AC122" s="218"/>
-      <c r="AD122" s="216"/>
-      <c r="AE122" s="217"/>
-      <c r="AF122" s="217"/>
-      <c r="AG122" s="217"/>
-      <c r="AH122" s="217"/>
-      <c r="AI122" s="217"/>
-      <c r="AJ122" s="217"/>
-      <c r="AK122" s="217"/>
-      <c r="AL122" s="217"/>
-      <c r="AM122" s="217"/>
-      <c r="AN122" s="217"/>
-      <c r="AO122" s="217"/>
-      <c r="AP122" s="217"/>
-      <c r="AQ122" s="218"/>
-      <c r="AR122" s="216"/>
-      <c r="AS122" s="217"/>
-      <c r="AT122" s="217"/>
-      <c r="AU122" s="217"/>
-      <c r="AV122" s="217"/>
-      <c r="AW122" s="217"/>
-      <c r="AX122" s="217"/>
-      <c r="AY122" s="217"/>
-      <c r="AZ122" s="217"/>
-      <c r="BA122" s="217"/>
-      <c r="BB122" s="217"/>
-      <c r="BC122" s="217"/>
-      <c r="BD122" s="217"/>
-      <c r="BE122" s="218"/>
-      <c r="BF122" s="216"/>
-      <c r="BG122" s="217"/>
-      <c r="BH122" s="217"/>
-      <c r="BI122" s="217"/>
-      <c r="BJ122" s="217"/>
-      <c r="BK122" s="217"/>
-      <c r="BL122" s="217"/>
-      <c r="BM122" s="217"/>
-      <c r="BN122" s="217"/>
-      <c r="BO122" s="217"/>
-      <c r="BP122" s="217"/>
-      <c r="BQ122" s="217"/>
-      <c r="BR122" s="217"/>
-      <c r="BS122" s="218"/>
+      <c r="A122" s="235"/>
+      <c r="B122" s="222"/>
+      <c r="C122" s="223"/>
+      <c r="D122" s="223"/>
+      <c r="E122" s="223"/>
+      <c r="F122" s="223"/>
+      <c r="G122" s="223"/>
+      <c r="H122" s="223"/>
+      <c r="I122" s="223"/>
+      <c r="J122" s="223"/>
+      <c r="K122" s="223"/>
+      <c r="L122" s="223"/>
+      <c r="M122" s="223"/>
+      <c r="N122" s="223"/>
+      <c r="O122" s="224"/>
+      <c r="P122" s="222"/>
+      <c r="Q122" s="223"/>
+      <c r="R122" s="223"/>
+      <c r="S122" s="223"/>
+      <c r="T122" s="223"/>
+      <c r="U122" s="223"/>
+      <c r="V122" s="223"/>
+      <c r="W122" s="223"/>
+      <c r="X122" s="223"/>
+      <c r="Y122" s="223"/>
+      <c r="Z122" s="223"/>
+      <c r="AA122" s="223"/>
+      <c r="AB122" s="223"/>
+      <c r="AC122" s="224"/>
+      <c r="AD122" s="222"/>
+      <c r="AE122" s="223"/>
+      <c r="AF122" s="223"/>
+      <c r="AG122" s="223"/>
+      <c r="AH122" s="223"/>
+      <c r="AI122" s="223"/>
+      <c r="AJ122" s="223"/>
+      <c r="AK122" s="223"/>
+      <c r="AL122" s="223"/>
+      <c r="AM122" s="223"/>
+      <c r="AN122" s="223"/>
+      <c r="AO122" s="223"/>
+      <c r="AP122" s="223"/>
+      <c r="AQ122" s="224"/>
+      <c r="AR122" s="222"/>
+      <c r="AS122" s="223"/>
+      <c r="AT122" s="223"/>
+      <c r="AU122" s="223"/>
+      <c r="AV122" s="223"/>
+      <c r="AW122" s="223"/>
+      <c r="AX122" s="223"/>
+      <c r="AY122" s="223"/>
+      <c r="AZ122" s="223"/>
+      <c r="BA122" s="223"/>
+      <c r="BB122" s="223"/>
+      <c r="BC122" s="223"/>
+      <c r="BD122" s="223"/>
+      <c r="BE122" s="224"/>
+      <c r="BF122" s="222"/>
+      <c r="BG122" s="223"/>
+      <c r="BH122" s="223"/>
+      <c r="BI122" s="223"/>
+      <c r="BJ122" s="223"/>
+      <c r="BK122" s="223"/>
+      <c r="BL122" s="223"/>
+      <c r="BM122" s="223"/>
+      <c r="BN122" s="223"/>
+      <c r="BO122" s="223"/>
+      <c r="BP122" s="223"/>
+      <c r="BQ122" s="223"/>
+      <c r="BR122" s="223"/>
+      <c r="BS122" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="131">
@@ -32686,8 +32710,8 @@
     <mergeCell ref="AR115:BE115"/>
     <mergeCell ref="AH5:AI5"/>
     <mergeCell ref="B115:O115"/>
+    <mergeCell ref="R4:S4"/>
     <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="H114:I114"/>
     <mergeCell ref="V4:W4"/>
@@ -32707,8 +32731,8 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="BF5:BG5"/>
     <mergeCell ref="AV5:AW5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="AX5:AY5"/>
-    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="AT114:AU114"/>
@@ -32760,8 +32784,8 @@
     <mergeCell ref="X4:Y4"/>
     <mergeCell ref="Z4:AA4"/>
     <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="AV4:AW4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="AV4:AW4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="AX4:AY4"/>
